--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R4f1be4e8e4f248ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R020d2a68c42c490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R0bdf1e071b7343e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rc52f1c38ce79475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R79dc46bc4b644af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R0056127bd7ab4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R0e99866e9df84905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="Rac97019888d84025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R5802fa96ce794271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R5b2a9e3475fc4844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rb4636fcd74054b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R610ee252c64547c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R891b0f70b4e642df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rabd14d281f484466"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -176,7 +176,7 @@
     <x:xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="67">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -371,6 +371,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="6">
@@ -3178,10 +3181,8 @@
           <x:t xml:space="preserve">시스템</x:t>
         </x:is>
       </x:c>
-      <x:c r="G22" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이미지를 업로드하면 비동기로 고지서 유형(공동주택 관리비 / 전기 / 수도 / 도시가스)을 판별하고 포함된 항목별 청구 월·금액·사용량을 추출한다. 대표 양식은 관리비 통합 1종과 개별 전기 1종을 우선 지원한다. 자동 확정하지 않는다. 진행 화면에 진행률(%)과 "자동으로 확인하는 정보: 청구 월 · 납부 금액 · 사용량 · 고지서 유형"을 표시한다.</x:t>
-        </x:is>
+      <x:c r="G22" s="53" t="str">
+        <x:v>이미지를 업로드하면 비동기로 고지서 유형(공동주택 관리비 / 전기 / 수도 / 도시가스)을 판별하고 포함된 항목별 청구 월·금액·사용량을 추출한다. 대표 양식은 관리비 통합·개별 전기·개별 수도·개별 도시가스 각 1종의 고정 데모 템플릿을 지원한다. 자동 확정하지 않는다. 진행 화면에 진행률(%)과 "자동으로 확인하는 정보: 청구 월 · 납부 금액 · 사용량 · 고지서 유형"을 표시한다.</x:v>
       </x:c>
       <x:c r="H22" s="55" t="inlineStr">
         <x:is>
@@ -3223,10 +3224,8 @@
           <x:t xml:space="preserve">AN-03</x:t>
         </x:is>
       </x:c>
-      <x:c r="P22" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">외부 OCR API 연동. 관리비 통합·개별 전기 샘플 확보 필요(C-5)</x:t>
-        </x:is>
+      <x:c r="P22" s="53" t="str">
+        <x:v>CLOVA Template OCR 연동. 관리비 통합(43341)·개별 전기(43345)·개별 수도(43347)·개별 도시가스(43348) 템플릿 등록·테스트 완료</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="31" customFormat="1" ht="58.20000076293945" customHeight="1">
@@ -11088,10 +11087,8 @@
       <x:c r="A6" s="48" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">관리비 통합·개별 전기 고지서 OCR → 인식 결과 확인 → 3탭 수정 → 요약 확정 → 저장, 직접 입력 대체 경로, 항목 단위 중복 차단</x:t>
-        </x:is>
+      <x:c r="B6" s="53" t="str">
+        <x:v>관리비 통합·개별 전기·개별 수도·개별 도시가스 고지서 고정 템플릿 OCR → 인식 결과 확인 → 항목 수정 → 요약 확정 → 저장, 직접 입력 대체 경로, 항목 단위 중복 차단</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="31" customFormat="1" ht="18" customHeight="1">
@@ -11342,10 +11339,8 @@
       <x:c r="A34" s="48" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B34" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">개별 수도·도시가스 고지서 OCR, 지역난방 — 수도·가스는 직접 입력, 지역난방은 배출계수 미공개로 미지원</x:t>
-        </x:is>
+      <x:c r="B34" s="53" t="str">
+        <x:v>지역난방 — 배출계수 미공개로 미지원</x:v>
       </x:c>
     </x:row>
     <x:row r="35" s="31" customFormat="1" ht="18" customHeight="1">
@@ -12068,14 +12063,12 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" s="31" customFormat="1" ht="15" customHeight="1">
+    <x:row r="8" s="31" customFormat="1" ht="54" customHeight="1">
       <x:c r="A8" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">관리비 통합 고지서·개별 전기 고지서 OCR 샘플 확보 + 인식률</x:t>
-        </x:is>
+      <x:c r="B8" s="53" t="str">
+        <x:v>관리비 통합·개별 전기·개별 수도·개별 도시가스 고지서 OCR 샘플 확보 + 인식률</x:v>
       </x:c>
       <x:c r="C8" s="55" t="inlineStr">
         <x:is>
@@ -12092,7 +12085,9 @@
           <x:t xml:space="preserve">합성 샘플 제작 후 OCR API 테스트</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="55" t="n"/>
+      <x:c r="F8" s="67" t="str">
+        <x:v>2026-09-06 합성 샘플 및 CLOVA 템플릿 등록·테스트 완료 — 관리비 43341, 전기 43345, 수도 43347, 도시가스 43348</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" s="31" customFormat="1" ht="15" customHeight="1">
       <x:c r="A9" s="48" t="n">

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="Rac97019888d84025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R5802fa96ce794271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R5b2a9e3475fc4844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rb4636fcd74054b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R610ee252c64547c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R891b0f70b4e642df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rabd14d281f484466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R4da3c87cf56a42be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R6a8f165a2727430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rcfa9dc7112734a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R07054b95137e4935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Re6ceb0dc6b1d4712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R7f34ede5850a4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R0c281e0df5c344f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -176,7 +176,7 @@
     <x:xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -374,6 +374,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="6">
@@ -706,10 +709,8 @@
           <x:t xml:space="preserve">문서 기준일</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-09-03 (ver3.1 — 결정 C-1~C-13 반영)</x:t>
-        </x:is>
+      <x:c r="B3" s="34" t="str">
+        <x:v>2026-09-06 (ver3.1 — 결정 C-1~C-15 반영)</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="31" customFormat="1" ht="15" customHeight="1">
@@ -2497,10 +2498,8 @@
           <x:t xml:space="preserve">사용자</x:t>
         </x:is>
       </x:c>
-      <x:c r="G13" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시·도를 먼저 고르고 시·군·구를 고른다. 시·도 선택 전에는 시·군·구 셀을 비활성화한다. "비교 자료가 없는 지역은 더 넓은 범위의 평균을 쓰고, 그 범위를 화면에 표시해요"를 안내한다.</x:t>
-        </x:is>
+      <x:c r="G13" s="53" t="str">
+        <x:v>시연 대상은 서울특별시로 한정한다. 시·도 목록은 서울특별시 1건, 시·군·구 목록은 서울 25개 자치구를 제공한다. 행정안전부 행정표준코드관리시스템·행정표준코드 API를 출처로 참고하되 실행 중에는 resources/data/seoul-regions.json의 고정 목록을 사용한다. 시·도 선택 전에는 시·군·구 셀을 비활성화한다. "비교 자료가 없는 지역은 더 넓은 범위의 평균을 쓰고, 그 범위를 화면에 표시해요"를 안내한다.</x:v>
       </x:c>
       <x:c r="H13" s="55" t="inlineStr">
         <x:is>
@@ -2517,10 +2516,8 @@
           <x:t xml:space="preserve">미선택 시 다음 버튼 비활성</x:t>
         </x:is>
       </x:c>
-      <x:c r="K13" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">저장한 지역이 A-3 기준선 조회와 B-1 서울 거주 판정에 반영된다.</x:t>
-        </x:is>
+      <x:c r="K13" s="53" t="str">
+        <x:v>서울 25개 자치구가 모두 조회되고 저장한 지역이 A-3 기준선 조회와 B-1 서울 거주 판정에 반영된다.</x:v>
       </x:c>
       <x:c r="L13" s="48" t="inlineStr">
         <x:is>
@@ -10324,6 +10321,20 @@
         <x:v>D-1-01, COM-01</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="31.5" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>C-15</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>행정구역 목록</x:v>
+      </x:c>
+      <x:c r="C31" s="68" t="str">
+        <x:v>서비스 대상은 서울특별시로 한정. 행정안전부 행정표준코드를 출처로 참고하고 런타임에는 서울 25개 자치구 JSON 고정 목록 사용</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>A-1-01</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R4da3c87cf56a42be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R6a8f165a2727430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rcfa9dc7112734a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R07054b95137e4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Re6ceb0dc6b1d4712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R7f34ede5850a4415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R0c281e0df5c344f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="Recb0dbe78dcb4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R1fc5916c2c504cd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rfaa2435bcf364bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R5c535d3ce1654643"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Ra8297dd2e82a499b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rc2284ae499e84e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R8d8e43739a72441c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="34" t="str">
-        <x:v>2026-09-06 (ver3.1 — 결정 C-1~C-15 반영)</x:v>
+        <x:v>2026-09-06 (ver3.1 — 결정 C-1~C-16 반영)</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="31" customFormat="1" ht="15" customHeight="1">
@@ -8390,40 +8390,26 @@
           <x:t xml:space="preserve">D-1-04</x:t>
         </x:is>
       </x:c>
-      <x:c r="E90" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">포켓 메인</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F90" s="54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시스템</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G90" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">잔액 카드(잔액, 포켓 관리, 내 출금계좌 — 계좌번호 전체 표시(결정 A-2), 출금 신청하기, 전환 가능한 마일리지), 적립 내역 안내 배너, 최근 적립 내역 2건 + 전체 보기, "마일리지 전환은 1일 1회만 가능해요 · 전환 후 취소는 불가능하니 신중히 확인해 주세요" 안내를 표시한다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H90" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">balance, defaultAccount, convertibleMileage, recentTransactions[2]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I90" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">포켓 존재</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J90" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">—</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K90" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">신규 상태와 데이터 보유 상태가 각각 정상 표시된다.</x:t>
-        </x:is>
+      <x:c r="E90" s="53" t="str">
+        <x:v>포켓 메인</x:v>
+      </x:c>
+      <x:c r="F90" s="54" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G90" s="53" t="str">
+        <x:v>잔액 카드(잔액, 포켓 관리, 내 출금계좌 — 계좌번호 전체 표시(결정 A-2), 출금 신청하기, 전환 가능한 마일리지), 적립 내역 안내 배너, 적립·출금 구분 없이 최신 거래 4건 + 전체 보기, "마일리지 전환은 1일 1회만 가능해요 · 전환 후 취소는 불가능하니 신중히 확인해 주세요" 안내를 표시한다(결정 C-16).</x:v>
+      </x:c>
+      <x:c r="H90" s="55" t="str">
+        <x:v>balance, defaultAccount, convertibleMileage, recentTransactions[4]</x:v>
+      </x:c>
+      <x:c r="I90" s="53" t="str">
+        <x:v>포켓 존재</x:v>
+      </x:c>
+      <x:c r="J90" s="55" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K90" s="53" t="str">
+        <x:v>신규 상태와 데이터 보유 상태가 각각 정상 표시된다.</x:v>
       </x:c>
       <x:c r="L90" s="48" t="inlineStr">
         <x:is>
@@ -8466,40 +8452,26 @@
           <x:t xml:space="preserve">D-1-05</x:t>
         </x:is>
       </x:c>
-      <x:c r="E91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">적립 내역 전체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F91" s="54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사용자</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 적립액, 월별 그룹(최신순)과 소계(2026년 8월 +3,900원), 항목별 출처(에코/녹색생활 구분)·입금 배지·일시·거래 ID·금액을 표시한다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H91" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GET /pocket/transactions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거래 존재</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">빈 상태</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">월 소계 합이 누적 적립과 일치한다.</x:t>
-        </x:is>
+      <x:c r="E91" s="53" t="str">
+        <x:v>거래 내역 전체</x:v>
+      </x:c>
+      <x:c r="F91" s="54" t="str">
+        <x:v>사용자</x:v>
+      </x:c>
+      <x:c r="G91" s="53" t="str">
+        <x:v>전체·적립·출금 탭을 제공하고, 선택한 탭의 거래를 월별 그룹(최신순)으로 표시한다. 전체 탭은 모든 거래, 적립 탭은 CREDIT, 출금 탭은 DEBIT 거래를 조회하며 항목별 출처·상태 배지·일시·거래 ID·금액을 표시한다(결정 C-16).</x:v>
+      </x:c>
+      <x:c r="H91" s="55" t="str">
+        <x:v>GET /pocket/transactions</x:v>
+      </x:c>
+      <x:c r="I91" s="53" t="str">
+        <x:v>거래 존재</x:v>
+      </x:c>
+      <x:c r="J91" s="53" t="str">
+        <x:v>빈 상태</x:v>
+      </x:c>
+      <x:c r="K91" s="53" t="str">
+        <x:v>전체·적립·출금 탭에서 선택한 방향에 맞는 거래만 표시되고 월 소계는 완료된 입금은 양수, 완료된 출금은 음수로 계산된다.</x:v>
       </x:c>
       <x:c r="L91" s="48" t="inlineStr">
         <x:is>
@@ -8704,10 +8676,8 @@
           <x:t xml:space="preserve">사용자</x:t>
         </x:is>
       </x:c>
-      <x:c r="G94" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">마일리지 전환하기 / 현금으로 바꾸기를 누르면 금액·출처·"현금 아님"·취소 불가 안내를 보여준 뒤 에코마일리지 누리집으로 이동한다. 복귀 시 전환 완료로 모의 전환하고 에코마일리지 수령액 입금 거래(D-1-03)를 생성한다(결정 A-1, 참여신청 배너와 같은 패턴). 나중에를 고르면 포켓에 미전환 상태로 남긴다. 1일 1회, 평가 회차당 1회만 허용한다.</x:t>
-        </x:is>
+      <x:c r="G94" s="53" t="str">
+        <x:v>마일리지 전환하기 / 현금으로 바꾸기를 누르면 금액·출처·"현금 아님"·취소 불가 안내를 보여준 뒤 에코마일리지 상품 신청 페이지(https://ecomileage.seoul.go.kr/goods/apply.do)로 이동한다. 복귀 시 전환 완료로 모의 전환하고 에코마일리지 수령액 입금 거래(D-1-03)를 생성한다(결정 A-1·C-16, 참여신청 배너와 같은 패턴). 나중에를 고르면 포켓에 미전환 상태로 남긴다. 1일 1회, 평가 회차당 1회만 허용한다.</x:v>
       </x:c>
       <x:c r="H94" s="55" t="inlineStr">
         <x:is>
@@ -10335,6 +10305,20 @@
         <x:v>A-1-01</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="68" t="str">
+        <x:v>C-16</x:v>
+      </x:c>
+      <x:c r="B32" s="68" t="str">
+        <x:v>포켓 거래 내역 구성</x:v>
+      </x:c>
+      <x:c r="C32" s="68" t="str">
+        <x:v>포켓 홈에는 적립·출금 구분 없이 최신 거래 4건을 표시하고, 전체 내역 화면은 전체·적립·출금 탭으로 필터링. 전환 확인 후 에코마일리지 상품 신청 페이지로 이동</x:v>
+      </x:c>
+      <x:c r="D32" s="68" t="str">
+        <x:v>D-1-04, D-1-05, D-2-02</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="Recb0dbe78dcb4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R1fc5916c2c504cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rfaa2435bcf364bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R5c535d3ce1654643"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Ra8297dd2e82a499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rc2284ae499e84e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R8d8e43739a72441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R6692aebebe1c4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R3c317fd5a9c94d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rf539c4206c894a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R2c4e2482cb604660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R5aaf31d168f04e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R696961c3ddce4c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R48e00537e9bb4166"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="34" t="str">
-        <x:v>2026-09-06 (ver3.1 — 결정 C-1~C-16 반영)</x:v>
+        <x:v>2026-09-07 (ver3.1 — 결정 C-1~C-17 반영)</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="31" customFormat="1" ht="15" customHeight="1">
@@ -7014,10 +7014,8 @@
           <x:t xml:space="preserve">사용자</x:t>
         </x:is>
       </x:c>
-      <x:c r="G72" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">앱은 자동으로 바꾸지 않고 제안만 한다. 해당 항목이 내야 할 몫(B-4-08), 고른 실천 예상 vs 실제 대비(예상 18% 줄이기 / 7월 실제 2% 늘어남)와 "실천을 놓쳤을 수도, 더위 탓일 수도 있어요. 앱은 어느 쪽인지 알 수 없어요", 부족분을 메울 수 있고 겹치지 않는 미션에 추천 배지, 추천 반영 시 합계 미리보기(약 18% → 28% 줄이기)를 표시한다. 목표 구간 하향은 2회 연속 미달일 때만 제안한다(목표를 낮추는 건 아직 권하지 않아요). 이대로 저장하기로 B-2-08 미션 선택을 갱신한다.</x:t>
-        </x:is>
+      <x:c r="G72" s="53" t="str">
+        <x:v>앱은 자동으로 바꾸지 않고 제안만 함. 해당 항목이 내야 할 몫(B-4-08), 고른 실천 예상 vs 실제 대비와 불확실성 안내를 표시. 이미 고른 deviceGroup에 더 강한 미션이 있으면 교체 추천을 우선하고, 추천 반영 합계에는 기존 미션과의 증가분만 반영. 그래도 부족하면 겹치지 않는 다른 deviceGroup 미션을 추가 추천. 목표 구간 하향은 2회 연속 미달일 때만 제안. 사용자가 저장해야 B-2-08 선택 갱신</x:v>
       </x:c>
       <x:c r="H72" s="55" t="inlineStr">
         <x:is>
@@ -10319,6 +10317,20 @@
         <x:v>D-1-04, D-1-05, D-2-02</x:v>
       </x:c>
     </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>C-17</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>실천 다시 고르기 추천</x:v>
+      </x:c>
+      <x:c r="C33" s="68" t="str">
+        <x:v>같은 deviceGroup의 더 강한 미션이 있으면 교체 추천을 우선하고 합계에는 증가분만 반영한다. 부족분이 남으면 다른 deviceGroup을 추가 추천한다. 앱은 자동 변경하지 않으며, 목표 구간 하향은 2회 연속 미달일 때만 제안한다.</x:v>
+      </x:c>
+      <x:c r="D33" s="68" t="str">
+        <x:v>B-3-04, B-4-09</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R6692aebebe1c4f2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R3c317fd5a9c94d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rf539c4206c894a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R2c4e2482cb604660"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R5aaf31d168f04e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R696961c3ddce4c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R48e00537e9bb4166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R5994e249ffdf483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R41593bac528644d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R87a52f29ea904699"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R6a83319f1d654373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R5668f05a8080446c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R92582fdfbf254698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R2f2ecb7f22454a1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="34" t="str">
-        <x:v>2026-09-07 (ver3.1 — 결정 C-1~C-17 반영)</x:v>
+        <x:v>2026-09-07 (ver3.1 — 결정 C-1~C-18 반영)</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="31" customFormat="1" ht="15" customHeight="1">
@@ -6014,10 +6014,8 @@
           <x:t xml:space="preserve">시스템</x:t>
         </x:is>
       </x:c>
-      <x:c r="G59" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">요금별 6~9개 미션을 사전 정의한다. 필드: 제목, 한 줄 설명, 난이도(쉬움·보통·어려움), 출처 수치(예: 월 40kWh · 4,880원), 산출 근거(예: 15평형 2kW를 20일 기준 · 40kWh ÷ 우리 집 223kWh), 출처 기관(전기·도시가스 = 한국에너지공단 / 수도 = 환경부·서울시 아리수), 기기 그룹(냉방·세탁·샤워 등), 계절 태그, 상한 적용 여부. 출처·산출 근거·기관 중 하나라도 없는 미션은 노출하지 않는다.</x:t>
-        </x:is>
+      <x:c r="G59" s="53" t="str">
+        <x:v>요금별 마스터 카탈로그를 9~12개 사전 정의하고, 화면에는 현재 계절·목표 구간·추천 맥락에 맞는 6~9개만 골라 보여준다. 미션은 자립 준비 청년이 임대 주거에서 직접 실행할 수 있는 습관 행동으로 한정하며 공사·설비 교체·전문업체 작업을 제외한다. 난이도는 비용이나 주거 권한이 아니라 한 달 동안 반복해야 하는 습관 변화의 강도(쉬움·보통·어려움)로 구분한다. 필드: 제목, 한 줄 설명, 난이도, 출처 수치, 산출 근거, 출처 기관, 기기 그룹, 계절 태그, 상한 적용 여부. 출처·산출 근거·기관 중 하나라도 없는 미션은 노출하지 않는다.</x:v>
       </x:c>
       <x:c r="H59" s="55" t="inlineStr">
         <x:is>
@@ -10331,6 +10329,22 @@
         <x:v>B-3-04, B-4-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>C-18</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>청년 실행 가능 미션</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>요금별 마스터 카탈로그는 9~12개로 확장하고 화면에는 현재 계절·목표·추천 맥락에 맞는 6~9개만 노출한다. 공사·설비 교체·전문업체 작업은 제외하며 난이도는 비용이 아니라 반복 습관의 강도로 구분한다.</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>B-3-01, B-3-05</x:v>
+      </x:c>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R5994e249ffdf483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R41593bac528644d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R87a52f29ea904699"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R6a83319f1d654373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R5668f05a8080446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R92582fdfbf254698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R2f2ecb7f22454a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R11ddba9daaf246e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R44acc647ed274e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R30af3e1be9af4979"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R9677a09b17e44247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rf101c06057d4412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rd4baaf3679af4d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R5f90aafd6a314390"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6936,15 +6936,11 @@
           <x:t xml:space="preserve">시스템</x:t>
         </x:is>
       </x:c>
-      <x:c r="G71" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">필요 월 감축률 = (목표 % × 6 − Σ 등록 월 감축률) ÷ 남은 개월로 계산한다(예: (10×6 − 9×4) ÷ 2 = 12%). 항목 단위로는 다른 항목 현 수준 유지를 전제로 미달 항목의 필요 감축률을 역산한다(전기 11% 줄여야 해요). 달성이 사실상 불가능한 수치(예: 필요 감축률이 미션 합계 상한을 크게 넘음)면 "하면 된다"식 확정 표현을 쓰지 않고 가능성 문구로 바꾼다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H71" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">targetRate, monthlyRates[], remainingMonths → requiredRate</x:t>
-        </x:is>
+      <x:c r="G71" s="53" t="str">
+        <x:v>필요 월 감축률 = (목표 % × 6 − Σ 등록 월 감축률) ÷ 남은 개월로 계산한다. 항목 단위로는 다른 항목의 현 수준 유지를 전제로 미달 항목의 필요 감축률을 역산한다. 회복 부담 배수 = 필요 월 감축률 ÷ 현재 목표 구간 하한으로 계산하며 달성이 사실상 불가능한 수치에는 확정 표현을 쓰지 않는다.</x:v>
+      </x:c>
+      <x:c r="H71" s="55" t="str">
+        <x:v>targetRate, monthlyRates[], remainingMonths → requiredRate, recoveryBurden</x:v>
       </x:c>
       <x:c r="I71" s="53" t="inlineStr">
         <x:is>
@@ -6956,10 +6952,8 @@
           <x:t xml:space="preserve">남은 개월 0 → 역산 생략, 달성 불가 → 확정 표현 금지</x:t>
         </x:is>
       </x:c>
-      <x:c r="K71" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">남은 개월 0에서 0 나눗셈이 발생하지 않는다.</x:t>
-        </x:is>
+      <x:c r="K71" s="53" t="str">
+        <x:v>남은 개월 0에서 0 나눗셈이 발생하지 않고 회복 부담 1.5배 경계를 정확히 판정한다.</x:v>
       </x:c>
       <x:c r="L71" s="48" t="inlineStr">
         <x:is>
@@ -7013,12 +7007,10 @@
         </x:is>
       </x:c>
       <x:c r="G72" s="53" t="str">
-        <x:v>앱은 자동으로 바꾸지 않고 제안만 함. 해당 항목이 내야 할 몫(B-4-08), 고른 실천 예상 vs 실제 대비와 불확실성 안내를 표시. 이미 고른 deviceGroup에 더 강한 미션이 있으면 교체 추천을 우선하고, 추천 반영 합계에는 기존 미션과의 증가분만 반영. 그래도 부족하면 겹치지 않는 다른 deviceGroup 미션을 추가 추천. 목표 구간 하향은 2회 연속 미달일 때만 제안. 사용자가 저장해야 B-2-08 선택 갱신</x:v>
-      </x:c>
-      <x:c r="H72" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">requiredRate, selectedExpected, actual, recommendations[]</x:t>
-        </x:is>
+        <x:v>앱은 자동으로 바꾸지 않고 제안만 한다. 같은 deviceGroup의 더 강한 미션으로 교체 추천하고 합계에는 증가분만 반영하며, 부족하면 다른 그룹 미션을 추가한다. 낮출 구간이 존재하고 회복 부담 배수가 1.5 이상이거나 추천 반영 합계가 필요 감축률에 못 미치면 한 단계 낮은 구간을 제안한다. 최저 5~10% 구간은 더 낮추지 않으며 연속 미달 횟수는 안내 문구에만 사용한다.</x:v>
+      </x:c>
+      <x:c r="H72" s="55" t="str">
+        <x:v>requiredRate, selectedExpected, actual, recommendations[], withRecommendedRate, consecutiveMisses</x:v>
       </x:c>
       <x:c r="I72" s="53" t="inlineStr">
         <x:is>
@@ -7030,10 +7022,8 @@
           <x:t xml:space="preserve">데이터 지연 → 안내</x:t>
         </x:is>
       </x:c>
-      <x:c r="K72" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">저장 후 메인 오늘의 실천이 갱신된다.</x:t>
-        </x:is>
+      <x:c r="K72" s="53" t="str">
+        <x:v>회복 부담 1.5배·추천 미션 부족·최저 구간 경계를 판정하고 저장 후 오늘의 실천이 갱신된다.</x:v>
       </x:c>
       <x:c r="L72" s="48" t="inlineStr">
         <x:is>
@@ -10323,7 +10313,7 @@
         <x:v>실천 다시 고르기 추천</x:v>
       </x:c>
       <x:c r="C33" s="68" t="str">
-        <x:v>같은 deviceGroup의 더 강한 미션이 있으면 교체 추천을 우선하고 합계에는 증가분만 반영한다. 부족분이 남으면 다른 deviceGroup을 추가 추천한다. 앱은 자동 변경하지 않으며, 목표 구간 하향은 2회 연속 미달일 때만 제안한다.</x:v>
+        <x:v>같은 deviceGroup의 더 강한 미션이 있으면 교체 추천을 우선하고 합계에는 증가분만 반영한다. 부족분이 남으면 다른 deviceGroup을 추가 추천하며 앱은 자동 변경하지 않는다.</x:v>
       </x:c>
       <x:c r="D33" s="68" t="str">
         <x:v>B-3-04, B-4-09</x:v>
@@ -10344,6 +10334,20 @@
       </x:c>
       <x:c r="E34"/>
       <x:c r="F34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>C-19</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>회복 가능성 기반 목표 하향</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>회복 부담 배수(requiredRate ÷ 현재 목표 구간 하한)가 1.5 이상이거나 추천 미션 합계가 필요 감축률에 못 미치면 한 단계 낮은 목표 구간을 제안한다. 연속 미달 횟수는 설명에만 사용하고 최저 구간은 더 낮추지 않으며 앱은 자동 변경하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>B-4-08, B-4-09</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11542,10 +11546,8 @@
           <x:t xml:space="preserve">앱은 사용자 선택을 말없이 바꾸지 않는다</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">실천 재선택은 제안만 하고, 목표 구간 하향은 2회 연속 미달일 때만 제안한다.</x:t>
-        </x:is>
+      <x:c r="C12" s="53" t="str">
+        <x:v>실천 재선택과 목표 구간 하향은 제안만 한다. 목표 하향은 횟수가 아니라 남은 기간의 회복 부담과 추천 미션 충족 가능성으로 판단하며 사용자가 직접 선택해야 적용한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="31" customFormat="1" ht="15" customHeight="1">
@@ -11791,20 +11793,14 @@
       <x:c r="A27" s="48" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B27" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">필요 월 감축률</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">R_req = (r_target × 6 − Σ R_m) ÷ 남은 개월</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(10×6 − 9×4) ÷ 2 = 12% — 남은 두 달 매달 12%</x:t>
-        </x:is>
+      <x:c r="B27" s="57" t="str">
+        <x:v>필요 월 감축률·회복 부담</x:v>
+      </x:c>
+      <x:c r="C27" s="55" t="str">
+        <x:v>R_req = (r_target × 6 − Σ R_m) ÷ 남은 개월, Q_recovery = R_req ÷ r_target. 낮출 구간이 있고 Q_recovery ≥ 1.5이거나 추천 미션 합계가 R_req 미만이면 한 단계 하향 제안</x:v>
+      </x:c>
+      <x:c r="D27" s="55" t="str">
+        <x:v>목표 10%에서 남은 기간 필요율 15%면 1.5배 — 5~10% 구간 제안</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="31" customFormat="1" ht="15" customHeight="1">

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R2b161a8f92f94eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rd517a4f8241249ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R921f4003e3aa43cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R94e14684159d4122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R0e96ac31b14845df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rb0c1f805d0184d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R44dd7c6fab7540f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="Rd480b06aeffe40b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R4539a345226a46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R702ea49833c14bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rf1a6b1fc8bd5419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Redb34bc95a4d4db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R7a7de3c2ce7d4636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rcddb56650a72426b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -478,12 +478,6 @@
     <x:t xml:space="preserve">시드 데이터 적재</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">지역 가구 평균 스냅샷, 에코마일리지 기준 사용량(2024·2025년 4~9월 평균)과 직전 연도 월별 사용량, 데모 고지서(2026-04~08월, 전기·수도·도시가스), 실천 미션 데이터, 녹색생활실천 항목·실적, 포켓 거래 내역을 화면 예시 숫자와 맞게 적재한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시드 파일(JSON/SQL)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">초기화 후 동일한 데모 결과가 생성된다.</x:t>
   </x:si>
   <x:si>
@@ -880,9 +874,6 @@
     <x:t xml:space="preserve">인식 내용 수정</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">전기 · 수도 · 도시가스 탭(항상 3개 고정, 인식 여부 배지)마다 청구 월·청구 금액·사용량(kWh / ㎥)을 확인·수정한다. 고지서에 없는 항목 탭은 N 내용 없음 · 필요하면 직접 입력할 수 있어요와 직접 입력하기 버튼을 보여준다. 내용 없음 항목은 합계·비교에서 제외하고 직접 입력하면 포함한다. 확인한 탭에는 ✓를 표시하고 상단 저장 또는 확인 완료로 다음 단계로 간다. "수정한 값은 전년 동월·지역 평균 비교에 사용돼요"를 안내한다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">utilityType, hasData, month, amount, usage, unit</x:t>
   </x:si>
   <x:si>
@@ -1060,102 +1051,54 @@
     <x:t xml:space="preserve">A-3-01</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">지역 가구 평균 기준선 데이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">한전 전력데이터 개방 포털 가구평균 전력사용량 API(year, month, metroCd, cityCd → houseCnt, powerUsage, bill)를 사전 호출해 서울 25개 구 × 최근 24개월을 로컬 스냅샷으로 저장한다. 수도·도시가스 지역 평균은 확보된 공개 데이터가 있을 때만 적재하고, 없으면 해당 항목 탭에 비교 데이터 준비 중을 표시한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">region_avg{year, month, sido, sigungu, houseCnt, avgUsage, avgBill, source, extractedAt}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">한전 API 인증키(C-3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">최신 제공 월이 데모 청구 월보다 이르면 데모 월 조정</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">모든 값에 출처·기준 월·추출일이 저장된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수집·가공은 비개발. 수도·가스 평균 공개 여부 확인(C-4)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">A-3-02</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">비교군 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">사용자 지역과 청구 월에 맞는 같은 지역 가구 평균을 최근 6개월분 조회한다. 시군구 자료가 없거나 표본이 부족하면 더 넓은 지역 평균을 사용하고 범위 배지(서울 관악구 → 서울)로 표시한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GET /diagnosis/baseline?sigungu&amp;month</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">프로필 지역</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">상위 지역도 없음 → A-3-03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">동일 조건에 동일 기준선이 반환된다.</x:t>
+    <x:t xml:space="preserve">A-3-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A-3-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">진단 빈 상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">등록된 고지서가 없으면 아직 등록된 고지서가 없어요 · 전기·수도·도시가스가 포함된 관리비 고지서도 한 번에 분석할 수 있어요와 N월 고지서 등록하기(A-2-01)를 표시한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">고지서 0건</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">신규 상태에서 다음 행동이 명확하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AN-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A-3-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">월 생활요금 합계 카드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">선택 월의 생활요금 합계(내용 있는 항목만)와 항목별(전기세·수도세·도시가스) 금액을 보여주고, 작년 동월 값이 있으면 작년보다 +1,900원 배지를 붙인다. 작년 값이 없으면 배지를 숨긴다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">currentTotal, previousYearTotal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">선택 월 고지서</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">작년 데이터 없음 → 배지 숨김</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">합계가 항목 합과 일치한다.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">AN-07</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">A-3-03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기준선 부재 처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">사용할 수 있는 비교군이 없으면 임의 값을 만들지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">비교 데이터 준비 중 안내와 다음 행동이 표시된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A-3-04</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">진단 빈 상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">등록된 고지서가 없으면 아직 등록된 고지서가 없어요 · 전기·수도·도시가스가 포함된 관리비 고지서도 한 번에 분석할 수 있어요와 N월 고지서 등록하기(A-2-01)를 표시한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">고지서 0건</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">신규 상태에서 다음 행동이 명확하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AN-01</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A-3-05</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">월 생활요금 합계 카드</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">선택 월의 생활요금 합계(내용 있는 항목만)와 항목별(전기세·수도세·도시가스) 금액을 보여주고, 작년 동월 값이 있으면 작년보다 +1,900원 배지를 붙인다. 작년 값이 없으면 배지를 숨긴다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">currentTotal, previousYearTotal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">선택 월 고지서</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">작년 데이터 없음 → 배지 숨김</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">합계가 항목 합과 일치한다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">A-3-06</x:t>
   </x:si>
   <x:si>
@@ -1183,45 +1126,9 @@
     <x:t xml:space="preserve">A-3-07</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">지역 평균 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">항목 탭(전기세·수도세·도시가스)별로 이번 달 금액, 지역 평균보다 +4,300원 차액, 최근 6개월 우리 집·지역 평균 2계열 라인 차트와 월별 툴팁(우리 집 43,200원 / 지역 평균 38,900원)을 보여준다. 지역 배지에 비교 범위를 표시한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">series{mine[], regionAvg[]}, regionLabel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기준선 존재</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">표본 부족 → 넓은 지역 평균 + 안내, 수도·가스 평균 없음 → 준비 중</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">평균의 지역·기준 월·출처가 함께 표시된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">라인 차트</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">A-3-08</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">차액 계산</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">사용자 금액 − 같은 지역 가구 평균 금액, 올해 금액 − 작년 동월 금액을 계산한다. 양수는 초과, 음수는 미만으로 처리하며 이전 값이 없으면 비교 불가로 표시한다. 원화 결과를 먼저 보여준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">diffRegion, diffLastYear</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기준 없음 → 비교 불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">양수·0·음수 경계 테스트를 통과한다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">A-3-09</x:t>
   </x:si>
   <x:si>
@@ -3259,9 +3166,6 @@
     <x:t xml:space="preserve">원화 우선</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">감축률과 함께 줄어드는 요금 −44,090원, 지역 평균보다 +4,300원처럼 원화 영향을 먼저 보여준다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">돈의 3단계 분리</x:t>
   </x:si>
   <x:si>
@@ -3289,9 +3193,6 @@
     <x:t xml:space="preserve">기준선 이원화</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">진단은 같은 지역 가구 평균(+작년 동월), What-if는 에코마일리지 규칙대로 직전 2년 같은 기간 평균. 개인 과거 이력은 에코마일리지 연동값에 한해 사용한다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">판정 근거 공개</x:t>
   </x:si>
   <x:si>
@@ -3439,24 +3340,6 @@
     <x:t xml:space="preserve">냉방 26℃와 에어컨 1시간은 같은 에어컨 → 큰 것 하나만</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">녹색생활실천 예정액</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">예정액 = 유효 횟수 × 단가, 항목 상한 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">전자영수증 24건 × 10원 = 240원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">지역 평균 차액</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">사용자 금액 − 같은 지역 가구 평균 금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">43,200 − 38,900 = +4,300원</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">작년 동월 차액</x:t>
   </x:si>
   <x:si>
@@ -3503,30 +3386,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2026-09-03 미지원 확정 — 배출계수 미공개로 탄소 환산 불가. utility_type 3종 유지, 데모 페르소나는 도시가스 사용 (결정 C-11)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">한전 가구평균 전력사용량 API 인증키 발급 + 최신 제공 월 (데모 청구 월 조정)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A-3-01, COM-09</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">유현</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">전력데이터 개방 포털 회원가입</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수도·도시가스 시군구 평균 공개 데이터 존재 여부 (없으면 해당 탭 준비 중)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A-3-01, A-3-07</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">공공데이터포털</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026-09-03 미확보 확정, 추후 확보 예정 — 그때까지 해당 탭 "비교 데이터 준비 중"(available:false) (결정 C-12)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">관리비 통합·개별 전기·개별 수도·개별 도시가스 고지서 OCR 샘플 확보 + 인식률</x:t>
@@ -3745,7 +3604,7 @@
     <x:xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
@@ -3828,6 +3687,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="7">
@@ -4095,7 +3963,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>그린포켓 기능명세서 ver3.3</x:v>
+        <x:v>그린포켓 기능명세서 ver3.4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -4103,7 +3971,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="27" t="str">
-        <x:v>2026-09-08 (결정 C-1~C-21 반영)</x:v>
+        <x:v>2026-09-08 (결정 C-1~C-22 반영)</x:v>
       </x:c>
       <x:c r="C3" s="25"/>
       <x:c r="D3" s="25"/>
@@ -4929,6 +4797,82 @@
       <x:c r="B67" t="s">
         <x:v>86</x:v>
       </x:c>
+    </x:row>
+    <x:row r="68" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A68" s="35" t="str">
+        <x:v>ver3.4 변경 사항</x:v>
+      </x:c>
+      <x:c r="B68" s="35"/>
+      <x:c r="C68" s="35"/>
+      <x:c r="D68" s="35"/>
+      <x:c r="E68" s="35"/>
+      <x:c r="F68" s="35"/>
+      <x:c r="G68" s="35"/>
+    </x:row>
+    <x:row r="69" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A69" s="35" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B69" s="35" t="str">
+        <x:v>변경 내용</x:v>
+      </x:c>
+      <x:c r="C69" s="35"/>
+      <x:c r="D69" s="35"/>
+      <x:c r="E69" s="35"/>
+      <x:c r="F69" s="35"/>
+      <x:c r="G69" s="35"/>
+    </x:row>
+    <x:row r="70" ht="30" hidden="0" customHeight="1">
+      <x:c r="A70" s="35" t="str">
+        <x:v>진단 비교군</x:v>
+      </x:c>
+      <x:c r="B70" s="36" t="str">
+        <x:v>C-22 지역 평균 금액 비교를 1인 가구 평균 사용량 비교로 변경</x:v>
+      </x:c>
+      <x:c r="C70" s="36"/>
+      <x:c r="D70" s="36"/>
+      <x:c r="E70" s="36"/>
+      <x:c r="F70" s="36"/>
+      <x:c r="G70" s="36"/>
+    </x:row>
+    <x:row r="71" ht="42" hidden="0" customHeight="1">
+      <x:c r="A71" s="35" t="str">
+        <x:v>비교 자료</x:v>
+      </x:c>
+      <x:c r="B71" s="36" t="str">
+        <x:v>전기·도시가스는 KESIS 2022년 전국 1인 가구 연간 집계를 월평균 사용량으로 환산하고, 수도는 서울시 2018년 아파트 1인 가구 하루 438L를 조회 월 일수로 환산</x:v>
+      </x:c>
+      <x:c r="C71" s="36"/>
+      <x:c r="D71" s="36"/>
+      <x:c r="E71" s="36"/>
+      <x:c r="F71" s="36"/>
+      <x:c r="G71" s="36"/>
+    </x:row>
+    <x:row r="72" ht="36" hidden="0" customHeight="1">
+      <x:c r="A72" s="35" t="str">
+        <x:v>API 계약</x:v>
+      </x:c>
+      <x:c r="B72" s="36" t="str">
+        <x:v>API 수는 유지하고 GET /diagnosis와 GET /diagnosis/baseline의 지역 평균 응답을 1인 가구 사용량 응답으로 교체</x:v>
+      </x:c>
+      <x:c r="C72" s="36"/>
+      <x:c r="D72" s="36"/>
+      <x:c r="E72" s="36"/>
+      <x:c r="F72" s="36"/>
+      <x:c r="G72" s="36"/>
+    </x:row>
+    <x:row r="73" ht="36" hidden="0" customHeight="1">
+      <x:c r="A73" s="35" t="str">
+        <x:v>한계 공개</x:v>
+      </x:c>
+      <x:c r="B73" s="36" t="str">
+        <x:v>전기·가스는 계절별 월 실측이 아닌 연간 집계 월평균이며 수도는 서울 아파트 표본임을 비교 결과에 함께 제공</x:v>
+      </x:c>
+      <x:c r="C73" s="36"/>
+      <x:c r="D73" s="36"/>
+      <x:c r="E73" s="36"/>
+      <x:c r="F73" s="36"/>
+      <x:c r="G73" s="36"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4965,6 +4909,10 @@
     <x:mergeCell ref="D27:H27"/>
     <x:mergeCell ref="B54:H54"/>
     <x:mergeCell ref="D26:H26"/>
+    <x:mergeCell ref="B70:G70"/>
+    <x:mergeCell ref="B71:G71"/>
+    <x:mergeCell ref="B72:G72"/>
+    <x:mergeCell ref="B73:G73"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5403,11 +5351,11 @@
       <x:c r="F9" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H9" s="13" t="s">
-        <x:v>155</x:v>
+      <x:c r="G9" s="13" t="str">
+        <x:v>1인 가구 평균 사용량 JSON, 에코마일리지 기준 사용량(2024·2025년 4~9월 평균)과 직전 연도 월별 사용량, 데모 고지서(2026-04~08월, 전기·수도·도시가스), 실천 미션 데이터, 녹색생활실천 항목·실적, 포켓 거래 내역을 화면 예시 숫자와 맞게 적재한다.</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="str">
+        <x:v>시드 파일(JSON/SQL)</x:v>
       </x:c>
       <x:c r="I9" s="15" t="s">
         <x:v>113</x:v>
@@ -5416,7 +5364,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>156</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="L9" s="8" t="s">
         <x:v>26</x:v>
@@ -5431,7 +5379,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="P9" s="13" t="s">
-        <x:v>157</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="29.899999618530273" customHeight="1">
@@ -5445,28 +5393,28 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G10" s="13" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H10" s="15" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="I10" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="J10" s="13" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K10" s="13" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="L10" s="8" t="s">
         <x:v>26</x:v>
@@ -5493,16 +5441,16 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G11" s="13" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H11" s="15" t="s">
         <x:v>113</x:v>
@@ -5514,7 +5462,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="L11" s="8" t="s">
         <x:v>28</x:v>
@@ -5526,10 +5474,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="O11" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="P11" s="13" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58.25" customHeight="1">
@@ -5543,19 +5491,19 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E12" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G12" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H12" s="15" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I12" s="15" t="s">
         <x:v>113</x:v>
@@ -5564,7 +5512,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K12" s="13" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="L12" s="8" t="s">
         <x:v>26</x:v>
@@ -5576,7 +5524,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O12" s="15" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="P12" s="15"/>
     </x:row>
@@ -5591,28 +5539,28 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D13" s="10" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G13" s="13" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H13" s="20" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="L13" s="22" t="s">
         <x:v>26</x:v>
@@ -5627,7 +5575,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="P13" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="29.899999618530273" customHeight="1">
@@ -5641,28 +5589,28 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D14" s="10" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E14" s="13" t="s">
-        <x:v>184</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G14" s="13" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H14" s="20" t="s">
+      <x:c r="J14" s="13" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="I14" s="13" t="s">
+      <x:c r="K14" s="13" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="J14" s="13" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="K14" s="13" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="L14" s="22" t="s">
         <x:v>26</x:v>
@@ -5677,7 +5625,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="P14" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="29.899999618530273" customHeight="1">
@@ -5691,28 +5639,28 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D15" s="10" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G15" s="20" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H15" s="20" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="H15" s="20" t="s">
+      <x:c r="J15" s="13" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="I15" s="13" t="s">
+      <x:c r="K15" s="13" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="J15" s="13" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="K15" s="13" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="L15" s="22" t="s">
         <x:v>26</x:v>
@@ -5727,7 +5675,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="P15" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="29.899999618530273" customHeight="1">
@@ -5741,28 +5689,28 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E16" s="13" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G16" s="20" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H16" s="20" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="H16" s="20" t="s">
+      <x:c r="J16" s="13" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
+      <x:c r="K16" s="13" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="L16" s="22" t="s">
         <x:v>26</x:v>
@@ -5774,10 +5722,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O16" s="20" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="P16" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
@@ -5788,31 +5736,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G17" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H17" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H17" s="15" t="s">
+      <x:c r="J17" s="13" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="I17" s="13" t="s">
+      <x:c r="K17" s="13" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="J17" s="13" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="K17" s="13" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="L17" s="8" t="s">
         <x:v>26</x:v>
@@ -5824,7 +5772,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O17" s="15" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="P17" s="15"/>
     </x:row>
@@ -5836,31 +5784,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E18" s="13" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G18" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H18" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H18" s="15" t="s">
+      <x:c r="K18" s="13" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="I18" s="13" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="K18" s="13" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="L18" s="8" t="s">
         <x:v>26</x:v>
@@ -5872,7 +5820,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O18" s="15" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="P18" s="15"/>
     </x:row>
@@ -5884,31 +5832,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E19" s="13" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G19" s="13" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="J19" s="13" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K19" s="13" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="H19" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="I19" s="13" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="J19" s="13" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="K19" s="13" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="L19" s="8" t="s">
         <x:v>26</x:v>
@@ -5920,7 +5868,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O19" s="15" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="P19" s="15"/>
     </x:row>
@@ -5932,31 +5880,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D20" s="10" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E20" s="13" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G20" s="13" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H20" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="I20" s="13" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H20" s="15" t="s">
+      <x:c r="J20" s="13" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="I20" s="13" t="s">
+      <x:c r="K20" s="13" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="J20" s="13" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="K20" s="13" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="L20" s="8" t="s">
         <x:v>26</x:v>
@@ -5968,7 +5916,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O20" s="15" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="P20" s="15"/>
     </x:row>
@@ -5980,31 +5928,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D21" s="10" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H21" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H21" s="15" t="s">
+      <x:c r="J21" s="13" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="I21" s="13" t="s">
+      <x:c r="K21" s="13" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="J21" s="13" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="K21" s="13" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="L21" s="8" t="s">
         <x:v>26</x:v>
@@ -6016,7 +5964,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O21" s="15" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="P21" s="15"/>
     </x:row>
@@ -6028,31 +5976,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G22" s="13" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H22" s="15" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="I22" s="13" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="J22" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K22" s="13" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="L22" s="8" t="s">
         <x:v>28</x:v>
@@ -6064,7 +6012,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O22" s="15" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="P22" s="13"/>
     </x:row>
@@ -6076,31 +6024,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="D23" s="10" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>248</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G23" s="13" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="H23" s="15" t="s">
+      <x:c r="J23" s="13" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="I23" s="15" t="s">
+      <x:c r="K23" s="13" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="J23" s="13" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="K23" s="13" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="L23" s="8" t="s">
         <x:v>26</x:v>
@@ -6112,7 +6060,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O23" s="15" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P23" s="15"/>
     </x:row>
@@ -6124,31 +6072,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="H24" s="15" t="s">
+      <x:c r="J24" s="13" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="I24" s="15" t="s">
+      <x:c r="K24" s="13" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="J24" s="13" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="K24" s="13" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="L24" s="8" t="s">
         <x:v>26</x:v>
@@ -6160,7 +6108,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O24" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="P24" s="15"/>
     </x:row>
@@ -6172,31 +6120,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C25" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E25" s="15" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G25" s="13" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H25" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="I25" s="15" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="H25" s="15" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="I25" s="15" t="s">
+      <x:c r="K25" s="15" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="K25" s="15" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="L25" s="8" t="s">
         <x:v>26</x:v>
@@ -6208,7 +6156,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O25" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="P25" s="15"/>
     </x:row>
@@ -6220,31 +6168,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C26" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E26" s="13" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G26" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H26" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="H26" s="15" t="s">
+      <x:c r="J26" s="13" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="I26" s="13" t="s">
+      <x:c r="K26" s="15" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="J26" s="13" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="K26" s="15" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="L26" s="8" t="s">
         <x:v>26</x:v>
@@ -6256,10 +6204,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O26" s="15" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="P26" s="15" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58.25" customHeight="1">
@@ -6270,31 +6218,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E27" s="13" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G27" s="13" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H27" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="H27" s="15" t="s">
+      <x:c r="J27" s="13" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="I27" s="13" t="s">
+      <x:c r="K27" s="13" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="J27" s="13" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="K27" s="13" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="L27" s="8" t="s">
         <x:v>26</x:v>
@@ -6306,7 +6254,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O27" s="15" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="P27" s="15"/>
     </x:row>
@@ -6318,31 +6266,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E28" s="13" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="13" t="s">
+      <x:c r="G28" s="13" t="str">
+        <x:v>전기 · 수도 · 도시가스 탭(항상 3개 고정, 인식 여부 배지)마다 청구 월·청구 금액·사용량(kWh / ㎥)을 확인·수정한다. 고지서에 없는 항목 탭은 N 내용 없음 · 필요하면 직접 입력할 수 있어요와 직접 입력하기 버튼을 보여준다. 내용 없음 항목은 합계·비교에서 제외하고 직접 입력하면 포함한다. 확인한 탭에는 ✓를 표시하고 상단 저장 또는 확인 완료로 다음 단계로 간다. "수정한 값은 전년 동월·1인 가구 평균 비교에 사용돼요"를 안내한다.</x:v>
+      </x:c>
+      <x:c r="H28" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="I28" s="13" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="J28" s="13" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="H28" s="15" t="s">
+      <x:c r="K28" s="13" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="I28" s="13" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="J28" s="13" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="K28" s="13" t="s">
-        <x:v>292</x:v>
       </x:c>
       <x:c r="L28" s="8" t="s">
         <x:v>26</x:v>
@@ -6354,7 +6302,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O28" s="15" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="P28" s="15"/>
     </x:row>
@@ -6366,31 +6314,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D29" s="10" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E29" s="13" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G29" s="13" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="H29" s="15" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="I29" s="13" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="J29" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K29" s="13" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="L29" s="8" t="s">
         <x:v>26</x:v>
@@ -6402,7 +6350,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O29" s="15" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="P29" s="15"/>
     </x:row>
@@ -6414,31 +6362,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C30" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D30" s="10" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E30" s="13" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F30" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="13" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H30" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="I30" s="13" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="J30" s="13" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="H30" s="15" t="s">
+      <x:c r="K30" s="13" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="I30" s="13" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="J30" s="13" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="K30" s="13" t="s">
-        <x:v>307</x:v>
       </x:c>
       <x:c r="L30" s="8" t="s">
         <x:v>26</x:v>
@@ -6450,7 +6398,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O30" s="15" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="P30" s="15"/>
     </x:row>
@@ -6462,31 +6410,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C31" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D31" s="10" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F31" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G31" s="13" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H31" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="J31" s="13" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="H31" s="15" t="s">
+      <x:c r="K31" s="13" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="I31" s="13" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="J31" s="13" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="K31" s="13" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="L31" s="8" t="s">
         <x:v>26</x:v>
@@ -6498,7 +6446,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O31" s="15" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="P31" s="13"/>
     </x:row>
@@ -6510,31 +6458,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C32" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D32" s="10" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E32" s="13" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G32" s="13" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H32" s="15" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="I32" s="13" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="J32" s="13" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="H32" s="15" t="s">
+      <x:c r="K32" s="13" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="I32" s="13" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="J32" s="13" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="K32" s="13" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="L32" s="8" t="s">
         <x:v>26</x:v>
@@ -6546,7 +6494,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O32" s="15" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="P32" s="13"/>
     </x:row>
@@ -6558,31 +6506,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C33" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D33" s="10" t="s">
-        <x:v>323</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E33" s="13" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F33" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G33" s="13" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H33" s="15" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="I33" s="13" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="J33" s="13" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="H33" s="15" t="s">
+      <x:c r="K33" s="13" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="I33" s="13" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="J33" s="13" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="K33" s="13" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="L33" s="8" t="s">
         <x:v>26</x:v>
@@ -6594,7 +6542,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O33" s="15" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="P33" s="15"/>
     </x:row>
@@ -6606,31 +6554,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D34" s="10" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E34" s="13" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F34" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G34" s="13" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="H34" s="15" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="I34" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="K34" s="13" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="H34" s="15" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="I34" s="15" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="K34" s="13" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="L34" s="8" t="s">
         <x:v>28</x:v>
@@ -6642,7 +6590,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O34" s="15" t="s">
-        <x:v>336</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="P34" s="15"/>
     </x:row>
@@ -6654,31 +6602,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D35" s="10" t="s">
-        <x:v>337</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E35" s="13" t="s">
-        <x:v>338</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F35" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G35" s="13" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="H35" s="15" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="I35" s="13" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="H35" s="15" t="s">
+      <x:c r="K35" s="13" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="I35" s="13" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="K35" s="13" t="s">
-        <x:v>343</x:v>
       </x:c>
       <x:c r="L35" s="8" t="s">
         <x:v>28</x:v>
@@ -6690,10 +6638,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O35" s="15" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="P35" s="15" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="44" customHeight="1">
@@ -6704,46 +6652,46 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D36" s="10" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="E36" s="13" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G36" s="13" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="H36" s="15" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="I36" s="13" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="J36" s="13" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="K36" s="13" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="L36" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N36" s="8" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O36" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="P36" s="15" t="s">
-        <x:v>354</x:v>
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>1인 가구 평균 사용량 기준선 데이터</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="str">
+        <x:v>전기·도시가스는 KESIS 2022년 전국 1인 가구 연간 에너지소비량·에너지원 비중을 사용량 월평균으로 환산하고, 수도는 서울시 2018년 아파트 1인 가구의 하루 438L를 조회 월 일수에 맞춰 환산한다. 런타임에는 검증된 JSON 스냅샷을 읽는다.</x:v>
+      </x:c>
+      <x:c r="H36" s="15" t="str">
+        <x:v>single_household_baseline{utilityType, averageUsage, usageUnit, sourceName, referencePeriod, calculationBasis, note}</x:v>
+      </x:c>
+      <x:c r="I36" s="13" t="str">
+        <x:v>공식 공개 집계와 환산 기준</x:v>
+      </x:c>
+      <x:c r="J36" s="13" t="str">
+        <x:v>월별 실측 또는 전체 주거유형 자료가 없으면 한계를 함께 제공</x:v>
+      </x:c>
+      <x:c r="K36" s="13" t="str">
+        <x:v>전기·수도·도시가스 기준값과 출처·기준 기간·환산 방식이 함께 제공된다.</x:v>
+      </x:c>
+      <x:c r="L36" s="8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="str">
+        <x:v>비개발</x:v>
+      </x:c>
+      <x:c r="N36" s="8" t="str">
+        <x:v>데이터</x:v>
+      </x:c>
+      <x:c r="O36" s="15" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="P36" s="15" t="str">
+        <x:v>전기·도시가스는 계절별 월 실측이 아닌 연간 집계의 월평균 환산값이며, 수도는 서울 아파트 표본이다(C-22).</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58.25" customHeight="1">
@@ -6754,43 +6702,43 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D37" s="10" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="E37" s="13" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="H37" s="15" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="I37" s="13" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="J37" s="13" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="K37" s="13" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="L37" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N37" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="O37" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>비교군 조회</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="str">
+        <x:v>청구 월과 에너지원에 맞는 1인 가구 평균 사용량을 조회한다. 수도는 조회 월의 실제 일수로 환산하고, 전기·도시가스는 연간 집계의 월평균 환산값을 사용한다.</x:v>
+      </x:c>
+      <x:c r="H37" s="15" t="str">
+        <x:v>GET /diagnosis/baseline?month&amp;utility</x:v>
+      </x:c>
+      <x:c r="I37" s="13" t="str">
+        <x:v>1인 가구 기준 JSON</x:v>
+      </x:c>
+      <x:c r="J37" s="13" t="str">
+        <x:v>기준 없음 → A-3-03</x:v>
+      </x:c>
+      <x:c r="K37" s="13" t="str">
+        <x:v>동일 월·에너지원에 동일 기준선이 반환되고 수도는 월 일수에 따라 달라진다.</x:v>
+      </x:c>
+      <x:c r="L37" s="8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="str">
+        <x:v>개발</x:v>
+      </x:c>
+      <x:c r="N37" s="8" t="str">
+        <x:v>BE</x:v>
+      </x:c>
+      <x:c r="O37" s="15" t="str">
+        <x:v>AN-07</x:v>
       </x:c>
       <x:c r="P37" s="13"/>
     </x:row>
@@ -6802,43 +6750,43 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="12" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="D38" s="10" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="E38" s="13" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G38" s="13" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="H38" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="I38" s="13" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="J38" s="13" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="K38" s="13" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="L38" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N38" s="8" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="O38" s="15" t="s">
-        <x:v>362</x:v>
+      <x:c r="E38" s="13" t="str">
+        <x:v>기준선 부재 처리</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="str">
+        <x:v>사용할 수 있는 1인 가구 평균 사용량 기준이 없으면 임의 값을 만들지 않는다.</x:v>
+      </x:c>
+      <x:c r="H38" s="15" t="str">
+        <x:v>available, unavailableReason</x:v>
+      </x:c>
+      <x:c r="I38" s="13" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J38" s="13" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K38" s="13" t="str">
+        <x:v>비교 데이터 준비 중 안내와 다음 행동이 표시된다.</x:v>
+      </x:c>
+      <x:c r="L38" s="8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="str">
+        <x:v>개발</x:v>
+      </x:c>
+      <x:c r="N38" s="8" t="str">
+        <x:v>FE·BE</x:v>
+      </x:c>
+      <x:c r="O38" s="15" t="str">
+        <x:v>AN-07</x:v>
       </x:c>
       <x:c r="P38" s="13"/>
     </x:row>
@@ -6850,31 +6798,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C39" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D39" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="E39" s="13" t="s">
-        <x:v>368</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F39" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G39" s="13" t="s">
-        <x:v>369</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="H39" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="I39" s="15" t="s">
-        <x:v>370</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="J39" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K39" s="13" t="s">
-        <x:v>371</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="L39" s="8" t="s">
         <x:v>26</x:v>
@@ -6886,7 +6834,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O39" s="15" t="s">
-        <x:v>372</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="P39" s="15"/>
     </x:row>
@@ -6898,31 +6846,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C40" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D40" s="10" t="s">
-        <x:v>373</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E40" s="13" t="s">
-        <x:v>374</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F40" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G40" s="13" t="s">
-        <x:v>375</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="H40" s="15" t="s">
-        <x:v>376</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="I40" s="13" t="s">
-        <x:v>377</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="J40" s="13" t="s">
-        <x:v>378</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="K40" s="13" t="s">
-        <x:v>379</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="L40" s="8" t="s">
         <x:v>26</x:v>
@@ -6934,7 +6882,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O40" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="P40" s="15"/>
     </x:row>
@@ -6946,31 +6894,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C41" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D41" s="10" t="s">
-        <x:v>380</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E41" s="15" t="s">
-        <x:v>381</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F41" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G41" s="13" t="s">
-        <x:v>382</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="H41" s="15" t="s">
-        <x:v>383</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="I41" s="13" t="s">
-        <x:v>384</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="J41" s="15" t="s">
-        <x:v>385</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="K41" s="13" t="s">
-        <x:v>386</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="L41" s="8" t="s">
         <x:v>28</x:v>
@@ -6982,10 +6930,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O41" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="P41" s="15" t="s">
-        <x:v>387</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="44" customHeight="1">
@@ -6996,46 +6944,46 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C42" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D42" s="10" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="E42" s="13" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G42" s="13" t="s">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="H42" s="15" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="I42" s="13" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="s">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="K42" s="13" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="L42" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N42" s="8" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="O42" s="15" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="P42" s="15" t="s">
-        <x:v>395</x:v>
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>1인 가구 평균 사용량 비교</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="str">
+        <x:v>항목 탭(전기·수도·도시가스)별로 이번 달 내 사용량, 1인 가구 평균 사용량, 사용량 차이와 차이율을 보여준다. 비교군·기준 연도·출처와 월평균/일수 환산 방식, 자료의 한계를 함께 표시한다.</x:v>
+      </x:c>
+      <x:c r="H42" s="15" t="str">
+        <x:v>singleHouseholdComparison.tabs[]{myUsage, averageUsage, differenceUsage, differenceRate, usageUnit, comparisonLabel, sourceName, referencePeriod, calculationBasis, note}</x:v>
+      </x:c>
+      <x:c r="I42" s="13" t="str">
+        <x:v>기준선 존재</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="str">
+        <x:v>기준 없음 → 비교 데이터 준비 중</x:v>
+      </x:c>
+      <x:c r="K42" s="13" t="str">
+        <x:v>세 항목의 사용량 차이·차이율과 비교 근거가 함께 표시된다.</x:v>
+      </x:c>
+      <x:c r="L42" s="8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="str">
+        <x:v>개발</x:v>
+      </x:c>
+      <x:c r="N42" s="8" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="O42" s="15" t="str">
+        <x:v>AN-07</x:v>
+      </x:c>
+      <x:c r="P42" s="15" t="str">
+        <x:v>지역 평균 6개월 라인 차트를 1인 가구 사용량 비교 카드로 교체(C-22)</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="35" customHeight="1">
@@ -7046,43 +6994,43 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C43" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D43" s="10" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="E43" s="13" t="s">
-        <x:v>397</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G43" s="13" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="H43" s="15" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="I43" s="13" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="J43" s="13" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="K43" s="13" t="s">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="L43" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N43" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="O43" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="str">
+        <x:v>사용량·차액 계산</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str">
+        <x:v>시스템</x:v>
+      </x:c>
+      <x:c r="G43" s="13" t="str">
+        <x:v>사용자 사용량 − 1인 가구 평균 사용량과 (사용자 사용량 − 평균) ÷ 평균 × 100, 올해 금액 − 작년 동월 금액을 계산한다. 양수는 초과, 음수는 미만으로 처리하며 기준이 없으면 비교 불가로 표시한다.</x:v>
+      </x:c>
+      <x:c r="H43" s="15" t="str">
+        <x:v>differenceUsage, differenceRate, diffLastYear</x:v>
+      </x:c>
+      <x:c r="I43" s="13" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J43" s="13" t="str">
+        <x:v>기준 없음 → 비교 불가</x:v>
+      </x:c>
+      <x:c r="K43" s="13" t="str">
+        <x:v>양수·0·음수 경계 테스트를 통과한다.</x:v>
+      </x:c>
+      <x:c r="L43" s="8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="str">
+        <x:v>개발</x:v>
+      </x:c>
+      <x:c r="N43" s="8" t="str">
+        <x:v>BE</x:v>
+      </x:c>
+      <x:c r="O43" s="15" t="str">
+        <x:v>AN-07</x:v>
       </x:c>
       <x:c r="P43" s="13"/>
     </x:row>
@@ -7094,31 +7042,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C44" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D44" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="E44" s="13" t="s">
-        <x:v>403</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F44" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G44" s="13" t="s">
-        <x:v>404</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="H44" s="15" t="s">
-        <x:v>405</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="I44" s="13" t="s">
-        <x:v>406</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="J44" s="15" t="s">
-        <x:v>407</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="K44" s="13" t="s">
-        <x:v>408</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="L44" s="8" t="s">
         <x:v>28</x:v>
@@ -7130,7 +7078,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O44" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="P44" s="15"/>
     </x:row>
@@ -7142,31 +7090,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C45" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D45" s="10" t="s">
-        <x:v>409</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="E45" s="13" t="s">
-        <x:v>410</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F45" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G45" s="13" t="s">
-        <x:v>411</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="H45" s="15" t="s">
-        <x:v>412</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="I45" s="13" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="J45" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K45" s="13" t="s">
-        <x:v>413</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="L45" s="8" t="s">
         <x:v>26</x:v>
@@ -7178,7 +7126,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O45" s="15" t="s">
-        <x:v>414</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="P45" s="15"/>
     </x:row>
@@ -7190,31 +7138,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D46" s="10" t="s">
-        <x:v>416</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="E46" s="13" t="s">
-        <x:v>417</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F46" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G46" s="13" t="s">
-        <x:v>418</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="H46" s="15" t="s">
-        <x:v>419</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="I46" s="13" t="s">
-        <x:v>420</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="J46" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K46" s="13" t="s">
-        <x:v>421</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L46" s="8" t="s">
         <x:v>26</x:v>
@@ -7226,7 +7174,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O46" s="15" t="s">
-        <x:v>422</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="P46" s="15"/>
     </x:row>
@@ -7238,31 +7186,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C47" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D47" s="10" t="s">
-        <x:v>423</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E47" s="13" t="s">
-        <x:v>424</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F47" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G47" s="13" t="s">
-        <x:v>425</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="H47" s="15" t="s">
-        <x:v>426</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="I47" s="13" t="s">
-        <x:v>427</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="J47" s="13" t="s">
-        <x:v>428</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="K47" s="13" t="s">
-        <x:v>429</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="L47" s="8" t="s">
         <x:v>26</x:v>
@@ -7274,10 +7222,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O47" s="15" t="s">
-        <x:v>430</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="P47" s="15" t="s">
-        <x:v>431</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="29.899999618530273" customHeight="1">
@@ -7288,31 +7236,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C48" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D48" s="10" t="s">
-        <x:v>432</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E48" s="13" t="s">
-        <x:v>433</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F48" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G48" s="13" t="s">
-        <x:v>434</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="H48" s="15" t="s">
-        <x:v>435</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="I48" s="13" t="s">
-        <x:v>436</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="J48" s="15" t="s">
-        <x:v>437</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="K48" s="13" t="s">
-        <x:v>438</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="L48" s="8" t="s">
         <x:v>26</x:v>
@@ -7324,7 +7272,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O48" s="15" t="s">
-        <x:v>439</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P48" s="15"/>
     </x:row>
@@ -7336,31 +7284,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C49" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D49" s="10" t="s">
-        <x:v>440</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E49" s="13" t="s">
-        <x:v>441</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="F49" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G49" s="15" t="s">
-        <x:v>442</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="H49" s="15" t="s">
-        <x:v>443</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="I49" s="15" t="s">
-        <x:v>444</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="J49" s="15" t="s">
-        <x:v>445</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="K49" s="13" t="s">
-        <x:v>446</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="L49" s="8" t="s">
         <x:v>26</x:v>
@@ -7372,7 +7320,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O49" s="15" t="s">
-        <x:v>447</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="P49" s="15"/>
     </x:row>
@@ -7384,31 +7332,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D50" s="10" t="s">
-        <x:v>448</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E50" s="13" t="s">
-        <x:v>449</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F50" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G50" s="13" t="s">
-        <x:v>450</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="H50" s="15" t="s">
-        <x:v>451</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="I50" s="13" t="s">
-        <x:v>452</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="J50" s="15" t="s">
-        <x:v>453</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="K50" s="13" t="s">
-        <x:v>454</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="L50" s="8" t="s">
         <x:v>26</x:v>
@@ -7420,7 +7368,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O50" s="15" t="s">
-        <x:v>455</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="P50" s="15"/>
     </x:row>
@@ -7432,31 +7380,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D51" s="10" t="s">
-        <x:v>456</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E51" s="13" t="s">
-        <x:v>457</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F51" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G51" s="13" t="s">
-        <x:v>458</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H51" s="15" t="s">
-        <x:v>459</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="I51" s="13" t="s">
-        <x:v>460</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="J51" s="15" t="s">
-        <x:v>461</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="K51" s="13" t="s">
-        <x:v>462</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="L51" s="8" t="s">
         <x:v>26</x:v>
@@ -7468,7 +7416,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O51" s="15" t="s">
-        <x:v>455</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="P51" s="15"/>
     </x:row>
@@ -7480,31 +7428,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C52" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D52" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E52" s="13" t="s">
-        <x:v>464</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F52" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G52" s="13" t="s">
-        <x:v>465</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="H52" s="15" t="s">
-        <x:v>466</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="I52" s="15" t="s">
-        <x:v>444</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="J52" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K52" s="13" t="s">
-        <x:v>467</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="L52" s="8" t="s">
         <x:v>26</x:v>
@@ -7516,7 +7464,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O52" s="15" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="P52" s="15"/>
     </x:row>
@@ -7528,19 +7476,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C53" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D53" s="10" t="s">
-        <x:v>469</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E53" s="13" t="s">
-        <x:v>470</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F53" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G53" s="13" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H53" s="15" t="s">
         <x:v>113</x:v>
@@ -7552,7 +7500,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K53" s="13" t="s">
-        <x:v>472</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="L53" s="8" t="s">
         <x:v>28</x:v>
@@ -7564,7 +7512,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O53" s="15" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="P53" s="15"/>
     </x:row>
@@ -7576,31 +7524,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C54" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D54" s="10" t="s">
-        <x:v>473</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="E54" s="13" t="s">
-        <x:v>474</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F54" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G54" s="13" t="s">
-        <x:v>475</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="H54" s="15" t="s">
-        <x:v>476</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="I54" s="13" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="J54" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K54" s="15" t="s">
-        <x:v>477</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="L54" s="8" t="s">
         <x:v>28</x:v>
@@ -7612,7 +7560,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O54" s="15" t="s">
-        <x:v>422</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="P54" s="15"/>
     </x:row>
@@ -7624,31 +7572,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C55" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D55" s="10" t="s">
-        <x:v>479</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E55" s="13" t="s">
-        <x:v>480</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F55" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G55" s="13" t="s">
-        <x:v>481</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="H55" s="15" t="s">
-        <x:v>482</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="I55" s="13" t="s">
-        <x:v>444</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="J55" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K55" s="13" t="s">
-        <x:v>483</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="L55" s="8" t="s">
         <x:v>26</x:v>
@@ -7660,7 +7608,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O55" s="15" t="s">
-        <x:v>455</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="P55" s="15"/>
     </x:row>
@@ -7672,22 +7620,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C56" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D56" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E56" s="13" t="s">
-        <x:v>485</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F56" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G56" s="13" t="s">
-        <x:v>486</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="H56" s="15" t="s">
-        <x:v>487</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="I56" s="13" t="s">
         <x:v>113</x:v>
@@ -7696,7 +7644,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K56" s="13" t="s">
-        <x:v>488</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="L56" s="8" t="s">
         <x:v>26</x:v>
@@ -7708,7 +7656,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O56" s="15" t="s">
-        <x:v>489</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="P56" s="15"/>
     </x:row>
@@ -7720,31 +7668,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C57" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D57" s="10" t="s">
-        <x:v>490</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E57" s="13" t="s">
-        <x:v>491</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F57" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G57" s="13" t="s">
-        <x:v>492</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="H57" s="15" t="s">
-        <x:v>493</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="I57" s="13" t="s">
-        <x:v>494</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="J57" s="13" t="s">
-        <x:v>495</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="K57" s="13" t="s">
-        <x:v>496</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="L57" s="8" t="s">
         <x:v>26</x:v>
@@ -7756,7 +7704,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O57" s="15" t="s">
-        <x:v>497</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="P57" s="15"/>
     </x:row>
@@ -7768,31 +7716,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C58" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D58" s="10" t="s">
-        <x:v>498</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E58" s="13" t="s">
-        <x:v>499</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F58" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G58" s="13" t="s">
-        <x:v>500</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="H58" s="15" t="s">
-        <x:v>501</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="I58" s="13" t="s">
-        <x:v>502</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="J58" s="13" t="s">
-        <x:v>503</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="K58" s="13" t="s">
-        <x:v>504</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="L58" s="8" t="s">
         <x:v>26</x:v>
@@ -7804,7 +7752,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O58" s="15" t="s">
-        <x:v>497</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="P58" s="15"/>
     </x:row>
@@ -7816,31 +7764,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C59" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D59" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E59" s="13" t="s">
-        <x:v>506</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F59" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G59" s="13" t="s">
-        <x:v>507</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="H59" s="15" t="s">
-        <x:v>508</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="I59" s="15" t="s">
-        <x:v>509</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="J59" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K59" s="13" t="s">
-        <x:v>510</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="L59" s="8" t="s">
         <x:v>26</x:v>
@@ -7852,7 +7800,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O59" s="15" t="s">
-        <x:v>497</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="P59" s="13"/>
     </x:row>
@@ -7864,31 +7812,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C60" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D60" s="10" t="s">
-        <x:v>511</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E60" s="13" t="s">
-        <x:v>512</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F60" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G60" s="13" t="s">
-        <x:v>513</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="H60" s="15" t="s">
-        <x:v>514</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="I60" s="13" t="s">
-        <x:v>515</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="J60" s="13" t="s">
-        <x:v>516</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="K60" s="13" t="s">
-        <x:v>517</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="L60" s="8" t="s">
         <x:v>28</x:v>
@@ -7900,7 +7848,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O60" s="15" t="s">
-        <x:v>518</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="P60" s="15"/>
     </x:row>
@@ -7912,31 +7860,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C61" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D61" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E61" s="13" t="s">
-        <x:v>520</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F61" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G61" s="13" t="s">
-        <x:v>521</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="H61" s="15" t="s">
-        <x:v>522</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="I61" s="13" t="s">
-        <x:v>523</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J61" s="15" t="s">
-        <x:v>524</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="K61" s="13" t="s">
-        <x:v>525</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="L61" s="8" t="s">
         <x:v>26</x:v>
@@ -7948,10 +7896,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O61" s="15" t="s">
-        <x:v>489</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="P61" s="15" t="s">
-        <x:v>526</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="58.25" customHeight="1">
@@ -7962,31 +7910,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C62" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D62" s="10" t="s">
-        <x:v>527</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E62" s="13" t="s">
-        <x:v>528</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F62" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G62" s="13" t="s">
-        <x:v>529</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="H62" s="15" t="s">
-        <x:v>530</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="I62" s="13" t="s">
-        <x:v>531</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="J62" s="13" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K62" s="13" t="s">
-        <x:v>532</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="L62" s="8" t="s">
         <x:v>26</x:v>
@@ -7998,7 +7946,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O62" s="15" t="s">
-        <x:v>533</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="P62" s="15"/>
     </x:row>
@@ -8010,13 +7958,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C63" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D63" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E63" s="13" t="s">
-        <x:v>536</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F63" s="14" t="s">
         <x:v>111</x:v>
@@ -8025,16 +7973,16 @@
         <x:v>요금별 마스터 카탈로그를 9~12개 사전 정의하고, 화면에는 현재 계절·목표 구간·추천 맥락에 맞는 6~9개만 골라 보여준다. 노출 순서는 이미 선택한 미션을 유지한 뒤 현재 계절 태그, 서로 다른 deviceGroup, 서버 반환 순서(display_order)를 우선하며, 실천 다시 고르기 화면은 recommended=true 미션을 먼저 보여준다. 미션은 자립 준비 청년이 임대 주거에서 직접 실행할 수 있는 습관 행동으로 한정하며 공사·설비 교체·전문업체 작업을 제외한다. 난이도는 비용이나 주거 권한이 아니라 한 달 동안 반복해야 하는 습관 변화의 강도(쉬움·보통·어려움)로 구분한다. 필드: 제목, 한 줄 설명, 난이도, 출처 수치, 산출 근거, 출처 기관, 기기 그룹, 계절 태그, 상한 적용 여부. 출처·산출 근거·기관 중 하나라도 없는 미션은 노출하지 않는다.</x:v>
       </x:c>
       <x:c r="H63" s="15" t="s">
-        <x:v>537</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="I63" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="J63" s="13" t="s">
-        <x:v>538</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="K63" s="13" t="s">
-        <x:v>539</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="L63" s="8" t="s">
         <x:v>26</x:v>
@@ -8046,10 +7994,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="O63" s="15" t="s">
-        <x:v>540</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="P63" s="15" t="s">
-        <x:v>541</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="23.899999618530273" customHeight="1">
@@ -8060,31 +8008,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C64" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D64" s="10" t="s">
-        <x:v>542</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="E64" s="15" t="s">
-        <x:v>543</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="F64" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G64" s="15" t="s">
-        <x:v>544</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="H64" s="15" t="s">
-        <x:v>545</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="I64" s="13" t="s">
-        <x:v>502</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="J64" s="15" t="s">
-        <x:v>546</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K64" s="13" t="s">
-        <x:v>547</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="L64" s="8" t="s">
         <x:v>28</x:v>
@@ -8096,7 +8044,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O64" s="15" t="s">
-        <x:v>489</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="P64" s="15"/>
     </x:row>
@@ -8108,31 +8056,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C65" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D65" s="10" t="s">
-        <x:v>548</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E65" s="13" t="s">
-        <x:v>549</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F65" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G65" s="13" t="s">
-        <x:v>550</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="H65" s="15" t="s">
-        <x:v>551</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="I65" s="13" t="s">
-        <x:v>552</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="J65" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K65" s="13" t="s">
-        <x:v>553</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="L65" s="8" t="s">
         <x:v>26</x:v>
@@ -8144,7 +8092,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O65" s="15" t="s">
-        <x:v>489</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="P65" s="15"/>
     </x:row>
@@ -8156,31 +8104,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C66" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D66" s="10" t="s">
-        <x:v>554</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="E66" s="13" t="s">
-        <x:v>555</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F66" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G66" s="13" t="s">
-        <x:v>556</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="H66" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="I66" s="13" t="s">
-        <x:v>549</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="J66" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="K66" s="13" t="s">
-        <x:v>559</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="L66" s="8" t="s">
         <x:v>26</x:v>
@@ -8192,7 +8140,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O66" s="15" t="s">
-        <x:v>497</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="P66" s="15"/>
     </x:row>
@@ -8204,31 +8152,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C67" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D67" s="10" t="s">
-        <x:v>560</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E67" s="13" t="s">
-        <x:v>561</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F67" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G67" s="13" t="s">
-        <x:v>562</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="H67" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="I67" s="13" t="s">
-        <x:v>564</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="J67" s="13" t="s">
-        <x:v>565</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="K67" s="13" t="s">
-        <x:v>566</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="L67" s="8" t="s">
         <x:v>28</x:v>
@@ -8240,7 +8188,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O67" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P67" s="15"/>
     </x:row>
@@ -8252,31 +8200,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C68" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D68" s="10" t="s">
-        <x:v>569</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E68" s="13" t="s">
-        <x:v>570</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F68" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G68" s="13" t="s">
-        <x:v>571</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="H68" s="15" t="s">
-        <x:v>572</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="I68" s="13" t="s">
-        <x:v>573</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="J68" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K68" s="13" t="s">
-        <x:v>574</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="L68" s="8" t="s">
         <x:v>26</x:v>
@@ -8288,7 +8236,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O68" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P68" s="15"/>
     </x:row>
@@ -8300,31 +8248,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C69" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D69" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E69" s="13" t="s">
-        <x:v>576</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F69" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G69" s="13" t="s">
-        <x:v>577</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="H69" s="15" t="s">
-        <x:v>578</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="I69" s="13" t="s">
-        <x:v>579</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J69" s="15" t="s">
-        <x:v>580</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="K69" s="13" t="s">
-        <x:v>581</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="L69" s="8" t="s">
         <x:v>26</x:v>
@@ -8336,7 +8284,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O69" s="15" t="s">
-        <x:v>582</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="P69" s="15"/>
     </x:row>
@@ -8348,31 +8296,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C70" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D70" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="E70" s="13" t="s">
-        <x:v>584</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F70" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G70" s="13" t="s">
-        <x:v>585</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="H70" s="15" t="s">
-        <x:v>586</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="I70" s="13" t="s">
-        <x:v>587</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="J70" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K70" s="13" t="s">
-        <x:v>588</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="L70" s="8" t="s">
         <x:v>26</x:v>
@@ -8384,7 +8332,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O70" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P70" s="15"/>
     </x:row>
@@ -8396,31 +8344,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C71" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D71" s="10" t="s">
-        <x:v>589</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="E71" s="13" t="s">
-        <x:v>590</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="F71" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G71" s="13" t="s">
-        <x:v>591</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="H71" s="15" t="s">
-        <x:v>592</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="I71" s="13" t="s">
-        <x:v>593</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="J71" s="13" t="s">
-        <x:v>594</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="K71" s="13" t="s">
-        <x:v>595</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="L71" s="8" t="s">
         <x:v>26</x:v>
@@ -8432,7 +8380,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O71" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P71" s="15"/>
     </x:row>
@@ -8444,31 +8392,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C72" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D72" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="E72" s="13" t="s">
-        <x:v>597</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F72" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G72" s="13" t="s">
-        <x:v>598</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="H72" s="15" t="s">
-        <x:v>599</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="I72" s="13" t="s">
-        <x:v>600</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="J72" s="13" t="s">
-        <x:v>601</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="K72" s="13" t="s">
-        <x:v>602</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="L72" s="8" t="s">
         <x:v>28</x:v>
@@ -8480,7 +8428,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O72" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P72" s="15"/>
     </x:row>
@@ -8492,31 +8440,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C73" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D73" s="10" t="s">
-        <x:v>603</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="E73" s="13" t="s">
-        <x:v>604</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F73" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G73" s="13" t="s">
-        <x:v>605</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="H73" s="15" t="s">
-        <x:v>606</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="I73" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="J73" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K73" s="13" t="s">
-        <x:v>607</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="L73" s="8" t="s">
         <x:v>26</x:v>
@@ -8528,10 +8476,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O73" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P73" s="15" t="s">
-        <x:v>526</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="72.25" customHeight="1">
@@ -8542,31 +8490,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C74" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D74" s="10" t="s">
-        <x:v>608</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="E74" s="13" t="s">
-        <x:v>609</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F74" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G74" s="13" t="s">
-        <x:v>610</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="H74" s="15" t="s">
-        <x:v>611</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="I74" s="13" t="s">
-        <x:v>612</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="J74" s="13" t="s">
-        <x:v>613</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="K74" s="13" t="s">
-        <x:v>614</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="L74" s="8" t="s">
         <x:v>26</x:v>
@@ -8578,10 +8526,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O74" s="15" t="s">
-        <x:v>615</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="P74" s="15" t="s">
-        <x:v>526</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="86.5" customHeight="1">
@@ -8592,31 +8540,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C75" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D75" s="10" t="s">
-        <x:v>616</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="E75" s="13" t="s">
-        <x:v>617</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F75" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G75" s="13" t="s">
-        <x:v>618</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="H75" s="15" t="s">
-        <x:v>619</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="I75" s="13" t="s">
-        <x:v>620</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J75" s="13" t="s">
-        <x:v>621</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="K75" s="13" t="s">
-        <x:v>622</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="L75" s="8" t="s">
         <x:v>28</x:v>
@@ -8628,7 +8576,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O75" s="15" t="s">
-        <x:v>623</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="P75" s="15"/>
     </x:row>
@@ -8640,13 +8588,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C76" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D76" s="10" t="s">
-        <x:v>624</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E76" s="13" t="s">
-        <x:v>625</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F76" s="14" t="s">
         <x:v>101</x:v>
@@ -8655,16 +8603,16 @@
         <x:v>앱은 자동으로 바꾸지 않고 제안만 한다. 같은 deviceGroup의 더 강한 미션으로 교체 추천하고 합계에는 증가분만 반영하며, 부족하면 다른 그룹 미션을 추가한다. 낮출 구간이 존재하고 회복 부담 배수가 1.5 이상이거나 추천 반영 합계가 필요 감축률에 못 미치면 한 단계 낮은 구간을 제안한다. 최저 5~10% 구간은 더 낮추지 않는다. consecutiveMisses는 선택 요금 단독 실적이 아니라 회차 전체 합산 월 감축률의 연속 미달 횟수이며 안내 문구에만 사용한다.</x:v>
       </x:c>
       <x:c r="H76" s="15" t="s">
-        <x:v>626</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="I76" s="13" t="s">
-        <x:v>627</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="J76" s="13" t="s">
-        <x:v>628</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="K76" s="13" t="s">
-        <x:v>629</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="L76" s="8" t="s">
         <x:v>28</x:v>
@@ -8676,7 +8624,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O76" s="15" t="s">
-        <x:v>630</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="P76" s="15"/>
     </x:row>
@@ -8688,19 +8636,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C77" s="12" t="s">
-        <x:v>568</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D77" s="10" t="s">
-        <x:v>631</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="E77" s="13" t="s">
-        <x:v>632</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F77" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G77" s="13" t="s">
-        <x:v>633</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="H77" s="15" t="s">
         <x:v>113</x:v>
@@ -8712,7 +8660,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K77" s="13" t="s">
-        <x:v>634</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="L77" s="8" t="s">
         <x:v>28</x:v>
@@ -8724,7 +8672,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O77" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P77" s="15"/>
     </x:row>
@@ -8736,31 +8684,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C78" s="12" t="s">
-        <x:v>635</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D78" s="10" t="s">
-        <x:v>636</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="E78" s="13" t="s">
-        <x:v>637</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F78" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G78" s="13" t="s">
-        <x:v>638</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="H78" s="15" t="s">
-        <x:v>639</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="I78" s="13" t="s">
-        <x:v>640</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="J78" s="13" t="s">
-        <x:v>641</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="K78" s="13" t="s">
-        <x:v>642</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="L78" s="8" t="s">
         <x:v>28</x:v>
@@ -8772,10 +8720,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O78" s="15" t="s">
-        <x:v>643</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="P78" s="15" t="s">
-        <x:v>526</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="29.899999618530273" customHeight="1">
@@ -8786,31 +8734,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C79" s="12" t="s">
-        <x:v>635</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D79" s="10" t="s">
-        <x:v>644</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="E79" s="13" t="s">
-        <x:v>645</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F79" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G79" s="13" t="s">
-        <x:v>646</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="H79" s="15" t="s">
-        <x:v>647</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="I79" s="13" t="s">
-        <x:v>648</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="J79" s="15" t="s">
-        <x:v>649</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="K79" s="13" t="s">
-        <x:v>650</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="L79" s="8" t="s">
         <x:v>26</x:v>
@@ -8822,10 +8770,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O79" s="15" t="s">
-        <x:v>651</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="P79" s="13" t="s">
-        <x:v>526</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="58.25" customHeight="1">
@@ -8836,31 +8784,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C80" s="12" t="s">
-        <x:v>635</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D80" s="10" t="s">
-        <x:v>652</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="E80" s="13" t="s">
-        <x:v>653</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="F80" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G80" s="15" t="s">
-        <x:v>654</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="H80" s="15" t="s">
-        <x:v>655</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="I80" s="15" t="s">
-        <x:v>656</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="J80" s="15" t="s">
-        <x:v>657</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="K80" s="13" t="s">
-        <x:v>658</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="L80" s="8" t="s">
         <x:v>26</x:v>
@@ -8872,7 +8820,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O80" s="15" t="s">
-        <x:v>659</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="P80" s="13"/>
     </x:row>
@@ -8884,31 +8832,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C81" s="12" t="s">
-        <x:v>635</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D81" s="10" t="s">
-        <x:v>660</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="E81" s="13" t="s">
-        <x:v>661</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F81" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G81" s="15" t="s">
-        <x:v>662</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="H81" s="15" t="s">
-        <x:v>663</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="I81" s="13" t="s">
-        <x:v>648</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="J81" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K81" s="13" t="s">
-        <x:v>664</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="L81" s="8" t="s">
         <x:v>28</x:v>
@@ -8920,7 +8868,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O81" s="15" t="s">
-        <x:v>665</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="P81" s="15"/>
     </x:row>
@@ -8932,31 +8880,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C82" s="12" t="s">
-        <x:v>666</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="D82" s="10" t="s">
-        <x:v>667</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E82" s="13" t="s">
-        <x:v>668</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="F82" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G82" s="13" t="s">
-        <x:v>669</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="H82" s="15" t="s">
-        <x:v>670</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="I82" s="13" t="s">
-        <x:v>671</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="J82" s="13" t="s">
-        <x:v>672</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="K82" s="13" t="s">
-        <x:v>673</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="L82" s="8" t="s">
         <x:v>26</x:v>
@@ -8968,7 +8916,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O82" s="15" t="s">
-        <x:v>674</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="P82" s="15"/>
     </x:row>
@@ -8980,31 +8928,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C83" s="12" t="s">
-        <x:v>666</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="D83" s="10" t="s">
-        <x:v>675</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="E83" s="13" t="s">
-        <x:v>676</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F83" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G83" s="15" t="s">
-        <x:v>677</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="H83" s="15" t="s">
-        <x:v>678</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="I83" s="13" t="s">
-        <x:v>679</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="J83" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K83" s="13" t="s">
-        <x:v>680</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="L83" s="8" t="s">
         <x:v>26</x:v>
@@ -9016,10 +8964,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O83" s="15" t="s">
-        <x:v>681</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="P83" s="15" t="s">
-        <x:v>431</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="58.25" customHeight="1">
@@ -9030,22 +8978,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C84" s="12" t="s">
-        <x:v>666</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="D84" s="10" t="s">
-        <x:v>682</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E84" s="13" t="s">
-        <x:v>683</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="F84" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G84" s="13" t="s">
-        <x:v>684</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="H84" s="15" t="s">
-        <x:v>685</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="I84" s="13" t="s">
         <x:v>113</x:v>
@@ -9054,7 +9002,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K84" s="13" t="s">
-        <x:v>686</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="L84" s="8" t="s">
         <x:v>26</x:v>
@@ -9066,10 +9014,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="O84" s="15" t="s">
-        <x:v>687</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="P84" s="15" t="s">
-        <x:v>688</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="29.899999618530273" customHeight="1">
@@ -9080,31 +9028,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C85" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D85" s="10" t="s">
-        <x:v>690</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="E85" s="13" t="s">
-        <x:v>691</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="F85" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G85" s="13" t="s">
-        <x:v>692</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="H85" s="15" t="s">
-        <x:v>693</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="I85" s="15" t="s">
-        <x:v>694</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="J85" s="13" t="s">
-        <x:v>695</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="K85" s="13" t="s">
-        <x:v>696</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="L85" s="8" t="s">
         <x:v>26</x:v>
@@ -9116,7 +9064,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O85" s="15" t="s">
-        <x:v>681</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="P85" s="15"/>
     </x:row>
@@ -9128,31 +9076,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C86" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D86" s="10" t="s">
-        <x:v>697</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E86" s="13" t="s">
-        <x:v>698</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="F86" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G86" s="13" t="s">
-        <x:v>699</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="H86" s="15" t="s">
-        <x:v>700</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="I86" s="13" t="s">
-        <x:v>694</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="J86" s="13" t="s">
-        <x:v>701</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="K86" s="13" t="s">
-        <x:v>702</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="L86" s="8" t="s">
         <x:v>28</x:v>
@@ -9164,7 +9112,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O86" s="15" t="s">
-        <x:v>681</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="P86" s="15"/>
     </x:row>
@@ -9176,31 +9124,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C87" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D87" s="10" t="s">
-        <x:v>703</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E87" s="13" t="s">
-        <x:v>704</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="F87" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G87" s="13" t="s">
-        <x:v>705</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="H87" s="15" t="s">
-        <x:v>706</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="I87" s="13" t="s">
-        <x:v>707</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="J87" s="13" t="s">
-        <x:v>708</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="K87" s="13" t="s">
-        <x:v>709</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="L87" s="8" t="s">
         <x:v>26</x:v>
@@ -9212,7 +9160,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O87" s="15" t="s">
-        <x:v>681</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="P87" s="15"/>
     </x:row>
@@ -9224,31 +9172,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C88" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D88" s="10" t="s">
-        <x:v>710</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="E88" s="13" t="s">
-        <x:v>711</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="F88" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G88" s="13" t="s">
-        <x:v>712</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="H88" s="15" t="s">
-        <x:v>713</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="I88" s="13" t="s">
-        <x:v>714</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="J88" s="13" t="s">
-        <x:v>715</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="K88" s="13" t="s">
-        <x:v>716</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="L88" s="8" t="s">
         <x:v>28</x:v>
@@ -9260,7 +9208,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O88" s="15" t="s">
-        <x:v>717</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="P88" s="15"/>
     </x:row>
@@ -9272,31 +9220,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C89" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D89" s="10" t="s">
-        <x:v>718</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="E89" s="13" t="s">
-        <x:v>719</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="F89" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G89" s="13" t="s">
-        <x:v>720</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="H89" s="15" t="s">
-        <x:v>721</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="I89" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="J89" s="13" t="s">
-        <x:v>722</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="K89" s="13" t="s">
-        <x:v>723</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="L89" s="8" t="s">
         <x:v>26</x:v>
@@ -9308,7 +9256,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O89" s="15" t="s">
-        <x:v>687</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="P89" s="15"/>
     </x:row>
@@ -9320,31 +9268,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C90" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D90" s="10" t="s">
-        <x:v>724</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="E90" s="13" t="s">
-        <x:v>725</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="F90" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G90" s="13" t="s">
-        <x:v>726</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="H90" s="15" t="s">
-        <x:v>727</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="I90" s="13" t="s">
-        <x:v>728</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="J90" s="15" t="s">
-        <x:v>729</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="K90" s="13" t="s">
-        <x:v>730</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="L90" s="8" t="s">
         <x:v>26</x:v>
@@ -9356,7 +9304,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O90" s="15" t="s">
-        <x:v>731</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="P90" s="15"/>
     </x:row>
@@ -9368,31 +9316,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C91" s="12" t="s">
-        <x:v>732</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D91" s="10" t="s">
-        <x:v>733</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="E91" s="13" t="s">
-        <x:v>734</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="F91" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G91" s="13" t="s">
-        <x:v>735</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="H91" s="15" t="s">
-        <x:v>736</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="I91" s="13" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="J91" s="13" t="s">
-        <x:v>737</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="K91" s="13" t="s">
-        <x:v>738</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="L91" s="8" t="s">
         <x:v>26</x:v>
@@ -9404,10 +9352,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O91" s="15" t="s">
-        <x:v>739</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="P91" s="15" t="s">
-        <x:v>740</x:v>
+        <x:v>709</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="58.25" customHeight="1">
@@ -9418,31 +9366,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C92" s="12" t="s">
-        <x:v>732</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D92" s="10" t="s">
-        <x:v>741</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E92" s="13" t="s">
-        <x:v>742</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="F92" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G92" s="13" t="s">
-        <x:v>743</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="H92" s="15" t="s">
-        <x:v>744</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="I92" s="13" t="s">
-        <x:v>745</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="J92" s="15" t="s">
-        <x:v>746</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="K92" s="13" t="s">
-        <x:v>747</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="L92" s="8" t="s">
         <x:v>26</x:v>
@@ -9454,7 +9402,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O92" s="15" t="s">
-        <x:v>748</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="P92" s="15"/>
     </x:row>
@@ -9466,31 +9414,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C93" s="12" t="s">
-        <x:v>732</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D93" s="10" t="s">
-        <x:v>749</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E93" s="13" t="s">
-        <x:v>750</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="F93" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G93" s="13" t="s">
-        <x:v>751</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="H93" s="15" t="s">
-        <x:v>752</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="I93" s="13" t="s">
-        <x:v>753</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="J93" s="15" t="s">
-        <x:v>754</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="K93" s="13" t="s">
-        <x:v>755</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="L93" s="8" t="s">
         <x:v>26</x:v>
@@ -9502,7 +9450,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O93" s="15" t="s">
-        <x:v>756</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="P93" s="15"/>
     </x:row>
@@ -9514,31 +9462,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C94" s="12" t="s">
-        <x:v>732</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D94" s="10" t="s">
-        <x:v>757</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="E94" s="13" t="s">
-        <x:v>758</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="F94" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G94" s="13" t="s">
-        <x:v>759</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="H94" s="15" t="s">
-        <x:v>760</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="I94" s="13" t="s">
-        <x:v>745</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="J94" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K94" s="13" t="s">
-        <x:v>761</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="L94" s="8" t="s">
         <x:v>26</x:v>
@@ -9550,7 +9498,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O94" s="15" t="s">
-        <x:v>748</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="P94" s="15"/>
     </x:row>
@@ -9562,31 +9510,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C95" s="12" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="D95" s="10" t="s">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="E95" s="13" t="s">
         <x:v>732</x:v>
-      </x:c>
-      <x:c r="D95" s="10" t="s">
-        <x:v>762</x:v>
-      </x:c>
-      <x:c r="E95" s="13" t="s">
-        <x:v>763</x:v>
       </x:c>
       <x:c r="F95" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G95" s="13" t="s">
-        <x:v>764</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H95" s="15" t="s">
-        <x:v>765</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="I95" s="13" t="s">
-        <x:v>766</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="J95" s="13" t="s">
-        <x:v>767</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="K95" s="13" t="s">
-        <x:v>768</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="L95" s="8" t="s">
         <x:v>26</x:v>
@@ -9598,7 +9546,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O95" s="15" t="s">
-        <x:v>756</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="P95" s="15"/>
     </x:row>
@@ -9610,31 +9558,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C96" s="12" t="s">
-        <x:v>732</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D96" s="10" t="s">
-        <x:v>769</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="E96" s="13" t="s">
-        <x:v>767</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="F96" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G96" s="13" t="s">
-        <x:v>770</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H96" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="I96" s="13" t="s">
-        <x:v>771</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="J96" s="13" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K96" s="13" t="s">
-        <x:v>772</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="L96" s="8" t="s">
         <x:v>26</x:v>
@@ -9646,7 +9594,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O96" s="15" t="s">
-        <x:v>773</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="P96" s="15"/>
     </x:row>
@@ -9658,31 +9606,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C97" s="12" t="s">
-        <x:v>774</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D97" s="10" t="s">
-        <x:v>775</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="E97" s="13" t="s">
-        <x:v>776</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="F97" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G97" s="13" t="s">
-        <x:v>777</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H97" s="15" t="s">
-        <x:v>778</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="I97" s="13" t="s">
-        <x:v>656</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="J97" s="13" t="s">
-        <x:v>779</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="K97" s="13" t="s">
-        <x:v>780</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="L97" s="8" t="s">
         <x:v>26</x:v>
@@ -9694,7 +9642,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O97" s="15" t="s">
-        <x:v>781</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="P97" s="15"/>
     </x:row>
@@ -9706,31 +9654,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C98" s="12" t="s">
-        <x:v>774</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D98" s="10" t="s">
-        <x:v>782</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="E98" s="13" t="s">
-        <x:v>783</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="F98" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G98" s="13" t="s">
-        <x:v>784</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="H98" s="15" t="s">
-        <x:v>785</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="I98" s="13" t="s">
-        <x:v>786</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="J98" s="13" t="s">
-        <x:v>787</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="K98" s="13" t="s">
-        <x:v>788</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="L98" s="8" t="s">
         <x:v>26</x:v>
@@ -9742,7 +9690,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O98" s="15" t="s">
-        <x:v>789</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="P98" s="15"/>
     </x:row>
@@ -9754,31 +9702,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C99" s="12" t="s">
-        <x:v>774</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D99" s="10" t="s">
-        <x:v>790</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="E99" s="13" t="s">
-        <x:v>791</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="F99" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G99" s="13" t="s">
-        <x:v>792</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="H99" s="15" t="s">
-        <x:v>793</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I99" s="13" t="s">
-        <x:v>794</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="J99" s="13" t="s">
-        <x:v>795</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="K99" s="13" t="s">
-        <x:v>796</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="L99" s="8" t="s">
         <x:v>26</x:v>
@@ -9790,7 +9738,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O99" s="15" t="s">
-        <x:v>781</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="P99" s="13"/>
     </x:row>
@@ -9802,31 +9750,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C100" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D100" s="10" t="s">
-        <x:v>798</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E100" s="13" t="s">
-        <x:v>799</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="F100" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G100" s="13" t="s">
-        <x:v>800</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="H100" s="15" t="s">
-        <x:v>801</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="I100" s="13" t="s">
-        <x:v>745</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="J100" s="13" t="s">
-        <x:v>802</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="K100" s="13" t="s">
-        <x:v>803</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="L100" s="8" t="s">
         <x:v>26</x:v>
@@ -9838,10 +9786,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O100" s="15" t="s">
-        <x:v>804</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="P100" s="15" t="s">
-        <x:v>805</x:v>
+        <x:v>774</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="29.899999618530273" customHeight="1">
@@ -9852,31 +9800,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C101" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D101" s="10" t="s">
-        <x:v>806</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="E101" s="13" t="s">
-        <x:v>807</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="F101" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G101" s="13" t="s">
-        <x:v>808</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="H101" s="15" t="s">
-        <x:v>809</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="I101" s="13" t="s">
-        <x:v>810</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="J101" s="13" t="s">
-        <x:v>811</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="K101" s="13" t="s">
-        <x:v>812</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="L101" s="8" t="s">
         <x:v>26</x:v>
@@ -9888,7 +9836,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O101" s="15" t="s">
-        <x:v>813</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="P101" s="13"/>
     </x:row>
@@ -9900,31 +9848,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C102" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D102" s="10" t="s">
-        <x:v>814</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="E102" s="13" t="s">
-        <x:v>815</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="F102" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G102" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="H102" s="15" t="s">
-        <x:v>817</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="I102" s="15" t="s">
-        <x:v>818</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="J102" s="15" t="s">
-        <x:v>819</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="K102" s="13" t="s">
-        <x:v>820</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="L102" s="8" t="s">
         <x:v>26</x:v>
@@ -9936,7 +9884,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O102" s="15" t="s">
-        <x:v>821</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="P102" s="13"/>
     </x:row>
@@ -9948,31 +9896,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C103" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D103" s="10" t="s">
-        <x:v>822</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="E103" s="13" t="s">
-        <x:v>823</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="F103" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G103" s="13" t="s">
-        <x:v>824</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="H103" s="15" t="s">
-        <x:v>825</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="I103" s="13" t="s">
-        <x:v>826</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="J103" s="15" t="s">
-        <x:v>767</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="K103" s="13" t="s">
-        <x:v>827</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="L103" s="8" t="s">
         <x:v>28</x:v>
@@ -9984,10 +9932,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O103" s="15" t="s">
-        <x:v>828</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="P103" s="13" t="s">
-        <x:v>829</x:v>
+        <x:v>798</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" customHeight="1">
@@ -9998,31 +9946,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C104" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D104" s="10" t="s">
-        <x:v>830</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="E104" s="13" t="s">
-        <x:v>831</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F104" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G104" s="13" t="s">
-        <x:v>832</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H104" s="15" t="s">
-        <x:v>833</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="I104" s="15" t="s">
-        <x:v>745</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="J104" s="15" t="s">
-        <x:v>737</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="K104" s="13" t="s">
-        <x:v>834</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="L104" s="8" t="s">
         <x:v>28</x:v>
@@ -10034,10 +9982,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O104" s="15" t="s">
-        <x:v>739</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="P104" s="15" t="s">
-        <x:v>835</x:v>
+        <x:v>804</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="72.25" customHeight="1">
@@ -10048,31 +9996,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C105" s="12" t="s">
-        <x:v>797</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D105" s="10" t="s">
-        <x:v>836</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="E105" s="13" t="s">
-        <x:v>837</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="F105" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G105" s="13" t="s">
-        <x:v>838</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="H105" s="15" t="s">
-        <x:v>839</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="I105" s="13" t="s">
-        <x:v>840</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="J105" s="13" t="s">
-        <x:v>841</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="K105" s="13" t="s">
-        <x:v>842</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="L105" s="8" t="s">
         <x:v>30</x:v>
@@ -10084,10 +10032,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O105" s="15" t="s">
-        <x:v>843</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="P105" s="15" t="s">
-        <x:v>844</x:v>
+        <x:v>813</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="29.899999618530273" customHeight="1">
@@ -10148,31 +10096,31 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>845</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="D107" t="s">
-        <x:v>846</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="E107" t="s">
-        <x:v>847</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="F107" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G107" t="s">
-        <x:v>848</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="H107" t="s">
-        <x:v>849</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="I107" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="J107" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K107" t="s">
-        <x:v>850</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="L107" t="s">
         <x:v>26</x:v>
@@ -10184,10 +10132,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O107" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="P107" t="s">
-        <x:v>851</x:v>
+        <x:v>820</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10198,19 +10146,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>845</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="D108" t="s">
-        <x:v>852</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="E108" t="s">
-        <x:v>853</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="F108" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G108" t="s">
-        <x:v>854</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="H108" t="s">
         <x:v>113</x:v>
@@ -10222,7 +10170,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="K108" t="s">
-        <x:v>855</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="L108" t="s">
         <x:v>28</x:v>
@@ -10234,7 +10182,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="O108" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -10245,31 +10193,31 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>856</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D109" t="s">
-        <x:v>857</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="E109" t="s">
-        <x:v>858</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="F109" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="G109" t="s">
-        <x:v>859</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="H109" t="s">
-        <x:v>860</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="I109" t="s">
-        <x:v>861</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="J109" t="s">
-        <x:v>862</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="K109" t="s">
-        <x:v>863</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="L109" t="s">
         <x:v>28</x:v>
@@ -10281,7 +10229,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="O109" t="s">
-        <x:v>864</x:v>
+        <x:v>833</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -10292,31 +10240,31 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>856</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D110" t="s">
-        <x:v>865</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="E110" t="s">
-        <x:v>866</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="F110" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="G110" t="s">
-        <x:v>867</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="H110" t="s">
-        <x:v>868</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="I110" t="s">
-        <x:v>869</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="J110" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K110" t="s">
-        <x:v>870</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="L110" t="s">
         <x:v>30</x:v>
@@ -10328,10 +10276,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O110" t="s">
-        <x:v>864</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="P110" t="s">
-        <x:v>844</x:v>
+        <x:v>813</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10388,74 +10336,74 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>871</x:v>
+        <x:v>840</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="6" t="s">
-        <x:v>872</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>873</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>874</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>875</x:v>
+        <x:v>844</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="16" t="s">
-        <x:v>876</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>877</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>878</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="D4" s="15" t="s">
-        <x:v>879</x:v>
+        <x:v>848</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="16" t="s">
-        <x:v>880</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
-        <x:v>881</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="C5" s="13" t="s">
-        <x:v>882</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="D5" s="15" t="s">
-        <x:v>883</x:v>
+        <x:v>852</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="16" t="s">
-        <x:v>884</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="B6" s="13" t="s">
-        <x:v>885</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="C6" s="13" t="s">
-        <x:v>886</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="D6" s="15" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="16" t="s">
-        <x:v>887</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
-        <x:v>888</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="C7" s="13" t="s">
-        <x:v>889</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
         <x:v>99</x:v>
@@ -10463,55 +10411,55 @@
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="16" t="s">
-        <x:v>890</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>891</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>892</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="16" t="s">
-        <x:v>893</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>837</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>894</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>895</x:v>
+        <x:v>864</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="16" t="s">
-        <x:v>896</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>897</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>898</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>899</x:v>
+        <x:v>868</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="16" t="s">
-        <x:v>900</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>901</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>902</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>109</x:v>
@@ -10519,13 +10467,13 @@
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="16" t="s">
-        <x:v>903</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>904</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>905</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>119</x:v>
@@ -10533,46 +10481,46 @@
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" s="16" t="s">
-        <x:v>906</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>907</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>908</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>769</x:v>
+        <x:v>738</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18">
       <x:c r="A15" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>878</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="6" t="s">
-        <x:v>872</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>873</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>874</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>875</x:v>
+        <x:v>844</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="16" t="s">
-        <x:v>910</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>911</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>912</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>109</x:v>
@@ -10580,268 +10528,268 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="16" t="s">
-        <x:v>913</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="B18" s="13" t="s">
-        <x:v>914</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>915</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>916</x:v>
+        <x:v>885</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="16" t="s">
-        <x:v>917</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>918</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>919</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>337</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="25">
       <x:c r="A20" s="16" t="s">
-        <x:v>920</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
-        <x:v>921</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>922</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>923</x:v>
+        <x:v>892</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="s">
-        <x:v>924</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>925</x:v>
+        <x:v>894</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>926</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>927</x:v>
+        <x:v>896</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="s">
-        <x:v>928</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>929</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>930</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>931</x:v>
+        <x:v>900</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="s">
-        <x:v>932</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>933</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>934</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>935</x:v>
+        <x:v>904</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="25">
       <x:c r="A24" s="16" t="s">
-        <x:v>936</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>937</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>938</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>939</x:v>
+        <x:v>908</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="s">
-        <x:v>940</x:v>
+        <x:v>909</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C25" s="15" t="s">
-        <x:v>941</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="s">
-        <x:v>942</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>943</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>944</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>945</x:v>
+        <x:v>914</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="25">
       <x:c r="A27" s="16" t="s">
-        <x:v>946</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>947</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>948</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>440</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="s">
-        <x:v>949</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="B28" s="13" t="s">
-        <x:v>950</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>951</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>388</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="s">
-        <x:v>952</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>953</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="C29" s="15" t="s">
-        <x:v>954</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
-        <x:v>955</x:v>
+        <x:v>924</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="19" t="s">
-        <x:v>956</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>957</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>958</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="D30" t="s">
-        <x:v>959</x:v>
+        <x:v>928</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="31.5" customHeight="1">
       <x:c r="A31" t="s">
-        <x:v>960</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>961</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C31" s="21" t="s">
-        <x:v>962</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="D31" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="21" t="s">
-        <x:v>963</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="B32" s="21" t="s">
-        <x:v>964</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="C32" s="21" t="s">
-        <x:v>965</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="D32" s="21" t="s">
-        <x:v>966</x:v>
+        <x:v>935</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
       <x:c r="A33" s="21" t="s">
-        <x:v>967</x:v>
+        <x:v>936</x:v>
       </x:c>
       <x:c r="B33" s="21" t="s">
-        <x:v>968</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="C33" s="21" t="s">
-        <x:v>969</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D33" s="21" t="s">
-        <x:v>970</x:v>
+        <x:v>939</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
       <x:c r="A34" s="21" t="s">
-        <x:v>971</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="B34" s="21" t="s">
-        <x:v>972</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="C34" s="21" t="s">
-        <x:v>973</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="D34" s="21" t="s">
-        <x:v>974</x:v>
+        <x:v>943</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="48" customHeight="1">
       <x:c r="A35" s="21" t="s">
-        <x:v>975</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="B35" s="21" t="s">
-        <x:v>976</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="C35" s="21" t="str">
         <x:v>요금별 9~12개 카탈로그, 화면 6~9개 노출. 선택 미션 유지 → 현재 계절 → 서로 다른 deviceGroup → display_order 순으로 우선하고 다시 고르기에서는 recommended 미션을 먼저 노출. 공사·설비 교체·전문업체 작업 제외. 난이도는 반복 습관 강도</x:v>
       </x:c>
       <x:c r="D35" s="21" t="s">
-        <x:v>977</x:v>
+        <x:v>946</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="48" customHeight="1">
       <x:c r="A36" s="21" t="s">
-        <x:v>978</x:v>
+        <x:v>947</x:v>
       </x:c>
       <x:c r="B36" s="21" t="s">
-        <x:v>979</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="C36" s="21" t="str">
         <x:v>requiredRate ÷ 목표 구간 하한이 1.5 이상이거나 추천 미션으로 필요 감축률을 채우지 못하면 한 단계 하향 제안. consecutiveMisses는 회차 전체 합산 월 감축률 기준의 설명용 값. 자동 변경 금지</x:v>
       </x:c>
       <x:c r="D36" s="21" t="s">
-        <x:v>980</x:v>
+        <x:v>949</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -10856,6 +10804,20 @@
       </x:c>
       <x:c r="D37" t="str">
         <x:v>D-1-04, D-4-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A38" s="36" t="str">
+        <x:v>C-22</x:v>
+      </x:c>
+      <x:c r="B38" s="36" t="str">
+        <x:v>진단 1인 가구 비교</x:v>
+      </x:c>
+      <x:c r="C38" s="36" t="str">
+        <x:v>진단의 두 번째 비교는 지역 평균 금액 대신 1인 가구 평균 사용량으로 제공한다. 전기·가스는 KESIS 전국 1인 가구 연간 집계를 월평균 환산하고 수도는 서울시 아파트 1인 가구 일 사용량을 월 환산한다. 출처·환산 방식·한계를 함께 표시하고 작년 동월 비교는 유지한다.</x:v>
+      </x:c>
+      <x:c r="D38" s="36" t="str">
+        <x:v>A-3-01~03, A-3-07~08</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10875,18 +10837,18 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>981</x:v>
+        <x:v>950</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>982</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>983</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>984</x:v>
+        <x:v>953</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
         <x:v>97</x:v>
@@ -10897,390 +10859,390 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>985</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>986</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="D4" s="15"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="16" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
-        <x:v>987</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="C5" s="13" t="s">
-        <x:v>988</x:v>
+        <x:v>957</x:v>
       </x:c>
       <x:c r="D5" s="13" t="s">
-        <x:v>989</x:v>
+        <x:v>958</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="16" t="s">
-        <x:v>372</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B6" s="13" t="s">
-        <x:v>990</x:v>
+        <x:v>959</x:v>
       </x:c>
       <x:c r="C6" s="13" t="s">
-        <x:v>991</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="D6" s="15"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="16" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
-        <x:v>992</x:v>
+        <x:v>961</x:v>
       </x:c>
       <x:c r="C7" s="13" t="s">
-        <x:v>993</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="D7" s="15"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B8" s="15" t="s">
-        <x:v>994</x:v>
+        <x:v>963</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>995</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="D8" s="15"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="16" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B9" s="15" t="s">
-        <x:v>996</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>997</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="D9" s="15"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="16" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>998</x:v>
+        <x:v>967</x:v>
       </x:c>
       <x:c r="D10" s="13" t="s">
-        <x:v>999</x:v>
+        <x:v>968</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="16" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>1000</x:v>
+        <x:v>969</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>1001</x:v>
+        <x:v>970</x:v>
       </x:c>
       <x:c r="D11" s="15"/>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="16" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>1002</x:v>
+        <x:v>971</x:v>
       </x:c>
       <x:c r="C12" s="13" t="s">
-        <x:v>1003</x:v>
+        <x:v>972</x:v>
       </x:c>
       <x:c r="D12" s="15"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" s="16" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>1004</x:v>
+        <x:v>973</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>1005</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>1006</x:v>
+        <x:v>975</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="A14" s="16" t="s">
-        <x:v>674</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>1007</x:v>
+        <x:v>976</x:v>
       </x:c>
       <x:c r="C14" s="13" t="s">
-        <x:v>1008</x:v>
+        <x:v>977</x:v>
       </x:c>
       <x:c r="D14" s="15"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
       <x:c r="A15" s="16" t="s">
-        <x:v>681</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>1009</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="C15" s="13" t="s">
-        <x:v>1010</x:v>
+        <x:v>979</x:v>
       </x:c>
       <x:c r="D15" s="15"/>
     </x:row>
     <x:row r="16" ht="15" customHeight="1">
       <x:c r="A16" s="16" t="s">
-        <x:v>717</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="B16" s="13" t="s">
-        <x:v>711</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="C16" s="13" t="s">
-        <x:v>1011</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="D16" s="15"/>
     </x:row>
     <x:row r="17" ht="15" customHeight="1">
       <x:c r="A17" s="16" t="s">
-        <x:v>422</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>1012</x:v>
+        <x:v>981</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>1013</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="D17" s="15"/>
     </x:row>
     <x:row r="18" ht="15" customHeight="1">
       <x:c r="A18" s="16" t="s">
-        <x:v>439</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B18" s="13" t="s">
-        <x:v>1014</x:v>
+        <x:v>983</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>1015</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="D18" s="15"/>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" s="16" t="s">
-        <x:v>455</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>1016</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>1017</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="D19" s="15"/>
     </x:row>
     <x:row r="20" ht="15" customHeight="1">
       <x:c r="A20" s="16" t="s">
-        <x:v>497</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
-        <x:v>1018</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>1019</x:v>
+        <x:v>988</x:v>
       </x:c>
       <x:c r="D20" s="15"/>
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
       <x:c r="A21" s="16" t="s">
-        <x:v>518</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>1020</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>1021</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="D21" s="15"/>
     </x:row>
     <x:row r="22" ht="15" customHeight="1">
       <x:c r="A22" s="16" t="s">
-        <x:v>567</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>1022</x:v>
+        <x:v>991</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>1023</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>1024</x:v>
+        <x:v>993</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" customHeight="1">
       <x:c r="A23" s="16" t="s">
-        <x:v>615</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>609</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>1025</x:v>
+        <x:v>994</x:v>
       </x:c>
       <x:c r="D23" s="15"/>
     </x:row>
     <x:row r="24" ht="15" customHeight="1">
       <x:c r="A24" s="16" t="s">
-        <x:v>630</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>625</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>1026</x:v>
+        <x:v>995</x:v>
       </x:c>
       <x:c r="D24" s="15"/>
     </x:row>
     <x:row r="25" ht="15" customHeight="1">
       <x:c r="A25" s="16" t="s">
-        <x:v>643</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>1027</x:v>
+        <x:v>996</x:v>
       </x:c>
       <x:c r="C25" s="15" t="s">
-        <x:v>1028</x:v>
+        <x:v>997</x:v>
       </x:c>
       <x:c r="D25" s="15"/>
     </x:row>
     <x:row r="26" ht="15" customHeight="1">
       <x:c r="A26" s="16" t="s">
-        <x:v>651</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>1029</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>1030</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="D26" s="15"/>
     </x:row>
     <x:row r="27" ht="15" customHeight="1">
       <x:c r="A27" s="16" t="s">
-        <x:v>659</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>1031</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>1032</x:v>
+        <x:v>1001</x:v>
       </x:c>
       <x:c r="D27" s="15"/>
     </x:row>
     <x:row r="28" ht="15" customHeight="1">
       <x:c r="A28" s="16" t="s">
-        <x:v>773</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B28" s="13" t="s">
-        <x:v>1033</x:v>
+        <x:v>1002</x:v>
       </x:c>
       <x:c r="C28" s="13" t="s">
-        <x:v>1034</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="D28" s="15"/>
     </x:row>
     <x:row r="29" ht="15" customHeight="1">
       <x:c r="A29" s="16" t="s">
-        <x:v>781</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>1035</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="C29" s="13" t="s">
-        <x:v>1036</x:v>
+        <x:v>1005</x:v>
       </x:c>
       <x:c r="D29" s="15"/>
     </x:row>
     <x:row r="30" ht="15" customHeight="1">
       <x:c r="A30" s="16" t="s">
-        <x:v>813</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B30" s="13" t="s">
-        <x:v>807</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="C30" s="13" t="s">
-        <x:v>1037</x:v>
+        <x:v>1006</x:v>
       </x:c>
       <x:c r="D30" s="15"/>
     </x:row>
     <x:row r="31" ht="15" customHeight="1">
       <x:c r="A31" s="16" t="s">
-        <x:v>821</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>1038</x:v>
+        <x:v>1007</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>1039</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="D31" s="15"/>
     </x:row>
     <x:row r="32" ht="15" customHeight="1">
       <x:c r="A32" s="16" t="s">
-        <x:v>756</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B32" s="13" t="s">
-        <x:v>1040</x:v>
+        <x:v>1009</x:v>
       </x:c>
       <x:c r="C32" s="13" t="s">
-        <x:v>1041</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="D32" s="15"/>
     </x:row>
     <x:row r="33" ht="15" customHeight="1">
       <x:c r="A33" s="16" t="s">
-        <x:v>739</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>1042</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="C33" s="13" t="s">
-        <x:v>1043</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="D33" s="15"/>
     </x:row>
     <x:row r="34" ht="15" customHeight="1">
       <x:c r="A34" s="16" t="s">
-        <x:v>843</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>1044</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="C34" s="15" t="s">
-        <x:v>1005</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="D34" s="15"/>
     </x:row>
     <x:row r="35" ht="15" customHeight="1">
       <x:c r="A35" s="16" t="s">
-        <x:v>828</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>823</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="C35" s="15" t="s">
-        <x:v>1005</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="D35" s="15"/>
     </x:row>
@@ -11363,12 +11325,12 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>1045</x:v>
+        <x:v>1014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="17.149999618530273" customHeight="1">
       <x:c r="A3" s="4" t="s">
-        <x:v>1046</x:v>
+        <x:v>1015</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
@@ -11376,7 +11338,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>1047</x:v>
+        <x:v>1016</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
@@ -11384,7 +11346,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
-        <x:v>1048</x:v>
+        <x:v>1017</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
@@ -11392,7 +11354,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="13" t="s">
-        <x:v>1049</x:v>
+        <x:v>1018</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
@@ -11400,7 +11362,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
-        <x:v>1050</x:v>
+        <x:v>1019</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
@@ -11408,7 +11370,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="15" t="s">
-        <x:v>1051</x:v>
+        <x:v>1020</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
@@ -11416,7 +11378,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>1052</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
@@ -11424,7 +11386,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="15" t="s">
-        <x:v>1053</x:v>
+        <x:v>1022</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
@@ -11432,7 +11394,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>1054</x:v>
+        <x:v>1023</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
@@ -11440,7 +11402,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>1055</x:v>
+        <x:v>1024</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
@@ -11448,7 +11410,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>1056</x:v>
+        <x:v>1025</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
@@ -11456,7 +11418,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>1057</x:v>
+        <x:v>1026</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
@@ -11464,12 +11426,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>1058</x:v>
+        <x:v>1027</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="17.149999618530273" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>1059</x:v>
+        <x:v>1028</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
@@ -11477,7 +11439,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B18" s="13" t="s">
-        <x:v>1060</x:v>
+        <x:v>1029</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
@@ -11485,7 +11447,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>1061</x:v>
+        <x:v>1030</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
@@ -11493,7 +11455,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
-        <x:v>1062</x:v>
+        <x:v>1031</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
@@ -11501,7 +11463,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>1063</x:v>
+        <x:v>1032</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
@@ -11509,7 +11471,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>1064</x:v>
+        <x:v>1033</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
@@ -11517,7 +11479,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>1065</x:v>
+        <x:v>1034</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
@@ -11525,7 +11487,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>1066</x:v>
+        <x:v>1035</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
@@ -11533,12 +11495,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>1067</x:v>
+        <x:v>1036</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="17.149999618530273" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>1068</x:v>
+        <x:v>1037</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="18" customHeight="1">
@@ -11546,7 +11508,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B28" s="13" t="s">
-        <x:v>1069</x:v>
+        <x:v>1038</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="18" customHeight="1">
@@ -11554,7 +11516,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>1070</x:v>
+        <x:v>1039</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="18" customHeight="1">
@@ -11562,7 +11524,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B30" s="13" t="s">
-        <x:v>1071</x:v>
+        <x:v>1040</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="18" customHeight="1">
@@ -11570,7 +11532,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>1072</x:v>
+        <x:v>1041</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="18" customHeight="1">
@@ -11578,7 +11540,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B32" s="13" t="s">
-        <x:v>1073</x:v>
+        <x:v>1042</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="18" customHeight="1">
@@ -11586,7 +11548,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>1074</x:v>
+        <x:v>1043</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="18" customHeight="1">
@@ -11594,7 +11556,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>1075</x:v>
+        <x:v>1044</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="18" customHeight="1">
@@ -11602,7 +11564,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>1076</x:v>
+        <x:v>1045</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11622,7 +11584,7 @@
   <x:sheetData>
     <x:row r="1" ht="17.399999618530273" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>1046</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -11630,10 +11592,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>1078</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>1079</x:v>
+        <x:v>1048</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -11641,10 +11603,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="17" t="s">
-        <x:v>1080</x:v>
-      </x:c>
-      <x:c r="C4" s="13" t="s">
-        <x:v>1081</x:v>
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="str">
+        <x:v>금액 비교가 가능한 작년 동월·예상 절감액은 원화 영향을 먼저 보여준다. 1인 가구 공개 기준처럼 요금이 없는 비교는 사용량 차이와 단위를 명확히 표시한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="29.899999618530273" customHeight="1">
@@ -11652,10 +11614,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>1082</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="C5" s="13" t="s">
-        <x:v>1083</x:v>
+        <x:v>1051</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="29.899999618530273" customHeight="1">
@@ -11663,10 +11625,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="17" t="s">
-        <x:v>1084</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="C6" s="13" t="s">
-        <x:v>1085</x:v>
+        <x:v>1053</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -11674,10 +11636,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>1086</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="C7" s="13" t="s">
-        <x:v>1087</x:v>
+        <x:v>1055</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29.899999618530273" customHeight="1">
@@ -11685,10 +11647,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="17" t="s">
-        <x:v>1088</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>1089</x:v>
+        <x:v>1057</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29.899999618530273" customHeight="1">
@@ -11696,10 +11658,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="17" t="s">
-        <x:v>1090</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>1091</x:v>
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>진단은 1인 가구 평균 사용량(+작년 동월), What-if는 에코마일리지 규칙대로 직전 2년 같은 기간 평균. 개인 과거 이력은 에코마일리지 연동값에 한해 사용한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -11707,10 +11669,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="17" t="s">
-        <x:v>1092</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>1093</x:v>
+        <x:v>1060</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="29.899999618530273" customHeight="1">
@@ -11718,10 +11680,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="17" t="s">
-        <x:v>1094</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>1095</x:v>
+        <x:v>1062</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="29.899999618530273" customHeight="1">
@@ -11729,10 +11691,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="17" t="s">
-        <x:v>1096</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="C12" s="13" t="s">
-        <x:v>1097</x:v>
+        <x:v>1064</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
@@ -11740,10 +11702,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="17" t="s">
-        <x:v>1098</x:v>
+        <x:v>1065</x:v>
       </x:c>
       <x:c r="C13" s="13" t="s">
-        <x:v>1099</x:v>
+        <x:v>1066</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
@@ -11751,15 +11713,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="17" t="s">
-        <x:v>1100</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>1101</x:v>
+        <x:v>1068</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="21.649999618530273" customHeight="1">
       <x:c r="A16" s="18" t="s">
-        <x:v>1102</x:v>
+        <x:v>1069</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" customHeight="1">
@@ -11767,13 +11729,13 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>1103</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>1104</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="D17" s="5" t="s">
-        <x:v>1105</x:v>
+        <x:v>1072</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="29.899999618530273" customHeight="1">
@@ -11781,13 +11743,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B18" s="17" t="s">
-        <x:v>1106</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="C18" s="13" t="s">
-        <x:v>1107</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="D18" s="13" t="s">
-        <x:v>1108</x:v>
+        <x:v>1075</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
@@ -11795,13 +11757,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="17" t="s">
-        <x:v>1109</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
-        <x:v>1110</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>1111</x:v>
+        <x:v>1078</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" customHeight="1">
@@ -11809,13 +11771,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B20" s="17" t="s">
-        <x:v>1112</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>1113</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>1114</x:v>
+        <x:v>1081</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
@@ -11823,13 +11785,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B21" s="17" t="s">
-        <x:v>506</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>1115</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>1116</x:v>
+        <x:v>1083</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" customHeight="1">
@@ -11837,13 +11799,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B22" s="17" t="s">
-        <x:v>1117</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>1118</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>1119</x:v>
+        <x:v>1086</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" customHeight="1">
@@ -11851,13 +11813,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B23" s="17" t="s">
-        <x:v>1120</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>1121</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="D23" s="13" t="s">
-        <x:v>1122</x:v>
+        <x:v>1089</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" customHeight="1">
@@ -11865,13 +11827,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="17" t="s">
-        <x:v>1123</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>1124</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>1125</x:v>
+        <x:v>1092</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" customHeight="1">
@@ -11879,13 +11841,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="17" t="s">
-        <x:v>1126</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="C25" s="15" t="s">
-        <x:v>1127</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="D25" s="13" t="s">
-        <x:v>1128</x:v>
+        <x:v>1095</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" customHeight="1">
@@ -11893,13 +11855,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B26" s="17" t="s">
-        <x:v>1129</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>1130</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>1131</x:v>
+        <x:v>1098</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" customHeight="1">
@@ -11907,13 +11869,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="17" t="s">
-        <x:v>1132</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>1133</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>1134</x:v>
+        <x:v>1101</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" customHeight="1">
@@ -11921,13 +11883,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B28" s="17" t="s">
-        <x:v>1135</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>1136</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>1137</x:v>
+        <x:v>1104</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" customHeight="1">
@@ -11935,41 +11897,41 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B29" s="17" t="s">
-        <x:v>1138</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="C29" s="13" t="s">
-        <x:v>1139</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="D29" s="13" t="s">
-        <x:v>1140</x:v>
+        <x:v>1107</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" customHeight="1">
       <x:c r="A30" s="8">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B30" s="17" t="s">
-        <x:v>1141</x:v>
-      </x:c>
-      <x:c r="C30" s="13" t="s">
-        <x:v>1142</x:v>
-      </x:c>
-      <x:c r="D30" s="13" t="s">
-        <x:v>1143</x:v>
+      <x:c r="B30" s="17" t="str">
+        <x:v>녹색생활실천 예정액</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="str">
+        <x:v>예정액 = 유효 횟수 × 단가, 항목 상한 적용</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="str">
+        <x:v>전자영수증 24건 × 10원 = 240원</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" customHeight="1">
       <x:c r="A31" s="8">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B31" s="17" t="s">
-        <x:v>1144</x:v>
-      </x:c>
-      <x:c r="C31" s="13" t="s">
-        <x:v>1145</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>1146</x:v>
+      <x:c r="B31" s="17" t="str">
+        <x:v>1인 가구 평균 사용량 차이</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="str">
+        <x:v>사용자 사용량 − 1인 가구 평균 사용량, 차이율 = 차이 ÷ 평균 × 100</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="str">
+        <x:v>전기 210.000 − 247.633 = −37.633kWh</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" customHeight="1">
@@ -11977,18 +11939,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B32" s="17" t="s">
-        <x:v>1147</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="C32" s="13" t="s">
-        <x:v>1148</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
-        <x:v>1149</x:v>
+        <x:v>1110</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
       <x:c r="B33" s="34" t="s">
-        <x:v>1150</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="C33" s="25"/>
       <x:c r="D33" s="25"/>
@@ -12014,7 +11976,7 @@
   <x:sheetData>
     <x:row r="1" ht="17.399999618530273" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>1151</x:v>
+        <x:v>1112</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -12022,19 +11984,19 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>1152</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>1153</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>1154</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>1155</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
-        <x:v>1156</x:v>
+        <x:v>1117</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -12042,16 +12004,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>1157</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>879</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="D4" s="13" t="s">
-        <x:v>1158</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="E4" s="15" t="s">
-        <x:v>1159</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="F4" s="15"/>
     </x:row>
@@ -12060,57 +12022,59 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
-        <x:v>1160</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>1161</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="D5" s="13" t="s">
-        <x:v>1158</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="E5" s="15" t="s">
-        <x:v>1159</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="F5" s="15" t="s">
-        <x:v>1162</x:v>
+        <x:v>1123</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="8">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="s">
-        <x:v>1163</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="s">
-        <x:v>1164</x:v>
-      </x:c>
-      <x:c r="D6" s="13" t="s">
-        <x:v>1165</x:v>
-      </x:c>
-      <x:c r="E6" s="13" t="s">
-        <x:v>1166</x:v>
-      </x:c>
-      <x:c r="F6" s="15"/>
+      <x:c r="B6" s="13" t="str">
+        <x:v>1인 가구 전기·도시가스 월별 마이크로데이터 추가 확보</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>A-3-01, COM-09</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="str">
+        <x:v>유현</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="str">
+        <x:v>KESIS 사용 목적 설문 후 다운로드</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="str">
+        <x:v>2026-09-08 공개 집계의 월평균 환산값 적용. 월별 마이크로데이터 확보 시 JSON 교체 예정(결정 C-22)</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="8">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="s">
-        <x:v>1167</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="s">
-        <x:v>1168</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="s">
-        <x:v>1165</x:v>
-      </x:c>
-      <x:c r="E7" s="13" t="s">
-        <x:v>1169</x:v>
-      </x:c>
-      <x:c r="F7" s="15" t="s">
-        <x:v>1170</x:v>
+      <x:c r="B7" s="13" t="str">
+        <x:v>1인 가구 수도 전체 주거유형 평균 추가 확보</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>A-3-01, A-3-07</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>유현</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>서울물연구원·공공데이터 검토</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str">
+        <x:v>2026-09-08 서울 아파트 1인 가구 하루 438L 적용. 전체 주거유형 자료 확보 시 JSON 교체 예정(결정 C-22)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -12118,19 +12082,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>1171</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D8" s="13" t="s">
-        <x:v>1172</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="E8" s="13" t="s">
-        <x:v>1173</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="F8" s="20" t="s">
-        <x:v>1174</x:v>
+        <x:v>1127</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
@@ -12138,19 +12102,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>1175</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>945</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>1176</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
-        <x:v>1177</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="F9" s="15" t="s">
-        <x:v>1178</x:v>
+        <x:v>1131</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -12158,19 +12122,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>1179</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>1180</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="D10" s="13" t="s">
-        <x:v>1181</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
-        <x:v>1182</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="F10" s="15" t="s">
-        <x:v>1183</x:v>
+        <x:v>1136</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
@@ -12178,22 +12142,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>1184</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>1185</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>1172</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>1186</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="F11" s="15"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="B13" s="11" t="s">
-        <x:v>1187</x:v>
+        <x:v>1140</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R2bee5e1ea7d64065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rd1502304baec462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R78315fc6e0c14d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R23acfabd39254b68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R056130b3acb44f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Ree30036ac4574eac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rfe9e2ba13c4c4f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R43a223bdb81e4568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R64bcccc7a72f47d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R0dbcc87dd25c4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R2f8c092f59a64e2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rddd22f1059c34770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rdef51515f2f34821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rf12e444970104186"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1137,7 +1137,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>그린포켓 기능명세서 ver3.4</x:v>
+        <x:v>그린포켓 기능명세서 ver3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -1145,7 +1145,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="27" t="str">
-        <x:v>2026-09-08 (결정 C-1~C-25 반영)</x:v>
+        <x:v>2026-09-08 (결정 C-1~C-28 반영)</x:v>
       </x:c>
       <x:c r="C3" s="25"/>
       <x:c r="D3" s="25"/>
@@ -1217,7 +1217,7 @@
     </x:row>
     <x:row r="10" ht="31.5" customHeight="1">
       <x:c r="A10" s="26" t="str">
-        <x:v>이메일 가입·로그인 → 2단계 프로필 → 고지서·진단 → 에코 What-if → 마일리지·포켓 → 마이 청년정책 추천</x:v>
+        <x:v>본인인증 정보 입력·이메일 가입 → 에코마일리지 연동 → 고지서·진단 → 에코 What-if → 마일리지·포켓 → 마이 선택형 청년정책 추천</x:v>
       </x:c>
       <x:c r="B10" s="25"/>
       <x:c r="C10" s="25"/>
@@ -1800,7 +1800,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="4" t="str">
-        <x:v>ver3.4 변경 사항</x:v>
+        <x:v>ver3.5 변경 사항</x:v>
       </x:c>
       <x:c r="B51"/>
     </x:row>
@@ -1820,10 +1820,10 @@
     </x:row>
     <x:row r="53" ht="20" customHeight="1">
       <x:c r="A53" s="2" t="str">
-        <x:v>마이 탭</x:v>
+        <x:v>회원가입</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>마이페이지를 마이로 변경하고 기존 기능 아래 청년정책 추천 추가(C-22)</x:v>
+        <x:v>본인인증 성공으로 간주하고 이름·생년월일·성별·휴대전화번호를 모두 가입 시 저장(C-27)</x:v>
       </x:c>
       <x:c r="C53" s="25"/>
       <x:c r="D53" s="25"/>
@@ -1837,7 +1837,7 @@
         <x:v>온보딩</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>ONB-02·03에서 생년월일·주거·현재 상태·연소득 구간·가구 상태·관심 분야 최대 3개 수집(C-23)</x:v>
+        <x:v>별도 온보딩 입력 화면을 제거하고 가입 직후 에코마일리지 연동 화면으로 이동(C-26)</x:v>
       </x:c>
       <x:c r="C54" s="25"/>
       <x:c r="D54" s="25"/>
@@ -1848,10 +1848,10 @@
     </x:row>
     <x:row r="55" ht="52" customHeight="1">
       <x:c r="A55" s="2" t="str">
-        <x:v>지역</x:v>
+        <x:v>정책 추천 조건</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>프로필 지역 입력·수정 제거, 에코마일리지 연동 주소를 단일 기준으로 사용(C-25)</x:v>
+        <x:v>현재 상태·연소득 구간·가구 상태는 마이에서 원하는 사용자만 입력·저장. 관심 분야·주거 형태·평수 미수집(C-28)</x:v>
       </x:c>
       <x:c r="C55" s="25"/>
       <x:c r="D55" s="25"/>
@@ -1862,10 +1862,10 @@
     </x:row>
     <x:row r="56" ht="20" customHeight="1">
       <x:c r="A56" s="2" t="str">
-        <x:v>정책 동기화</x:v>
+        <x:v>지역</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>온통청년 OPEN API를 100건 단위로 주기 동기화하고 사용자 조회는 로컬 DB 사용(C-24)</x:v>
+        <x:v>거주지는 에코마일리지 연동 주소만 사용하고 앱 내부 입력·수정은 제공하지 않음(C-26)</x:v>
       </x:c>
       <x:c r="C56" s="25"/>
       <x:c r="D56" s="25"/>
@@ -1876,10 +1876,10 @@
     </x:row>
     <x:row r="57" ht="36" customHeight="1">
       <x:c r="A57" s="2" t="str">
-        <x:v>판정</x:v>
+        <x:v>정책 동기화</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>명확한 조건만 자동 판정하고 자유 텍스트·미수집 조건은 확인 필요</x:v>
+        <x:v>온통청년 OPEN API를 100건 단위로 주기 동기화하고 사용자 조회는 로컬 DB 사용(C-24)</x:v>
       </x:c>
       <x:c r="C57" s="25"/>
       <x:c r="D57" s="25"/>
@@ -1890,10 +1890,10 @@
     </x:row>
     <x:row r="58" ht="20" customHeight="1">
       <x:c r="A58" s="2" t="str">
-        <x:v>보안</x:v>
+        <x:v>판정</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>YOUTH_POLICY_API_KEY 환경변수 사용, 인증키 저장소·로그 노출 금지</x:v>
+        <x:v>생년월일·에코 연동 지역 등 구조화된 확실한 조건만 자동 판정. 자유 텍스트 조건은 확인 필요</x:v>
       </x:c>
       <x:c r="C58" s="25"/>
       <x:c r="D58" s="25"/>
@@ -1907,7 +1907,7 @@
         <x:v>건수</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>기능 109→116(P0 82→89), API 65→71</x:v>
+        <x:v>기능 116건 유지, API는 온보딩 프로필 저장·수정 제거 후 69건</x:v>
       </x:c>
       <x:c r="C59"/>
       <x:c r="D59"/>
@@ -2646,19 +2646,19 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G13" s="13" t="str">
-        <x:v>이메일은 공백 제거 후 소문자로 정규화하고 중복을 차단한다. 비밀번호는 8자 이상·UTF-8 기준 72바이트 이하이며 BCrypt 해시만 저장한다. 성공 시 Access Token을 응답하고 Refresh Token은 HttpOnly 쿠키로 설정한다.</x:v>
+        <x:v>이메일은 공백 제거 후 소문자로 정규화하고 중복을 차단한다. 본인인증은 성공한 것으로 간주하고 이름·생년월일·성별·휴대전화번호를 모두 받는다. 비밀번호는 8자 이상·UTF-8 기준 72바이트 이하이며 BCrypt 해시만 저장한다. 성공 시 Access Token을 응답하고 Refresh Token은 HttpOnly 쿠키로 설정한다.</x:v>
       </x:c>
       <x:c r="H13" s="20" t="str">
-        <x:v>email, password, name, accessToken, refreshToken(cookie)</x:v>
+        <x:v>email, password, name, birthDate, gender, phoneNumber, accessToken, refreshToken(cookie)</x:v>
       </x:c>
       <x:c r="I13" s="13" t="str">
         <x:v>없음</x:v>
       </x:c>
       <x:c r="J13" s="13" t="str">
-        <x:v>이메일 형식·비밀번호 길이·중복 이메일 오류</x:v>
+        <x:v>필수값 누락·이메일/생년월일/휴대전화번호 형식 오류·중복 이메일·중복 휴대전화번호</x:v>
       </x:c>
       <x:c r="K13" s="13" t="str">
-        <x:v>app_user와 인증 계정이 함께 생성되고 그린포켓 계좌번호가 발급되며 ONB-02로 이동한다.</x:v>
+        <x:v>app_user와 인증 계정이 함께 생성되고 본인인증 정보와 그린포켓 계좌번호가 저장되며 WF-01로 이동한다.</x:v>
       </x:c>
       <x:c r="L13" s="22" t="str">
         <x:v>P0</x:v>
@@ -2673,7 +2673,7 @@
         <x:v>ONB-01</x:v>
       </x:c>
       <x:c r="P13" s="20" t="str">
-        <x:v>결정 C-17</x:v>
+        <x:v>결정 C-17·C-27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="29.899999618530273" customHeight="1">
@@ -2708,7 +2708,7 @@
         <x:v>자격 증명 불일치</x:v>
       </x:c>
       <x:c r="K14" s="13" t="str">
-        <x:v>미완료 사용자는 ONB-02, 온보딩 완료 사용자는 WF-06으로 이동한다.</x:v>
+        <x:v>에코 미연동은 WF-01, 연동 중은 WF-02, 연동 완료는 WF-06으로 이동한다.</x:v>
       </x:c>
       <x:c r="L14" s="22" t="str">
         <x:v>P0</x:v>
@@ -2834,31 +2834,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D17" s="10" t="str">
         <x:v>A-1-01</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>생년월일·정책 지역 기준</x:v>
+        <x:v>가입 본인인증 정보 저장</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>사용자</x:v>
+        <x:v>시스템</x:v>
       </x:c>
       <x:c r="G17" s="13" t="str">
-        <x:v>생년월일을 입력해 만 나이를 계산한다. 거주지역은 온보딩에서 받지 않고 에코마일리지 연동 주소를 정책 추천의 단일 지역 기준으로 사용한다.</x:v>
+        <x:v>회원가입 본인인증 화면에서 이름·생년월일·성별·휴대전화번호를 모두 입력받고 인증 성공으로 간주해 사용자 정보에 저장한다.</x:v>
       </x:c>
       <x:c r="H17" s="15" t="str">
-        <x:v>birthDate, ecoSidoCode, ecoSigunguCode</x:v>
+        <x:v>name, birthDate, gender, phoneNumber</x:v>
       </x:c>
       <x:c r="I17" s="13" t="str">
-        <x:v>회원가입 완료</x:v>
+        <x:v>회원가입 시도</x:v>
       </x:c>
       <x:c r="J17" s="13" t="str">
-        <x:v>미래 날짜·지원 범위를 벗어난 날짜 → 입력 오류, 에코 미연동 → 전국 정책만 추천</x:v>
+        <x:v>필수값 누락·미래 생년월일·휴대전화번호 형식 오류·중복 번호 → 입력 오류</x:v>
       </x:c>
       <x:c r="K17" s="13" t="str">
-        <x:v>생년월일이 저장되고 에코 연동 여부에 따라 전국 또는 전국+지역 정책이 추천된다.</x:v>
+        <x:v>가입 후 본인인증 정보가 사용자 계정에서 조회된다.</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
         <x:v>P0</x:v>
@@ -2870,10 +2870,10 @@
         <x:v>FE·BE</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>ONB-02</x:v>
+        <x:v>ONB-01</x:v>
       </x:c>
       <x:c r="P17" s="15" t="str">
-        <x:v>결정 C-23·C-25</x:v>
+        <x:v>결정 C-27</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="29.899999618530273" customHeight="1">
@@ -2884,31 +2884,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D18" s="10" t="str">
         <x:v>A-1-02</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
-        <x:v>주거 형태 선택</x:v>
+        <x:v>별도 온보딩 입력 제거</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>사용자</x:v>
+        <x:v>시스템</x:v>
       </x:c>
       <x:c r="G18" s="13" t="str">
-        <x:v>원룸 · 오피스텔 · 아파트 · 다세대 칩 중 하나를 선택한다(그룹 단일 선택).</x:v>
+        <x:v>회원가입 뒤 생활·주거·정책 추천 정보를 받는 별도 온보딩 화면을 두지 않는다.</x:v>
       </x:c>
       <x:c r="H18" s="15" t="str">
-        <x:v>housingType</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I18" s="13" t="str">
         <x:v>회원가입 완료</x:v>
       </x:c>
       <x:c r="J18" s="15" t="str">
-        <x:v>미선택 그룹 안내</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="K18" s="13" t="str">
-        <x:v>필수값이 없으면 다음이 비활성화되고 안내가 표시된다.</x:v>
+        <x:v>추가 입력 없이 바로 에코마일리지 연동 화면으로 이동한다.</x:v>
       </x:c>
       <x:c r="L18" s="8" t="str">
         <x:v>P0</x:v>
@@ -2920,9 +2920,11 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
-        <x:v>ONB-02</x:v>
-      </x:c>
-      <x:c r="P18" s="15"/>
+        <x:v>ONB-01</x:v>
+      </x:c>
+      <x:c r="P18" s="15" t="str">
+        <x:v>결정 C-26</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58.25" customHeight="1">
       <x:c r="A19" s="8" t="n">
@@ -2932,31 +2934,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C19" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D19" s="10" t="str">
         <x:v>A-1-03</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>평수 구간 선택</x:v>
+        <x:v>에코마일리지 연동 우선 진입</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>사용자</x:v>
+        <x:v>시스템</x:v>
       </x:c>
       <x:c r="G19" s="13" t="str">
-        <x:v>10평 이하 · 10~20평 · 20평 이상 라디오 중 하나를 선택한다.</x:v>
+        <x:v>신규 사용자는 가입 완료 직후 WF-01로 이동한다. 다시 로그인하면 에코 연동 상태에 따라 WF-01·WF-02·WF-06으로 라우팅한다.</x:v>
       </x:c>
       <x:c r="H19" s="15" t="str">
-        <x:v>areaBand</x:v>
+        <x:v>ecoLinkStatus, entryScreen</x:v>
       </x:c>
       <x:c r="I19" s="13" t="str">
-        <x:v>회원가입 완료</x:v>
+        <x:v>회원가입 또는 로그인 완료</x:v>
       </x:c>
       <x:c r="J19" s="13" t="str">
-        <x:v>미선택 그룹 안내</x:v>
+        <x:v>연동 실패 → WF-01에서 재시도</x:v>
       </x:c>
       <x:c r="K19" s="13" t="str">
-        <x:v>선택 구간이 프로필 요약(진단 헤더·마이)에 표시된다.</x:v>
+        <x:v>사용자가 에코마일리지 연동 흐름을 먼저 시작한다.</x:v>
       </x:c>
       <x:c r="L19" s="8" t="str">
         <x:v>P0</x:v>
@@ -2968,9 +2970,11 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>ONB-02</x:v>
-      </x:c>
-      <x:c r="P19" s="15"/>
+        <x:v>WF-01</x:v>
+      </x:c>
+      <x:c r="P19" s="15" t="str">
+        <x:v>결정 C-26</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="29.899999618530273" customHeight="1">
       <x:c r="A20" s="8" t="n">
@@ -2980,31 +2984,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C20" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D20" s="10" t="str">
         <x:v>A-1-04</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>정책 추천 조건 입력</x:v>
+        <x:v>마이 정책 추천 조건 입력</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G20" s="13" t="str">
-        <x:v>현재 상태·연소득 구간·가구 상태를 각각 하나 선택하고 관심 분야는 일자리·주거·교육·복지문화·참여권리 중 최대 3개를 선택한다. 미수집 조건은 자동 탈락 근거로 사용하지 않는다.</x:v>
+        <x:v>청년정책 추천을 원하는 사용자만 마이에서 현재 상태·연소득 구간·가구 상태를 각각 하나 선택한다. 관심 분야·주거 형태·평수는 받지 않는다.</x:v>
       </x:c>
       <x:c r="H20" s="15" t="str">
-        <x:v>currentStatus, annualIncomeBand, householdStatus, interestCategories[]</x:v>
+        <x:v>currentStatus, annualIncomeBand, householdStatus</x:v>
       </x:c>
       <x:c r="I20" s="13" t="str">
-        <x:v>A-1-01~03 입력</x:v>
+        <x:v>로그인</x:v>
       </x:c>
       <x:c r="J20" s="13" t="str">
-        <x:v>필수값 누락·관심 분야 4개 이상·중복 선택 → 입력 오류</x:v>
+        <x:v>필수값 누락·지원하지 않는 enum → 입력 오류</x:v>
       </x:c>
       <x:c r="K20" s="13" t="str">
-        <x:v>저장된 조건으로 추천 결과를 재현할 수 있다.</x:v>
+        <x:v>저장 전 임시 조건으로 추천을 미리 확인할 수 있다.</x:v>
       </x:c>
       <x:c r="L20" s="8" t="str">
         <x:v>P0</x:v>
@@ -3016,10 +3020,10 @@
         <x:v>FE·BE</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>ONB-03</x:v>
+        <x:v>MY-02 · MY-06</x:v>
       </x:c>
       <x:c r="P20" s="15" t="str">
-        <x:v>결정 C-23</x:v>
+        <x:v>결정 C-28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58.25" customHeight="1">
@@ -3030,31 +3034,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C21" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D21" s="10" t="str">
         <x:v>A-1-05</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str">
-        <x:v>프로필 저장·시작</x:v>
+        <x:v>정책 추천 조건 저장</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G21" s="13" t="str">
-        <x:v>ONB-02 생활 기본 정보와 ONB-03 정책 추천 정보를 저장한 뒤 온보딩을 완료하고 What-if 탭(홈)으로 이동한다. 지역은 입력받지 않는다.</x:v>
+        <x:v>마이에서 입력한 현재 상태·연소득 구간·가구 상태만 저장한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 읽기 전용으로 사용한다.</x:v>
       </x:c>
       <x:c r="H21" s="15" t="str">
-        <x:v>POST /profile</x:v>
+        <x:v>PUT /profile/policy-preferences</x:v>
       </x:c>
       <x:c r="I21" s="13" t="str">
-        <x:v>생년월일·주거 형태·평수·현재 상태·연소득 구간·가구 상태 입력</x:v>
+        <x:v>로그인</x:v>
       </x:c>
       <x:c r="J21" s="13" t="str">
-        <x:v>저장 실패 → 재시도</x:v>
+        <x:v>필수값 누락 → 409</x:v>
       </x:c>
       <x:c r="K21" s="13" t="str">
-        <x:v>다시 진입했을 때 프로필이 유지되고 온보딩을 건너뛴다.</x:v>
+        <x:v>저장 후 마이 첫 화면에 추천 정책 최대 5개가 표시된다.</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
         <x:v>P0</x:v>
@@ -3066,10 +3070,10 @@
         <x:v>FE·BE</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>ONB-02 · ONB-03</x:v>
+        <x:v>MY-02 · MY-01</x:v>
       </x:c>
       <x:c r="P21" s="15" t="str">
-        <x:v>결정 C-23</x:v>
+        <x:v>결정 C-28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72.25" customHeight="1">
@@ -3080,31 +3084,31 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
         <x:v>A-1-06</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>프로필 조회·수정</x:v>
+        <x:v>본인 정보·추천 조건 조회</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G22" s="13" t="str">
-        <x:v>마이 기본 정보에서 이름·생년월일·주거 형태·평수와 정책 추천 조건을 조회한다. 수정은 ONB-02·03 폼을 재사용하며 거주지역 수정은 제공하지 않는다.</x:v>
+        <x:v>마이에서 이름·생년월일·성별·휴대전화번호와 저장된 정책 추천 조건을 조회한다. 본인인증 정보와 에코 연동 주소는 읽기 전용이다.</x:v>
       </x:c>
       <x:c r="H22" s="15" t="str">
-        <x:v>PUT /profile</x:v>
+        <x:v>GET /profile, GET /profile/policy-preferences</x:v>
       </x:c>
       <x:c r="I22" s="13" t="str">
-        <x:v>프로필 존재</x:v>
+        <x:v>로그인</x:v>
       </x:c>
       <x:c r="J22" s="13" t="str">
-        <x:v>잘못된 생년월일·지원하지 않는 enum·관심 분야 4개 이상 → 입력 오류</x:v>
+        <x:v>미설정 추천 조건 → 빈값과 설정 CTA</x:v>
       </x:c>
       <x:c r="K22" s="13" t="str">
-        <x:v>수정한 조건으로 프로필과 맞춤 추천 결과가 즉시 갱신된다.</x:v>
+        <x:v>본인 정보와 선택형 추천 조건이 구분되어 표시된다.</x:v>
       </x:c>
       <x:c r="L22" s="8" t="str">
         <x:v>P0</x:v>
@@ -3118,7 +3122,9 @@
       <x:c r="O22" s="15" t="str">
         <x:v>MY-01 · MY-02</x:v>
       </x:c>
-      <x:c r="P22" s="13"/>
+      <x:c r="P22" s="13" t="str">
+        <x:v>결정 C-27·C-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58.25" customHeight="1">
       <x:c r="A23" s="8" t="n">
@@ -3128,7 +3134,7 @@
         <x:v>A. 생활비 진단</x:v>
       </x:c>
       <x:c r="C23" s="12" t="str">
-        <x:v>A-1. 온보딩 프로필</x:v>
+        <x:v>A-1. 가입·선택 프로필</x:v>
       </x:c>
       <x:c r="D23" s="10" t="str">
         <x:v>A-1-07</x:v>
@@ -3140,19 +3146,19 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G23" s="13" t="str">
-        <x:v>진단 헤더의 기존 호환 표시는 유지한다. 마이 카드에는 이름·주거 형태·평수와 에코 연동 주소를 각각 표시하며 프로필 주소와 비교하지 않는다.</x:v>
+        <x:v>마이 카드에는 본인인증 정보와 에코 연동 주소를 각각 표시한다. 주거 형태·평수·앱 내부 거주지 입력·수정은 표시하지 않는다.</x:v>
       </x:c>
       <x:c r="H23" s="15" t="str">
-        <x:v>profile</x:v>
+        <x:v>profile, ecoAddress</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>프로필 존재</x:v>
+        <x:v>로그인</x:v>
       </x:c>
       <x:c r="J23" s="13" t="str">
-        <x:v>—</x:v>
+        <x:v>에코 미연동 → 주소 없음과 연동 CTA</x:v>
       </x:c>
       <x:c r="K23" s="13" t="str">
-        <x:v>프로필과 에코 연동 주소가 구분되어 표시된다.</x:v>
+        <x:v>마이 첫 화면에서 본인 정보·연동 정보·정책 추천 영역을 확인한다.</x:v>
       </x:c>
       <x:c r="L23" s="8" t="str">
         <x:v>P1</x:v>
@@ -3164,9 +3170,11 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>AN-07 · MY-01</x:v>
-      </x:c>
-      <x:c r="P23" s="15"/>
+        <x:v>MY-01</x:v>
+      </x:c>
+      <x:c r="P23" s="15" t="str">
+        <x:v>결정 C-26~C-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="86.5" customHeight="1">
       <x:c r="A24" s="8" t="n">
@@ -7260,10 +7268,10 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G108" t="str">
-        <x:v>기존 보관함·연동·포켓 정보와 이름·생년월일·주거 형태·평수를 표시한다. 거주지역은 에코마일리지 등록 주소만 표시하며 앱 내부 수정·프로필 주소 비교를 제공하지 않는다. 기본 정보 아래에 맞춤 정책 추천 영역을 둔다.</x:v>
+        <x:v>기존 보관함·연동·포켓 정보와 이름·생년월일·성별·휴대전화번호를 표시한다. 거주지역은 에코마일리지 등록 주소만 읽기 전용으로 표시한다. 첫 화면 하단에 맞춤 정책 추천 최대 5개를 둔다.</x:v>
       </x:c>
       <x:c r="H108" t="str">
-        <x:v>profile, ecoAddress{label, registeredAt}, policyRecommendationSummary</x:v>
+        <x:v>profile{name,birthDate,gender,phoneNumber}, ecoAddress, policyRecommendationSummary.preview(최대 5)</x:v>
       </x:c>
       <x:c r="I108" t="str">
         <x:v>프로필 존재</x:v>
@@ -7272,7 +7280,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>저장 프로필·에코 주소·추천 요약이 각각 올바르게 표시된다.</x:v>
+        <x:v>본인 정보·에코 주소·추천 5개와 설정 CTA가 상태에 맞게 표시된다.</x:v>
       </x:c>
       <x:c r="L108" t="str">
         <x:v>P0</x:v>
@@ -7287,7 +7295,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P108" t="str">
-        <x:v>에코 미연동이면 전국 정책 추천과 연동 CTA 표시(결정 C-25)</x:v>
+        <x:v>정책 조건 미설정은 설정 CTA, 에코 미연동은 연동 CTA 표시(결정 C-26~C-28)</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7456,19 +7464,19 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>저장된 생년월일·현재 상태·연소득 구간·가구 상태·관심 분야와 에코 연동 주소로 정책을 판정하고 신청 가능성이 높은 순으로 추천한다. 명확하지 않은 자유 텍스트 조건은 확인 필요로 표시한다.</x:v>
+        <x:v>가입 시 저장한 생년월일, 마이에서 저장한 현재 상태·연소득 구간·가구 상태, 에코 연동 주소로 정책을 정렬한다. 연령·지역처럼 구조화된 확실한 조건만 자동 판정하고 자유 텍스트 조건은 확인 필요로 표시한다.</x:v>
       </x:c>
       <x:c r="H112" t="str">
         <x:v>GET /policies/recommendations</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>정책 추천 프로필 완료, 정책 동기화 데이터 존재</x:v>
+        <x:v>정책 추천 조건 완료, 정책 동기화 데이터 존재</x:v>
       </x:c>
       <x:c r="J112" t="str">
-        <x:v>에코 미연동 → 전국 정책만 추천+연동 CTA, 데이터 없음 → 준비 중</x:v>
+        <x:v>조건 미설정 → 설정 CTA, 에코 미연동 → 전국 정책+연동 CTA, 데이터 없음 → 준비 중</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>같은 사용자 조건은 같은 추천·사유를 반환한다.</x:v>
+        <x:v>마이 첫 화면에는 상위 5개, 전체 화면에는 동일 기준 전체 결과를 반환한다.</x:v>
       </x:c>
       <x:c r="L112" t="str">
         <x:v>P0</x:v>
@@ -7482,7 +7490,9 @@
       <x:c r="O112" t="str">
         <x:v>MY-01</x:v>
       </x:c>
-      <x:c r="P112" t="str"/>
+      <x:c r="P112" t="str">
+        <x:v>결정 C-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="n">
@@ -7600,13 +7610,13 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G115" t="str">
-        <x:v>화면에서 바꾼 조건으로 추천을 다시 계산하되 저장된 사용자 정보를 변경하지 않는다.</x:v>
+        <x:v>마이 상세 화면에서 현재 상태·연소득 구간·가구 상태만 바꿔 추천을 다시 계산한다. 가입 생년월일과 에코 연동 주소는 읽기 전용이며 저장된 사용자 정보는 변경하지 않는다.</x:v>
       </x:c>
       <x:c r="H115" t="str">
         <x:v>POST /policies/recommendations/preview</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>정책 동기화 데이터 존재</x:v>
+        <x:v>로그인, 정책 동기화 데이터 존재</x:v>
       </x:c>
       <x:c r="J115" t="str">
         <x:v>잘못된 조건 → 400</x:v>
@@ -7626,7 +7636,9 @@
       <x:c r="O115" t="str">
         <x:v>MY-06</x:v>
       </x:c>
-      <x:c r="P115" t="str"/>
+      <x:c r="P115" t="str">
+        <x:v>결정 C-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="n">
@@ -7648,7 +7660,7 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G116" t="str">
-        <x:v>내 정보에 저장을 선택했을 때만 생년월일·주거 형태·평수·현재 상태·연소득 구간·가구 상태·관심 분야를 갱신한다.</x:v>
+        <x:v>내 정보에 저장을 선택했을 때만 현재 상태·연소득 구간·가구 상태를 갱신한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 사용한다.</x:v>
       </x:c>
       <x:c r="H116" t="str">
         <x:v>GET/PUT /profile/policy-preferences</x:v>
@@ -7657,10 +7669,10 @@
         <x:v>로그인</x:v>
       </x:c>
       <x:c r="J116" t="str">
-        <x:v>관심 분야 4개 이상 → 400</x:v>
+        <x:v>필수값 누락·지원하지 않는 enum → 400 또는 409</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>저장 후 마이 추천이 새 조건으로 갱신된다.</x:v>
+        <x:v>저장 후 마이 첫 화면의 상위 5개 추천이 새 조건으로 갱신된다.</x:v>
       </x:c>
       <x:c r="L116" t="str">
         <x:v>P0</x:v>
@@ -7674,7 +7686,9 @@
       <x:c r="O116" t="str">
         <x:v>MY-06</x:v>
       </x:c>
-      <x:c r="P116" t="str"/>
+      <x:c r="P116" t="str">
+        <x:v>결정 C-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="n">
@@ -8324,6 +8338,48 @@
         <x:v>A-1-01, E-3-01~05</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>C-26</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>온보딩 제거·에코 연동 우선</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>별도 온보딩 입력 화면을 제거한다. 회원가입 직후 에코마일리지 연동 화면으로 이동하고 거주지는 연동 주소만 사용한다. 주거 형태·평수는 수집하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>COM-13~14, A-1-02~03, E-1-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>C-27</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>회원가입 본인인증 정보</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>외부 본인인증 API 없이 성공한 것으로 간주한다. 이름·생년월일·성별·휴대전화번호를 모두 필수 입력받아 app_user에 저장한다.</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>COM-13, A-1-01, A-1-06~07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>C-28</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>마이 선택형 정책 추천</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>현재 상태·연소득 구간·가구 상태는 마이에서 원하는 사용자만 저장한다. 관심 분야는 받지 않는다. 마이 첫 화면에는 상위 5개, 상세에서는 전체 목록·임시 조건 재추천을 제공한다.</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>A-1-04~07, E-1-01, E-3-01~05</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8341,7 +8397,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>화면 ID 체계 (ONB-03·MY-05·MY-06 추가)</x:v>
+        <x:v>화면 ID 체계 (ONB-02·03 제거, MY-02 정책 추천 설정으로 변경)</x:v>
       </x:c>
       <x:c r="B1"/>
       <x:c r="C1"/>
@@ -8386,13 +8442,13 @@
         <x:v>ONB-02</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>생활 기본 정보</x:v>
+        <x:v>사용하지 않음</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>온보딩 02 · 주거 프로필.png</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>생년월일·주거 형태·평수, 거주지역 없음</x:v>
+        <x:v>별도 온보딩 제거(결정 C-26)</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -8400,13 +8456,13 @@
         <x:v>ONB-03</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>정책 추천 정보</x:v>
+        <x:v>사용하지 않음</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>신규 시안</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>현재 상태·연소득 구간·가구 상태·관심 분야 최대 3개</x:v>
+        <x:v>정책 추천 조건은 MY-02에서 선택 입력(결정 C-28)</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -8808,13 +8864,13 @@
         <x:v>MY-02</x:v>
       </x:c>
       <x:c r="B39" s="13" t="str">
-        <x:v>기본 정보 수정</x:v>
+        <x:v>정책 추천 조건 설정</x:v>
       </x:c>
       <x:c r="C39" s="13" t="str">
-        <x:v>— (ONB-02·03 폼 재사용)</x:v>
+        <x:v>신규 시안</x:v>
       </x:c>
       <x:c r="D39" s="15" t="str">
-        <x:v>거주지역 수정 없음</x:v>
+        <x:v>현재 상태·연소득 구간·가구 상태 입력. 본인정보·에코 주소는 읽기 전용</x:v>
       </x:c>
     </x:row>
     <x:row r="40">

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R1b4726e64e364656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rdf796f90828c4bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Reca09b1bc27644c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R9b9b2fc593e2471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rd01a4a94e0364709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Raefe7a0d0cd24a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R348422822ca34b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R9907d626739e4f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rce65fdbbb5234a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rbab0647f69124573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Re87c7e0d4a0d46dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Ref539e70eeb74d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rbded3fdf4c9c4889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R1c125d06548d4336"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1098,7 +1098,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>그린포켓 기능명세서 ver3.6</x:v>
+        <x:v>그린포켓 기능명세서 ver3.8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -1106,7 +1106,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="27" t="str">
-        <x:v>2026-09-09 (결정 C-1~C-29 반영)</x:v>
+        <x:v>2026-09-09 (결정 C-1~C-30 반영)</x:v>
       </x:c>
       <x:c r="C3" s="25"/>
       <x:c r="D3" s="25"/>
@@ -1134,7 +1134,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="26" t="str">
-        <x:v>기존 109건 + 청년정책 추천 7건 = 총 116건</x:v>
+        <x:v>기존 109건 + 청년정책 추천 6건 = 총 115건</x:v>
       </x:c>
       <x:c r="C5" s="25"/>
       <x:c r="D5" s="25"/>
@@ -1812,7 +1812,7 @@
         <x:v>정책 추천 조건</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>현재 상태·연소득 구간·가구 상태는 마이에서 원하는 사용자만 입력·저장. 관심 분야·주거 형태·평수 미수집(C-28)</x:v>
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 마이에서 입력·저장. 가구·혼인 상태·주거 형태·평수 미수집(C-30)</x:v>
       </x:c>
       <x:c r="C55" s="25"/>
       <x:c r="D55" s="25"/>
@@ -1840,7 +1840,7 @@
         <x:v>정책 동기화</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>온통청년 OPEN API를 100건 단위로 주기 동기화하고 사용자 조회는 로컬 DB 사용(C-24)</x:v>
+        <x:v>온통청년 API 전체 원본을 수집하되 승인·현재 신청 가능·개인 대상·분류·지역·신청 경로 검증을 통과한 정책만 활성화(C-30)</x:v>
       </x:c>
       <x:c r="C57" s="25"/>
       <x:c r="D57" s="25"/>
@@ -1854,7 +1854,7 @@
         <x:v>판정</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>생년월일·에코 연동 지역 등 구조화된 확실한 조건만 자동 판정. 자유 텍스트 조건은 확인 필요</x:v>
+        <x:v>구조화된 조건을 모두 충족한 ELIGIBLE 정책만 최대 5개 추천. 확인 필요·부적격 정책은 맞춤 추천에서 제외(C-30)</x:v>
       </x:c>
       <x:c r="C58" s="25"/>
       <x:c r="D58" s="25"/>
@@ -1868,7 +1868,7 @@
         <x:v>건수</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>기능 116건 유지, API는 온보딩 프로필 저장·수정 제거 후 69건</x:v>
+        <x:v>기능 115건, API는 상세 화면 임시 추천 API 제거 후 68건</x:v>
       </x:c>
       <x:c r="C59"/>
       <x:c r="D59"/>
@@ -1990,6 +1990,108 @@
       <x:c r="B74" t="str">
         <x:v>기존 청년정책 결정 C-22~C-28을 유지하고 진단 결정은 C-29로 기록</x:v>
       </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>ver3.8 변경 사항</x:v>
+      </x:c>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>변경 내용</x:v>
+      </x:c>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>활성 정책</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>승인 완료·현재 신청 가능·개인 대상 제공 방식·분류·지역·실제 신청 경로가 확인된 정책만 활성화(C-30)</x:v>
+      </x:c>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>추천 조건</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장. 가구·혼인 상태는 수집하지 않음(C-30)</x:v>
+      </x:c>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>저장 유지</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>저장된 선택값은 사용자가 MY-02에서 다시 저장할 때까지 유지. MY-06 상세 화면에서는 조건 변경·임시 재추천을 제공하지 않음(C-30)</x:v>
+      </x:c>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>추천 결과</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>ELIGIBLE 정책만 최대 5개 반환. CHECK_REQUIRED·NOT_ELIGIBLE은 맞춤 추천에서 제외(C-30)</x:v>
+      </x:c>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>전체 목록</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>엄격하게 선별된 활성 정책을 검색어·분야·지역으로 조회. 신청 상태 필터 제거(C-30)</x:v>
+      </x:c>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>결정 번호</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>청년정책 정밀 추천·활성 정책 선별을 C-30으로 기록</x:v>
+      </x:c>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3011,19 +3113,19 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G20" s="13" t="str">
-        <x:v>청년정책 추천을 원하는 사용자만 마이에서 현재 상태·연소득 구간·가구 상태를 각각 하나 선택한다. 관심 분야·주거 형태·평수는 받지 않는다.</x:v>
+        <x:v>청년정책 추천을 원하는 사용자만 마이에서 현재 상태·연소득 구간·학력을 각각 하나, 관심 분야를 1~2개 선택한다. 가구·혼인 상태·주거 형태·평수는 받지 않는다.</x:v>
       </x:c>
       <x:c r="H20" s="15" t="str">
-        <x:v>currentStatus, annualIncomeBand, householdStatus</x:v>
+        <x:v>currentStatus, annualIncomeBand, educationStatus, interestCategories(1~2개)</x:v>
       </x:c>
       <x:c r="I20" s="13" t="str">
         <x:v>로그인</x:v>
       </x:c>
       <x:c r="J20" s="13" t="str">
-        <x:v>필수값 누락·지원하지 않는 enum → 입력 오류</x:v>
+        <x:v>필수값 누락·관심 분야 0개 또는 3개 이상·중복·지원하지 않는 enum → 입력 오류</x:v>
       </x:c>
       <x:c r="K20" s="13" t="str">
-        <x:v>저장 전 임시 조건으로 추천을 미리 확인할 수 있다.</x:v>
+        <x:v>저장된 선택값이 다시 방문해도 유지되며, 사용자가 수정해 저장하기 전까지 추천 조건이 바뀌지 않는다.</x:v>
       </x:c>
       <x:c r="L20" s="8" t="str">
         <x:v>P0</x:v>
@@ -3035,10 +3137,10 @@
         <x:v>FE·BE</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>MY-02 · MY-06</x:v>
+        <x:v>MY-02</x:v>
       </x:c>
       <x:c r="P20" s="15" t="str">
-        <x:v>결정 C-28</x:v>
+        <x:v>결정 C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58.25" customHeight="1">
@@ -3061,7 +3163,7 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G21" s="13" t="str">
-        <x:v>마이에서 입력한 현재 상태·연소득 구간·가구 상태만 저장한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 읽기 전용으로 사용한다.</x:v>
+        <x:v>마이에서 입력한 현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장한다. 저장값은 사용자가 다시 저장할 때까지 유지한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 읽기 전용으로 사용한다.</x:v>
       </x:c>
       <x:c r="H21" s="15" t="str">
         <x:v>PUT /profile/policy-preferences</x:v>
@@ -3073,7 +3175,7 @@
         <x:v>필수값 누락 → 409</x:v>
       </x:c>
       <x:c r="K21" s="13" t="str">
-        <x:v>저장 후 마이 첫 화면에 추천 정책 최대 5개가 표시된다.</x:v>
+        <x:v>저장 후 마이 첫 화면에 적격 추천 정책 최대 5개가 표시된다.</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
         <x:v>P0</x:v>
@@ -3088,7 +3190,7 @@
         <x:v>MY-02 · MY-01</x:v>
       </x:c>
       <x:c r="P21" s="15" t="str">
-        <x:v>결정 C-28</x:v>
+        <x:v>결정 C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72.25" customHeight="1">
@@ -3138,7 +3240,7 @@
         <x:v>MY-01 · MY-02</x:v>
       </x:c>
       <x:c r="P22" s="13" t="str">
-        <x:v>결정 C-27·C-28</x:v>
+        <x:v>결정 C-27·C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58.25" customHeight="1">
@@ -3188,7 +3290,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P23" s="15" t="str">
-        <x:v>결정 C-26~C-28</x:v>
+        <x:v>결정 C-26~C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="86.5" customHeight="1">
@@ -7283,7 +7385,7 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G108" t="str">
-        <x:v>기존 보관함·연동·포켓 정보와 이름·생년월일·성별·휴대전화번호를 표시한다. 거주지역은 에코마일리지 등록 주소만 읽기 전용으로 표시한다. 첫 화면 하단에 맞춤 정책 추천 최대 5개를 둔다.</x:v>
+        <x:v>기존 보관함·연동·포켓 정보와 이름·생년월일·성별·휴대전화번호를 표시한다. 거주지역은 에코마일리지 등록 주소만 읽기 전용으로 표시한다. 월별 리포트·ECO 리포트 바로가기를 나를 위한 청년정책 위에 배치하고, 그 아래에 맞춤 정책 최대 5개를 둔다.</x:v>
       </x:c>
       <x:c r="H108" t="str">
         <x:v>profile{name,birthDate,gender,phoneNumber}, ecoAddress, policyRecommendationSummary.preview(최대 5)</x:v>
@@ -7310,7 +7412,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P108" t="str">
-        <x:v>정책 조건 미설정은 설정 CTA, 에코 미연동은 연동 CTA 표시(결정 C-26~C-28)</x:v>
+        <x:v>정책 조건 미설정은 설정 CTA, 에코 미연동은 연동 CTA 표시(결정 C-26~C-30)</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7479,7 +7581,7 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>가입 시 저장한 생년월일, 마이에서 저장한 현재 상태·연소득 구간·가구 상태, 에코 연동 주소로 정책을 정렬한다. 연령·지역처럼 구조화된 확실한 조건만 자동 판정하고 자유 텍스트 조건은 확인 필요로 표시한다.</x:v>
+        <x:v>가입 시 저장한 생년월일, 마이에서 저장한 현재 상태·연소득 구간·학력·관심 분야, 에코 연동 주소로 정책을 판정·정렬한다. 조건 코드 누락은 제한 없음이 아니라 확인 필요로 보고, 대출·보증·보험처럼 별도 심사가 필요한 정책도 CHECK_REQUIRED로 분류한다. 구조화 조건을 모두 명확히 충족한 ELIGIBLE 정책만 추천하며 관심 분야는 우선순위에 반영한다.</x:v>
       </x:c>
       <x:c r="H112" t="str">
         <x:v>GET /policies/recommendations</x:v>
@@ -7491,7 +7593,7 @@
         <x:v>조건 미설정 → 설정 CTA, 에코 미연동 → 전국 정책+연동 CTA, 데이터 없음 → 준비 중</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>마이 첫 화면에는 상위 5개, 전체 화면에는 동일 기준 전체 결과를 반환한다.</x:v>
+        <x:v>마이 첫 화면과 추천 결과 화면 모두 명확히 적격인 정책을 최대 5개만 반환한다. 5개 미만이어도 불확실한 정책으로 채우지 않는다.</x:v>
       </x:c>
       <x:c r="L112" t="str">
         <x:v>P0</x:v>
@@ -7506,7 +7608,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P112" t="str">
-        <x:v>결정 C-28</x:v>
+        <x:v>결정 C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7529,10 +7631,10 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G113" t="str">
-        <x:v>전체 정책을 검색어·분야·지역·신청 상태로 필터링하고 0-base 페이징한다.</x:v>
+        <x:v>승인 완료·현재 신청 가능·개인 대상·신청 경로가 명확한 활성 정책을 검색어·정책 분야·지역으로 필터링한다. 전체 정책은 한 페이지에 6개씩 표시하고 이전·페이지 번호·다음으로 이동한다. 정책 분야 필터는 목록만 바꾸며 저장된 관심 분야는 바꾸지 않는다.</x:v>
       </x:c>
       <x:c r="H113" t="str">
-        <x:v>GET /policies</x:v>
+        <x:v>GET /policies?keyword&amp;category&amp;regionCode&amp;page&amp;size</x:v>
       </x:c>
       <x:c r="I113" t="str">
         <x:v>정책 동기화 데이터 존재</x:v>
@@ -7541,7 +7643,7 @@
         <x:v>데이터 없음 → 준비 중</x:v>
       </x:c>
       <x:c r="K113" t="str">
-        <x:v>필터·페이징 경계와 최신 동기화 시각을 반환한다.</x:v>
+        <x:v>필터 적용 결과가 페이지당 6개씩 표시되고 번호 버튼으로 이동한다. 최신 동기화 시각을 확인할 수 있다.</x:v>
       </x:c>
       <x:c r="L113" t="str">
         <x:v>P0</x:v>
@@ -7555,7 +7657,9 @@
       <x:c r="O113" t="str">
         <x:v>MY-05</x:v>
       </x:c>
-      <x:c r="P113" t="str"/>
+      <x:c r="P113" t="str">
+        <x:v>결정 C-30</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="n">
@@ -7577,7 +7681,7 @@
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G114" t="str">
-        <x:v>지원 내용·신청 기간·대상 조건·신청 방법·기관·링크와 현재 사용자 기준 조건별 판정 사유를 제공한다. 자격을 확정 표현하지 않는다.</x:v>
+        <x:v>지원 내용·신청 기간·대상 조건·신청 방법·기관·링크와 현재 사용자 기준 조건별 판정 사유를 제공한다. 상시 신청 정책은 기간을 '상시 신청'으로 표시한다. 명시적 무제한 공통코드만 '제한 없음'으로 표시하고 누락 코드는 세부 조건 확인으로 표시한다. 구조화된 연소득 범위는 구체적인 금액으로 표시하며, 대출·보증·보험형 정책은 취업·학업·심사 조건 확인과 CHECK_REQUIRED 사유를 표시한다. 자격을 확정 표현하지 않는다.</x:v>
       </x:c>
       <x:c r="H114" t="str">
         <x:v>GET /policies/{policyId}</x:v>
@@ -7589,7 +7693,7 @@
         <x:v>없는 정책 → 404</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>상세 내용과 충족·불충족·확인 필요 사유를 확인할 수 있다.</x:v>
+        <x:v>상세 화면에서 상시 신청·명시적 제한 없음·누락 또는 심사 필요 조건이 구분되고, 연소득 범위와 충족·불충족·확인 필요 사유를 확인할 수 있다.</x:v>
       </x:c>
       <x:c r="L114" t="str">
         <x:v>P0</x:v>
@@ -7619,25 +7723,25 @@
         <x:v>E-3-04</x:v>
       </x:c>
       <x:c r="E115" t="str">
-        <x:v>임시 조건 다시 추천</x:v>
+        <x:v>정책 추천 조건 저장</x:v>
       </x:c>
       <x:c r="F115" t="str">
         <x:v>사용자</x:v>
       </x:c>
       <x:c r="G115" t="str">
-        <x:v>마이 상세 화면에서 현재 상태·연소득 구간·가구 상태만 바꿔 추천을 다시 계산한다. 가입 생년월일과 에코 연동 주소는 읽기 전용이며 저장된 사용자 정보는 변경하지 않는다.</x:v>
+        <x:v>MY-02에서 현재 상태·연소득 구간·학력·관심 분야를 저장한다. 저장값은 사용자가 다시 저장할 때까지 유지한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 사용하며 MY-06 상세 화면에서는 조건을 변경하지 않는다.</x:v>
       </x:c>
       <x:c r="H115" t="str">
-        <x:v>POST /policies/recommendations/preview</x:v>
+        <x:v>GET/PUT /profile/policy-preferences</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>로그인, 정책 동기화 데이터 존재</x:v>
+        <x:v>로그인</x:v>
       </x:c>
       <x:c r="J115" t="str">
-        <x:v>잘못된 조건 → 400</x:v>
+        <x:v>필수값 누락·관심 분야 개수 또는 중복 오류 → 400 또는 409</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>요청 전후 저장 프로필이 동일하고 임시 조건만 결과에 반영된다.</x:v>
+        <x:v>저장 후 마이 첫 화면의 적격 추천 최대 5개가 새 조건으로 갱신된다.</x:v>
       </x:c>
       <x:c r="L115" t="str">
         <x:v>P0</x:v>
@@ -7649,10 +7753,10 @@
         <x:v>FE·BE</x:v>
       </x:c>
       <x:c r="O115" t="str">
-        <x:v>MY-06</x:v>
+        <x:v>MY-02</x:v>
       </x:c>
       <x:c r="P115" t="str">
-        <x:v>결정 C-28</x:v>
+        <x:v>결정 C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -7669,25 +7773,25 @@
         <x:v>E-3-05</x:v>
       </x:c>
       <x:c r="E116" t="str">
-        <x:v>정책 추천 조건 저장</x:v>
+        <x:v>온통청년 정책 동기화</x:v>
       </x:c>
       <x:c r="F116" t="str">
-        <x:v>사용자</x:v>
+        <x:v>시스템</x:v>
       </x:c>
       <x:c r="G116" t="str">
-        <x:v>내 정보에 저장을 선택했을 때만 현재 상태·연소득 구간·가구 상태를 갱신한다. 생년월일은 가입 정보, 지역은 에코 연동 주소를 사용한다.</x:v>
+        <x:v>온통청년 정책 API를 최대 100건 단위로 전 페이지 조회하되 승인 완료·현재 신청 가능·개인 대상 제공 방식·분류·지역·신청 경로 검증을 통과한 정책만 외부 정책 ID 기준 활성 upsert한다. 조건 공통코드와 수치 범위를 원문대로 저장하며 누락 값을 제한 없음 코드로 보정하지 않는다. 장애·인증 실패 시 마지막 정상 데이터를 유지한다.</x:v>
       </x:c>
       <x:c r="H116" t="str">
-        <x:v>GET/PUT /profile/policy-preferences</x:v>
+        <x:v>youth_policy, youth_policy_region, youth_policy_condition, youth_policy_sync</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>로그인</x:v>
+        <x:v>API 인증키 환경변수 존재</x:v>
       </x:c>
       <x:c r="J116" t="str">
-        <x:v>필수값 누락·지원하지 않는 enum → 400 또는 409</x:v>
+        <x:v>403·타임아웃·잘못된 응답 → 실패 기록, 기존 정책 유지</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>저장 후 마이 첫 화면의 상위 5개 추천이 새 조건으로 갱신된다.</x:v>
+        <x:v>재실행해도 중복 없이 엄격 선별된 활성 정책만 갱신되고 인증키가 저장소·로그에 노출되지 않는다.</x:v>
       </x:c>
       <x:c r="L116" t="str">
         <x:v>P0</x:v>
@@ -7696,64 +7800,32 @@
         <x:v>개발</x:v>
       </x:c>
       <x:c r="N116" t="str">
-        <x:v>FE·BE</x:v>
+        <x:v>BE</x:v>
       </x:c>
       <x:c r="O116" t="str">
-        <x:v>MY-06</x:v>
+        <x:v>화면 없음</x:v>
       </x:c>
       <x:c r="P116" t="str">
-        <x:v>결정 C-28</x:v>
+        <x:v>결정 C-24·C-30</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" t="n">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B117" t="str">
-        <x:v>E. 마이</x:v>
-      </x:c>
-      <x:c r="C117" t="str">
-        <x:v>E-3. 청년지원정책 추천</x:v>
-      </x:c>
-      <x:c r="D117" t="str">
-        <x:v>E-3-06</x:v>
-      </x:c>
-      <x:c r="E117" t="str">
-        <x:v>온통청년 정책 동기화</x:v>
-      </x:c>
-      <x:c r="F117" t="str">
-        <x:v>시스템</x:v>
-      </x:c>
-      <x:c r="G117" t="str">
-        <x:v>온통청년 정책 API를 최대 100건 단위로 전 페이지 조회해 외부 정책 ID 기준 upsert한다. 장애·인증 실패 시 마지막 정상 데이터를 유지한다.</x:v>
-      </x:c>
-      <x:c r="H117" t="str">
-        <x:v>youth_policy, youth_policy_region, youth_policy_condition, youth_policy_sync</x:v>
-      </x:c>
-      <x:c r="I117" t="str">
-        <x:v>API 인증키 환경변수 존재</x:v>
-      </x:c>
-      <x:c r="J117" t="str">
-        <x:v>403·타임아웃·잘못된 응답 → 실패 기록, 기존 정책 유지</x:v>
-      </x:c>
-      <x:c r="K117" t="str">
-        <x:v>재실행해도 중복 없이 갱신되고 인증키가 저장소·로그에 노출되지 않는다.</x:v>
-      </x:c>
-      <x:c r="L117" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="M117" t="str">
-        <x:v>개발</x:v>
-      </x:c>
-      <x:c r="N117" t="str">
-        <x:v>BE</x:v>
-      </x:c>
-      <x:c r="O117" t="str">
-        <x:v>화면 없음</x:v>
-      </x:c>
-      <x:c r="P117" t="str">
-        <x:v>결정 C-24</x:v>
-      </x:c>
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
+      <x:c r="I117"/>
+      <x:c r="J117"/>
+      <x:c r="K117"/>
+      <x:c r="L117"/>
+      <x:c r="M117"/>
+      <x:c r="N117"/>
+      <x:c r="O117"/>
+      <x:c r="P117"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L2:L106">
@@ -7902,7 +7974,7 @@
         <x:v>시드 데이터 모의. 단, 온통청년 청년정책 API는 C-24에 따라 실연동</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>COM-12, E-3-06</x:v>
+        <x:v>COM-12, E-3-05</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
@@ -8308,7 +8380,7 @@
         <x:v>마이페이지를 마이로 바꾸고 기존 정보 아래에 맞춤 추천·전체 목록·상세를 제공. 신청 대행·자격 확정 제외</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>COM-02, E-1-01, E-3-01~05</x:v>
+        <x:v>COM-02, E-1-01, E-3-01~04</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -8336,7 +8408,7 @@
         <x:v>온통청년 OPEN API를 100건 단위로 주기 동기화하고 사용자 조회는 로컬 DB 사용. 인증키 저장소·로그 노출 금지</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>COM-12, E-3-06</x:v>
+        <x:v>COM-12, E-3-05</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -8350,7 +8422,7 @@
         <x:v>에코 연동 주소를 단일 지역 기준으로 사용. 미연동은 전국 정책만 추천. 자유 텍스트 조건은 확인 필요</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>A-1-01, E-3-01~05</x:v>
+        <x:v>A-1-01, E-3-01~04</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -8389,10 +8461,10 @@
         <x:v>마이 선택형 정책 추천</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>현재 상태·연소득 구간·가구 상태는 마이에서 원하는 사용자만 저장한다. 관심 분야는 받지 않는다. 마이 첫 화면에는 상위 5개, 상세에서는 전체 목록·임시 조건 재추천을 제공한다.</x:v>
+        <x:v>당시 현재 상태·연소득 구간·가구 상태를 마이에서 저장하고 상세에서 임시 재추천하기로 했다. 입력 조건과 상세 화면 재추천 방식은 C-30에서 대체한다.</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>A-1-04~07, E-1-01, E-3-01~05</x:v>
+        <x:v>A-1-04~07, E-1-01, E-3-01~04</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -8407,6 +8479,20 @@
       </x:c>
       <x:c r="D45" t="str">
         <x:v>A-3-01~03, A-3-07~08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>C-30</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>청년정책 정밀 추천</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>승인 완료·현재 신청 가능·개인 대상·분류·지역·신청 경로가 명확한 정책만 활성화한다. 현재 상태·연소득·학력·관심 분야 1~2개를 MY-02에서 저장하며 가구·혼인 상태는 받지 않는다. 저장값은 다시 저장할 때까지 유지한다. 조건 코드 누락은 제한 없음으로 해석하지 않고, 대출·보증·보험처럼 별도 심사가 필요한 정책은 CHECK_REQUIRED로 분류한다. 명확히 ELIGIBLE인 정책만 최대 5개 추천하며 5개 미만이어도 불확실한 정책으로 채우지 않는다. MY-06은 상세 정보만 제공하며 조건 변경·임시 재추천을 제공하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>A-1-04~06, E-1-01, E-3-01~05</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8885,7 +8971,7 @@
         <x:v>마이페이지 image 464</x:v>
       </x:c>
       <x:c r="D38" s="15" t="str">
-        <x:v>기존 정보 아래 맞춤 청년정책 추천 영역 추가</x:v>
+        <x:v>기존 정보와 월별·ECO 리포트 바로가기를 먼저 표시하고, 그 아래에 맞춤 청년정책 Top 5 영역을 배치</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" customHeight="1">
@@ -8899,7 +8985,7 @@
         <x:v>신규 시안</x:v>
       </x:c>
       <x:c r="D39" s="15" t="str">
-        <x:v>현재 상태·연소득 구간·가구 상태 입력. 본인정보·에코 주소는 읽기 전용</x:v>
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개 입력. 저장값 유지. 본인정보·에코 주소는 읽기 전용</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -8937,7 +9023,7 @@
         <x:v>신규 시안</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>검색·필터·페이징</x:v>
+        <x:v>엄격 선별된 현재 신청 가능 정책을 검색·정책 분야·지역으로 필터링. 페이지당 6개, 이전·번호·다음 페이지 이동</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -8945,13 +9031,13 @@
         <x:v>MY-06</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>청년정책 상세·다시 추천</x:v>
+        <x:v>청년정책 상세</x:v>
       </x:c>
       <x:c r="C43" t="str">
         <x:v>신규 시안</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>임시 조건 추천과 내 정보 저장 분리</x:v>
+        <x:v>지원 내용·신청 안내·대상 조건·판정 근거·신청 링크를 표시. 상시 정책은 '상시 신청', 명시적 무제한 조건은 '제한 없음'으로 표시. 조건 수정·임시 재추천 기능 없음</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R1b4726e64e364656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rdf796f90828c4bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Reca09b1bc27644c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="R9b9b2fc593e2471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rd01a4a94e0364709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Raefe7a0d0cd24a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R348422822ca34b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R12c88dd9723e48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rb111e01e05164c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rb836685c682f4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rde1fa88d4c3042fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rca28ac9cb13e4a53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R43e9d5f662234f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rb3a00e0c19c34609"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -748,7 +748,7 @@
     <x:xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
@@ -831,6 +831,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="7">
@@ -993,9 +999,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1098,7 +1104,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>그린포켓 기능명세서 ver3.6</x:v>
+        <x:v>그린포켓 기능명세서 ver3.7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -1106,7 +1112,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="27" t="str">
-        <x:v>2026-09-09 (결정 C-1~C-29 반영)</x:v>
+        <x:v>2026-09-09 (결정 C-1~C-30 반영)</x:v>
       </x:c>
       <x:c r="C3" s="25"/>
       <x:c r="D3" s="25"/>
@@ -1990,6 +1996,95 @@
       <x:c r="B74" t="str">
         <x:v>기존 청년정책 결정 C-22~C-28을 유지하고 진단 결정은 C-29로 기록</x:v>
       </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>ver3.7 변경 사항</x:v>
+      </x:c>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>변경 내용</x:v>
+      </x:c>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+    </x:row>
+    <x:row r="78" ht="30" customHeight="1">
+      <x:c r="A78" t="str">
+        <x:v>월별 비교 자료</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>전기·도시가스는 KESIS 2023년 기준 14차 가구에너지패널조사 마이크로데이터를 가구 횡단가중치로 가중평균</x:v>
+      </x:c>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+    </x:row>
+    <x:row r="79" ht="30" customHeight="1">
+      <x:c r="A79" t="str">
+        <x:v>비교군</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>전기는 유효 가중치가 있는 전국 1인 가구 1,221가구, 도시가스는 연간 사용량이 있는 841가구 고정 비교군</x:v>
+      </x:c>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+    </x:row>
+    <x:row r="80" ht="30" customHeight="1">
+      <x:c r="A80" t="str">
+        <x:v>API 계약</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>API 수는 유지하고 GET /diagnosis의 항목별 응답에 선택 월까지 최근 6개월 series를 추가</x:v>
+      </x:c>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+    </x:row>
+    <x:row r="81" ht="30" customHeight="1">
+      <x:c r="A81" t="str">
+        <x:v>결측 처리</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>사용자 고지서가 없는 월의 myUsage는 null로 제공하며 임의 보간하지 않음. 수도는 기존 일 사용량×월 일수 기준 유지</x:v>
+      </x:c>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+    </x:row>
+    <x:row r="82" ht="30" customHeight="1">
+      <x:c r="A82" t="str">
+        <x:v>결정 번호</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>C-30 월별 1인 가구 기준선과 최근 6개월 사용량 시계열 제공</x:v>
+      </x:c>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3819,7 +3914,7 @@
         <x:v>시안 없음 — AN-05 폼 재사용 고지서 묶음(upload_batch_id)과 수정 이력은 관리하지 않는다. 조회·수정·삭제는 레코드 단위이고 updated_at 만 갱신한다(결정 C-3).</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="58.25" customHeight="1">
+    <x:row r="37" ht="95" customHeight="1">
       <x:c r="A37" s="8" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -3839,19 +3934,19 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G37" s="15" t="str">
-        <x:v>전기·도시가스는 KESIS 2022년 전국 1인 가구 연간 에너지소비량·에너지원 비중을 사용량 월평균으로 환산하고, 수도는 서울시 2018년 아파트 1인 가구의 하루 438L를 조회 월 일수에 맞춰 환산한다. 런타임에는 검증된 JSON 스냅샷을 읽는다.</x:v>
+        <x:v>전기·도시가스는 KESIS 2023년 기준 14차 가구에너지패널조사 마이크로데이터에서 1인 가구를 선별하고 가구 횡단가중치로 월별 사용량 추정평균을 산출한다. 전기는 유효 가중치 1인 가구 1,221가구, 도시가스는 연간 사용량이 있는 841가구 고정 비교군의 월별 0 사용량을 포함한다. 수도는 서울시 2018년 아파트 1인 가구의 하루 438L를 조회 월 일수에 맞춰 환산한다. 런타임에는 검증된 JSON 스냅샷을 읽는다.</x:v>
       </x:c>
       <x:c r="H37" s="15" t="str">
-        <x:v>single_household_baseline{utilityType, averageUsage, usageUnit, sourceName, referencePeriod, calculationBasis, note}</x:v>
+        <x:v>single_household_baseline{utilityType, monthlyAverageUsage[12], usageUnit, sourceName, referencePeriod, calculationBasis, note}</x:v>
       </x:c>
       <x:c r="I37" s="13" t="str">
         <x:v>공식 공개 집계와 환산 기준</x:v>
       </x:c>
       <x:c r="J37" s="13" t="str">
-        <x:v>월별 실측 또는 전체 주거유형 자료가 없으면 한계를 함께 제공</x:v>
+        <x:v>월별 원자료 또는 비교 기준이 없으면 임의 값을 만들지 않고 한계를 함께 제공</x:v>
       </x:c>
       <x:c r="K37" s="13" t="str">
-        <x:v>전기·수도·도시가스 기준값과 출처·기준 기간·환산 방식이 함께 제공된다.</x:v>
+        <x:v>전기·수도·도시가스 기준값과 출처·기준 기간·가중평균/환산 방식이 함께 제공된다.</x:v>
       </x:c>
       <x:c r="L37" s="8" t="str">
         <x:v>P0</x:v>
@@ -3866,10 +3961,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="P37" s="13" t="str">
-        <x:v>전기·도시가스는 계절별 월 실측이 아닌 연간 집계의 월평균 환산값이며, 수도는 서울 아파트 표본이다(C-29).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="44" customHeight="1">
+        <x:v>전기·도시가스는 실제 월별 계절성을 반영하고, 수도는 서울 아파트 표본을 월 일수로 환산한다(C-30).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="62" customHeight="1">
       <x:c r="A38" s="8" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -3889,7 +3984,7 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G38" s="13" t="str">
-        <x:v>청구 월과 에너지원에 맞는 1인 가구 평균 사용량을 조회한다. 수도는 조회 월의 실제 일수로 환산하고, 전기·도시가스는 연간 집계의 월평균 환산값을 사용한다.</x:v>
+        <x:v>청구 월과 에너지원에 맞는 1인 가구 평균 사용량을 조회한다. 전기·도시가스는 요청 월과 같은 달의 KESIS 가중평균을 사용하고, 수도는 조회 월의 실제 일수로 환산한다.</x:v>
       </x:c>
       <x:c r="H38" s="15" t="str">
         <x:v>GET /diagnosis/baseline?month&amp;utility</x:v>
@@ -3901,7 +3996,7 @@
         <x:v>기준 없음 → A-3-03</x:v>
       </x:c>
       <x:c r="K38" s="13" t="str">
-        <x:v>동일 월·에너지원에 동일 기준선이 반환되고 수도는 월 일수에 따라 달라진다.</x:v>
+        <x:v>동일 월·에너지원에 동일 기준선이 반환되고 전기·도시가스는 달별 평균, 수도는 월 일수에 따라 달라진다.</x:v>
       </x:c>
       <x:c r="L38" s="8" t="str">
         <x:v>P0</x:v>
@@ -4111,7 +4206,7 @@
         <x:v>작년 값 = 에코마일리지 연동값</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="35" customHeight="1">
+    <x:row r="43" ht="95" customHeight="1">
       <x:c r="A43" s="8" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -4131,10 +4226,10 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G43" s="13" t="str">
-        <x:v>항목 탭(전기·수도·도시가스)별로 이번 달 내 사용량, 1인 가구 평균 사용량, 사용량 차이와 차이율을 보여준다. 비교군·기준 연도·출처와 월평균/일수 환산 방식, 자료의 한계를 함께 표시한다.</x:v>
+        <x:v>항목 탭(전기·수도·도시가스)별로 이번 달 내 사용량, 1인 가구 평균 사용량, 사용량 차이와 차이율을 보여준다. 선택 월까지 최근 6개월의 내 사용량과 평균 사용량 시계열을 꺾은선 그래프로 표시한다. 내 고지서가 없는 달은 값을 보간하지 않는다. 비교군·기준 연도·출처와 가중평균/일수 환산 방식, 자료의 한계를 함께 표시한다.</x:v>
       </x:c>
       <x:c r="H43" s="15" t="str">
-        <x:v>singleHouseholdComparison.tabs[]{myUsage, averageUsage, differenceUsage, differenceRate, usageUnit, comparisonLabel, sourceName, referencePeriod, calculationBasis, note}</x:v>
+        <x:v>singleHouseholdComparison.tabs[]{myUsage, averageUsage, differenceUsage, differenceRate, usageUnit, comparisonLabel, sourceName, referencePeriod, calculationBasis, note, series[]{yearMonth, myUsage, averageUsage}}</x:v>
       </x:c>
       <x:c r="I43" s="13" t="str">
         <x:v>기준선 존재</x:v>
@@ -4143,7 +4238,7 @@
         <x:v>기준 없음 → 비교 데이터 준비 중</x:v>
       </x:c>
       <x:c r="K43" s="13" t="str">
-        <x:v>세 항목의 사용량 차이·차이율과 비교 근거가 함께 표시된다.</x:v>
+        <x:v>세 항목의 선택 월 사용량 차이·차이율, 최근 6개월 시계열과 비교 근거가 함께 표시된다.</x:v>
       </x:c>
       <x:c r="L43" s="8" t="str">
         <x:v>P0</x:v>
@@ -4158,7 +4253,7 @@
         <x:v>AN-07</x:v>
       </x:c>
       <x:c r="P43" s="13" t="str">
-        <x:v>지역 평균 6개월 라인 차트를 1인 가구 사용량 비교 카드로 교체(C-29)</x:v>
+        <x:v>최근 6개월 1인 가구 평균 사용량 라인 차트를 제공한다. 사용자 결측 월은 선을 연결하지 않는다(C-30).</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58.25" customHeight="1">
@@ -8409,6 +8504,20 @@
         <x:v>A-3-01~03, A-3-07~08</x:v>
       </x:c>
     </x:row>
+    <x:row r="46" ht="82" customHeight="1">
+      <x:c r="A46" s="36" t="str">
+        <x:v>C-30</x:v>
+      </x:c>
+      <x:c r="B46" s="36" t="str">
+        <x:v>진단 월별 1인 가구 기준선</x:v>
+      </x:c>
+      <x:c r="C46" s="36" t="str">
+        <x:v>전기·가스는 KESIS 2023년 기준 14차 가구에너지패널조사 마이크로데이터에서 1인 가구를 선별해 가구 횡단가중치로 월별 평균을 산출한다. 전기는 유효 가중치 1,221가구, 가스는 연간 사용량이 있는 841가구 고정 비교군이며 월별 0 사용량을 포함한다. GET /diagnosis는 선택 월까지 최근 6개월의 내 사용량과 평균 시계열을 제공하고 사용자 결측 월은 null로 둔다. 수도는 기존 일 사용량 월환산을 유지한다.</x:v>
+      </x:c>
+      <x:c r="D46" s="36" t="str">
+        <x:v>A-3-01~03, A-3-07~08</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9305,7 +9414,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
-        <x:v>진단은 1인 가구 평균 사용량(+작년 동월), What-if는 에코마일리지 규칙대로 직전 2년 같은 기간 평균. 개인 과거 이력은 에코마일리지 연동값에 한해 사용한다.</x:v>
+        <x:v>진단은 1인 가구 평균 사용량(+작년 동월), What-if는 에코마일리지 규칙대로 직전 2년 같은 기간 평균. 진단의 전기·가스는 KESIS 월별 가중평균, 수도는 일 사용량 월환산을 쓰며 개인 과거 이력은 에코마일리지 연동값에 한해 사용한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -9681,7 +9790,7 @@
         <x:v>169</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" customHeight="1">
+    <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" s="8">
         <x:v>3</x:v>
       </x:c>
@@ -9698,7 +9807,7 @@
         <x:v>KESIS 사용 목적 설문 후 다운로드</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
-        <x:v>2026-09-08 공개 집계의 월평균 환산값 적용. 월별 마이크로데이터 확보 시 JSON 교체 예정(결정 C-29)</x:v>
+        <x:v>2026-09-09 KESIS 2023년 기준 14차 마이크로데이터 확보·검증 완료. 전기 1,221가구, 도시가스 841가구를 가구 횡단가중치로 월별 평균 산출해 적용(결정 C-30)</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R9907d626739e4f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rce65fdbbb5234a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rbab0647f69124573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Re87c7e0d4a0d46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Ref539e70eeb74d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rbded3fdf4c9c4889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R1c125d06548d4336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R27d43734a2ee480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R73662ca8b3074fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rc4137cefec2e4b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Rbce8660408344a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="R6f7809156a0d4de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="R6a676f73a5854a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R452b0f7e1c03436b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2033,7 +2033,7 @@
         <x:v>추천 조건</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장. 가구·혼인 상태는 수집하지 않음(C-30)</x:v>
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장. 가구·혼인 상태는 수집하지 않음(C-33)</x:v>
       </x:c>
       <x:c r="C78"/>
       <x:c r="D78"/>
@@ -2046,7 +2046,7 @@
         <x:v>저장 유지</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>저장된 선택값은 사용자가 MY-02에서 다시 저장할 때까지 유지. MY-06 상세 화면에서는 조건 변경·임시 재추천을 제공하지 않음(C-30)</x:v>
+        <x:v>저장된 선택값은 사용자가 MY-02에서 다시 저장할 때까지 유지. MY-06 상세 화면에서는 조건 변경·임시 재추천을 제공하지 않음(C-33)</x:v>
       </x:c>
       <x:c r="C79"/>
       <x:c r="D79"/>
@@ -2059,7 +2059,7 @@
         <x:v>추천 결과</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>ELIGIBLE 정책만 최대 5개 반환. CHECK_REQUIRED·NOT_ELIGIBLE은 맞춤 추천에서 제외(C-30)</x:v>
+        <x:v>ELIGIBLE 정책만 최대 5개 반환. CHECK_REQUIRED·NOT_ELIGIBLE은 맞춤 추천에서 제외(C-33)</x:v>
       </x:c>
       <x:c r="C80"/>
       <x:c r="D80"/>
@@ -2072,7 +2072,7 @@
         <x:v>전체 목록</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>엄격하게 선별된 활성 정책을 검색어·분야·지역으로 조회. 신청 상태 필터 제거(C-30)</x:v>
+        <x:v>엄격하게 선별된 활성 정책을 검색어·분야·지역으로 조회. 신청 상태 필터 제거(C-33)</x:v>
       </x:c>
       <x:c r="C81"/>
       <x:c r="D81"/>
@@ -2085,7 +2085,7 @@
         <x:v>결정 번호</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>청년정책 정밀 추천·활성 정책 선별을 C-30으로 기록</x:v>
+        <x:v>청년정책 정밀 추천은 C-33, 검증 정책 60건 운영은 C-35로 기록</x:v>
       </x:c>
       <x:c r="C82"/>
       <x:c r="D82"/>
@@ -8481,18 +8481,88 @@
         <x:v>A-3-01~03, A-3-07~08</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="14.5" hidden="0" customHeight="1">
       <x:c r="A46" t="str">
         <x:v>C-30</x:v>
       </x:c>
       <x:c r="B46" t="str">
+        <x:v>What-if 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>홈(WF-06)은 헤더(오늘 남은 실천 수·캐릭터) + 감축률 카드 + 오늘의 실천 두 카드로 구성한다. 감축률 카드의 구간은 지급 구간과 같은 4칸 바(0~5 / 5~10 / 10~15 / 15%+)이며 목표 칸을 마커로 표시한다. 전달 리포트·목표 카드는 홈에서 빼고 감축률 카드 하단 링크(월 리포트 → WF-07 · 내 목표 → WF-04)로 진입한다. 참여신청 배너는 홈에서 빼고 입구는 보류한다.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>B-4-01, B-4-03~06, B-3-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>C-31</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>포켓 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>포켓 홈(PK-01)은 헤더·잔액 카드·추천 상품 카드·최근 내역 카드 순으로 구성한다. 잔액 카드에는 전환 가능한 마일리지와 출금 신청 진입점을 두고, 계좌번호 전체 표시와 상세 안내는 관리·출금·전환 화면으로 분리한다.</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>D-1-04, D-1-06, D-4-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>C-32</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>혜택 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>혜택 홈(BN-01·BN-02)은 참여 상태별 헤드라인과 월 적립·실천 항목 카드를 제공한다. 미참여 사용자는 참여 방법과 대표 실천 항목을 보고 공식 누리집으로 이동한다. 기준 연도·최근 연동 시각·제도명은 상세(BN-03)에 둔다.</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>C-1-01~03, C-2-01~03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>C-33</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
         <x:v>청년정책 정밀 추천</x:v>
       </x:c>
-      <x:c r="C46" t="str">
-        <x:v>승인 완료·현재 신청 가능·개인 대상·분류·지역·신청 경로가 명확한 정책만 활성화한다. 현재 상태·연소득·학력·관심 분야 1~2개를 MY-02에서 저장하며 가구·혼인 상태는 받지 않는다. 저장값은 다시 저장할 때까지 유지한다. 조건 코드 누락은 제한 없음으로 해석하지 않고, 대출·보증·보험처럼 별도 심사가 필요한 정책은 CHECK_REQUIRED로 분류한다. 명확히 ELIGIBLE인 정책만 최대 5개 추천하며 5개 미만이어도 불확실한 정책으로 채우지 않는다. MY-06은 상세 정보만 제공하며 조건 변경·임시 재추천을 제공하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="C49" t="str">
+        <x:v>승인 완료·현재 신청 가능·개인 대상·분류·지역·신청 경로가 명확한 정책만 활성화한다. 현재 상태·연소득·학력·관심 분야 1~2개를 MY-02에서 저장하며 가구·혼인 상태는 받지 않는다. 저장값은 다시 저장할 때까지 유지한다. 조건 코드 누락은 제한 없음으로 해석하지 않고, 대출·보증·보험처럼 별도 심사가 필요한 정책은 CHECK_REQUIRED로 분류한다. 명확히 ELIGIBLE인 정책만 최대 5개 추천하며 MY-06은 상세 정보만 제공한다.</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
         <x:v>A-1-04~06, E-1-01, E-3-01~05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>C-34</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>미션 계절 노출 규칙</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>목표 정하기(WF-04·WF-08)는 오늘부터 회차 끝까지 남은 달의 계절과 하나라도 맞는 미션과 사계절 미션만 보여준다. 이미 고른 미션은 계절이 맞지 않아도 해제할 수 있게 표시한다. 오늘의 실천은 오늘 계절만 노출하고 현재 계절에 맞는 실천 수를 안내한다.</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>B-3-03, B-3-05, C-19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="14.5" hidden="0" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>C-35</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>검증 정책 60건 운영</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>온통청년 원본 전 페이지는 갱신 검증용으로만 수집하고 팀이 검증한 고정 정책 ID 60건만 운영 DB에 저장한다. 새 60건을 모두 수집·정규화한 뒤 한 트랜잭션에서 교체하고 미선정 정책과 하위 지역·조건 데이터는 삭제한다. 외부 동기화 실패 시 번들 스냅샷 또는 마지막 정상 60건을 유지한다.</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>COM-12, E-3-01~05</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/feature-spec/기능명세서.xlsx
+++ b/docs/feature-spec/기능명세서.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R9907d626739e4f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="Rce65fdbbb5234a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="Rbab0647f69124573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Re87c7e0d4a0d46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Ref539e70eeb74d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rbded3fdf4c9c4889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="R1c125d06548d4336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" r:id="R8beb71015a494762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세" sheetId="2" r:id="R567e4a9df96d452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정 사항" sheetId="3" r:id="R1558da68d1ed4a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="4" r:id="Re0a2685247034ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP 컷라인" sheetId="5" r:id="Rb9aa796e38a84c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비즈니스 규칙·계산식" sheetId="6" r:id="Rc886419bb9774d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인 필요 사항" sheetId="7" r:id="Rf10b9e144e5d40c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -993,9 +993,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1098,7 +1098,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.649999618530273" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>그린포켓 기능명세서 ver3.8</x:v>
+        <x:v>그린포켓 기능명세서 ver3.9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -1106,7 +1106,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="27" t="str">
-        <x:v>2026-09-09 (결정 C-1~C-30 반영)</x:v>
+        <x:v>2026-09-09 (결정 C-1~C-35 반영)</x:v>
       </x:c>
       <x:c r="C3" s="25"/>
       <x:c r="D3" s="25"/>
@@ -1812,7 +1812,7 @@
         <x:v>정책 추천 조건</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 마이에서 입력·저장. 가구·혼인 상태·주거 형태·평수 미수집(C-30)</x:v>
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 마이에서 입력·저장. 가구·혼인 상태·주거 형태·평수 미수집(C-33)</x:v>
       </x:c>
       <x:c r="C55" s="25"/>
       <x:c r="D55" s="25"/>
@@ -1840,7 +1840,7 @@
         <x:v>정책 동기화</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>온통청년 API 전체 원본을 수집하되 승인·현재 신청 가능·개인 대상·분류·지역·신청 경로 검증을 통과한 정책만 활성화(C-30)</x:v>
+        <x:v>온통청년 API 전체 원본을 수집하되 승인·현재 신청 가능·개인 대상·분류·지역·신청 경로 검증을 통과한 정책만 활성화(C-33)</x:v>
       </x:c>
       <x:c r="C57" s="25"/>
       <x:c r="D57" s="25"/>
@@ -1854,7 +1854,7 @@
         <x:v>판정</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>구조화된 조건을 모두 충족한 ELIGIBLE 정책만 최대 5개 추천. 확인 필요·부적격 정책은 맞춤 추천에서 제외(C-30)</x:v>
+        <x:v>구조화된 조건을 모두 충족한 ELIGIBLE 정책만 최대 5개 추천. 확인 필요·부적격 정책은 맞춤 추천에서 제외(C-33)</x:v>
       </x:c>
       <x:c r="C58" s="25"/>
       <x:c r="D58" s="25"/>
@@ -2020,7 +2020,7 @@
         <x:v>활성 정책</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>승인 완료·현재 신청 가능·개인 대상 제공 방식·분류·지역·실제 신청 경로가 확인된 정책만 활성화(C-30)</x:v>
+        <x:v>승인 완료·현재 신청 가능·개인 대상 제공 방식·분류·지역·실제 신청 경로가 확인된 정책만 활성화(C-33)</x:v>
       </x:c>
       <x:c r="C77"/>
       <x:c r="D77"/>
@@ -2033,7 +2033,7 @@
         <x:v>추천 조건</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장. 가구·혼인 상태는 수집하지 않음(C-30)</x:v>
+        <x:v>현재 상태·연소득 구간·학력·관심 분야 1~2개를 저장. 가구·혼인 상태는 수집하지 않음(C-33)</x:v>
       </x:c>
       <x:c r="C78"/>
       <x:c r="D78"/>
@@ -2046,7 +2046,7 @@
         <x:v>저장 유지</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>저장된 선택값은 사용자가 MY-02에서 다시 저장할 때까지 유지. MY-06 상세 화면에서는 조건 변경·임시 재추천을 제공하지 않음(C-30)</x:v>
+        <x:v>저장된 선택값은 사용자가 MY-02에서 다시 저장할 때까지 유지. MY-06 상세 화면에서는 조건 변경·임시 재추천을 제공하지 않음(C-33)</x:v>
       </x:c>
       <x:c r="C79"/>
       <x:c r="D79"/>
@@ -2059,7 +2059,7 @@
         <x:v>추천 결과</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>ELIGIBLE 정책만 최대 5개 반환. CHECK_REQUIRED·NOT_ELIGIBLE은 맞춤 추천에서 제외(C-30)</x:v>
+        <x:v>ELIGIBLE 정책만 최대 5개 반환. CHECK_REQUIRED·NOT_ELIGIBLE은 맞춤 추천에서 제외(C-33)</x:v>
       </x:c>
       <x:c r="C80"/>
       <x:c r="D80"/>
@@ -2072,7 +2072,7 @@
         <x:v>전체 목록</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>엄격하게 선별된 활성 정책을 검색어·분야·지역으로 조회. 신청 상태 필터 제거(C-30)</x:v>
+        <x:v>엄격하게 선별된 활성 정책을 검색어·분야·지역으로 조회. 신청 상태 필터 제거(C-33)</x:v>
       </x:c>
       <x:c r="C81"/>
       <x:c r="D81"/>
@@ -2085,13 +2085,89 @@
         <x:v>결정 번호</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>청년정책 정밀 추천·활성 정책 선별을 C-30으로 기록</x:v>
+        <x:v>청년정책 정밀 추천·활성 정책 선별을 C-33으로 기록</x:v>
       </x:c>
       <x:c r="C82"/>
       <x:c r="D82"/>
       <x:c r="E82"/>
       <x:c r="F82"/>
       <x:c r="G82"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>ver3.9 변경 사항</x:v>
+      </x:c>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>변경 내용</x:v>
+      </x:c>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>결정</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>C-34 미션 계절 노출 규칙과 C-35 진단 월별 1인 가구 기준선을 반영</x:v>
+      </x:c>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>진단 자료</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>KESIS 2023년 기준 14차 마이크로데이터에서 전기 1,221가구·도시가스 841가구의 월별 가구 횡단가중 평균 산출</x:v>
+      </x:c>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>진단 API</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>GET /diagnosis에 선택 월까지 최근 6개월의 내 사용량·평균 사용량 시계열 추가. 사용자 결측 월은 null로 유지</x:v>
+      </x:c>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+      <x:c r="G88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>유지</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>수도는 서울 아파트 1인 가구 하루 438L의 월 일수 환산값 유지. DB와 API 개수는 변경 없음</x:v>
+      </x:c>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3140,7 +3216,7 @@
         <x:v>MY-02</x:v>
       </x:c>
       <x:c r="P20" s="15" t="str">
-        <x:v>결정 C-30</x:v>
+        <x:v>결정 C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58.25" customHeight="1">
@@ -3190,7 +3266,7 @@
         <x:v>MY-02 · MY-01</x:v>
       </x:c>
       <x:c r="P21" s="15" t="str">
-        <x:v>결정 C-30</x:v>
+        <x:v>결정 C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72.25" customHeight="1">
@@ -3240,7 +3316,7 @@
         <x:v>MY-01 · MY-02</x:v>
       </x:c>
       <x:c r="P22" s="13" t="str">
-        <x:v>결정 C-27·C-30</x:v>
+        <x:v>결정 C-27·C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58.25" customHeight="1">
@@ -3290,7 +3366,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P23" s="15" t="str">
-        <x:v>결정 C-26~C-30</x:v>
+        <x:v>결정 C-26~C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="86.5" customHeight="1">
@@ -3941,19 +4017,19 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G37" s="15" t="str">
-        <x:v>전기·도시가스는 KESIS 2022년 전국 1인 가구 연간 에너지소비량·에너지원 비중을 사용량 월평균으로 환산하고, 수도는 서울시 2018년 아파트 1인 가구의 하루 438L를 조회 월 일수에 맞춰 환산한다. 런타임에는 검증된 JSON 스냅샷을 읽는다.</x:v>
+        <x:v>전기·도시가스는 KESIS 2023년 기준 14차 가구에너지패널조사 마이크로데이터에서 1인 가구를 선별하고 가구 횡단가중치로 월별 사용량 추정평균을 산출한다. 전기는 유효 가중치 1인 가구 1,221가구, 도시가스는 연간 사용량이 있는 841가구 고정 비교군의 월별 0 사용량을 포함한다. 수도는 서울시 2018년 아파트 1인 가구의 하루 438L를 조회 월 일수에 맞춰 환산한다. 런타임에는 검증된 JSON 스냅샷을 읽는다.</x:v>
       </x:c>
       <x:c r="H37" s="15" t="str">
-        <x:v>single_household_baseline{utilityType, averageUsage, usageUnit, sourceName, referencePeriod, calculationBasis, note}</x:v>
+        <x:v>singleHouseholdBaseline{utilityType, monthlyAverageUsage[12], comparisonLabel, averageUsage, usageUnit, sourceName, referencePeriod, calculationBasis, note}</x:v>
       </x:c>
       <x:c r="I37" s="13" t="str">
-        <x:v>공식 공개 집계와 환산 기준</x:v>
+        <x:v>공식 원자료 변수·가중치·표본 조건 검증</x:v>
       </x:c>
       <x:c r="J37" s="13" t="str">
-        <x:v>월별 실측 또는 전체 주거유형 자료가 없으면 한계를 함께 제공</x:v>
+        <x:v>기준 데이터 누락·파싱 실패 → 애플리케이션 기동 실패, 특정 항목 기준 부재 → A-3-03</x:v>
       </x:c>
       <x:c r="K37" s="13" t="str">
-        <x:v>전기·수도·도시가스 기준값과 출처·기준 기간·환산 방식이 함께 제공된다.</x:v>
+        <x:v>모든 값에 비교군·출처·기준 연도·환산 방식·자료 한계가 함께 제공된다.</x:v>
       </x:c>
       <x:c r="L37" s="8" t="str">
         <x:v>P0</x:v>
@@ -3968,7 +4044,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="P37" s="13" t="str">
-        <x:v>전기·도시가스는 계절별 월 실측이 아닌 연간 집계의 월평균 환산값이며, 수도는 서울 아파트 표본이다(C-29).</x:v>
+        <x:v>전기·도시가스는 실제 월별 계절성을 반영하고, 수도는 서울 아파트 표본을 월 일수로 환산한다(C-35).</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="44" customHeight="1">
@@ -3991,7 +4067,7 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G38" s="13" t="str">
-        <x:v>청구 월과 에너지원에 맞는 1인 가구 평균 사용량을 조회한다. 수도는 조회 월의 실제 일수로 환산하고, 전기·도시가스는 연간 집계의 월평균 환산값을 사용한다.</x:v>
+        <x:v>청구 월과 에너지원에 맞는 1인 가구 평균 사용량을 조회한다. 전기·도시가스는 요청 월과 같은 달의 KESIS 가중평균을 사용하고, 수도는 조회 월의 실제 일수로 환산한다.</x:v>
       </x:c>
       <x:c r="H38" s="15" t="str">
         <x:v>GET /diagnosis/baseline?month&amp;utility</x:v>
@@ -4000,10 +4076,10 @@
         <x:v>1인 가구 기준 JSON</x:v>
       </x:c>
       <x:c r="J38" s="13" t="str">
-        <x:v>기준 없음 → A-3-03</x:v>
+        <x:v>해당 에너지원 기준 없음 → A-3-03</x:v>
       </x:c>
       <x:c r="K38" s="13" t="str">
-        <x:v>동일 월·에너지원에 동일 기준선이 반환되고 수도는 월 일수에 따라 달라진다.</x:v>
+        <x:v>동일 월·에너지원에 동일 기준선이 반환되고 전기·도시가스는 달별 평균, 수도는 월 일수에 따라 달라진다.</x:v>
       </x:c>
       <x:c r="L38" s="8" t="str">
         <x:v>P0</x:v>
@@ -4233,19 +4309,19 @@
         <x:v>시스템</x:v>
       </x:c>
       <x:c r="G43" s="13" t="str">
-        <x:v>항목 탭(전기·수도·도시가스)별로 이번 달 내 사용량, 1인 가구 평균 사용량, 사용량 차이와 차이율을 보여준다. 비교군·기준 연도·출처와 월평균/일수 환산 방식, 자료의 한계를 함께 표시한다.</x:v>
+        <x:v>항목 탭(전기·수도·도시가스)별로 이번 달 내 사용량, 1인 가구 평균 사용량, 사용량 차이와 차이율을 보여준다. 선택 월까지 최근 6개월의 내 사용량과 평균 사용량 시계열을 꺾은선 그래프로 표시한다. 내 고지서가 없는 달은 값을 보간하지 않는다. 비교군·기준 연도·출처와 가중평균/일수 환산 방식, 자료의 한계를 함께 표시한다.</x:v>
       </x:c>
       <x:c r="H43" s="15" t="str">
-        <x:v>singleHouseholdComparison.tabs[]{myUsage, averageUsage, differenceUsage, differenceRate, usageUnit, comparisonLabel, sourceName, referencePeriod, calculationBasis, note}</x:v>
+        <x:v>singleHouseholdComparison.tabs[]{myUsage, averageUsage, differenceUsage, differenceRate, usageUnit, comparisonLabel, sourceName, referencePeriod, calculationBasis, note, series[]{yearMonth, myUsage, averageUsage}}</x:v>
       </x:c>
       <x:c r="I43" s="13" t="str">
         <x:v>기준선 존재</x:v>
       </x:c>
       <x:c r="J43" s="13" t="str">
-        <x:v>기준 없음 → 비교 데이터 준비 중</x:v>
+        <x:v>기준 없음 → 준비 중</x:v>
       </x:c>
       <x:c r="K43" s="13" t="str">
-        <x:v>세 항목의 사용량 차이·차이율과 비교 근거가 함께 표시된다.</x:v>
+        <x:v>세 항목의 선택 월 사용량 차이·차이율, 최근 6개월 시계열과 비교 근거가 함께 표시된다.</x:v>
       </x:c>
       <x:c r="L43" s="8" t="str">
         <x:v>P0</x:v>
@@ -4260,7 +4336,7 @@
         <x:v>AN-07</x:v>
       </x:c>
       <x:c r="P43" s="13" t="str">
-        <x:v>지역 평균 6개월 라인 차트를 1인 가구 사용량 비교 카드로 교체(C-29)</x:v>
+        <x:v>작년 동월 요금 비교 카드는 별도로 유지한다. 사용자 결측 월은 선을 연결하지 않는다(C-35).</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58.25" customHeight="1">
@@ -7412,7 +7488,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P108" t="str">
-        <x:v>정책 조건 미설정은 설정 CTA, 에코 미연동은 연동 CTA 표시(결정 C-26~C-30)</x:v>
+        <x:v>정책 조건 미설정은 설정 CTA, 에코 미연동은 연동 CTA 표시(결정 C-26~C-33)</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7608,7 +7684,7 @@
         <x:v>MY-01</x:v>
       </x:c>
       <x:c r="P112" t="str">
-        <x:v>결정 C-30</x:v>
+        <x:v>결정 C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7658,7 +7734,7 @@
         <x:v>MY-05</x:v>
       </x:c>
       <x:c r="P113" t="str">
-        <x:v>결정 C-30</x:v>
+        <x:v>결정 C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -7756,7 +7832,7 @@
         <x:v>MY-02</x:v>
       </x:c>
       <x:c r="P115" t="str">
-        <x:v>결정 C-30</x:v>
+        <x:v>결정 C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -7806,7 +7882,7 @@
         <x:v>화면 없음</x:v>
       </x:c>
       <x:c r="P116" t="str">
-        <x:v>결정 C-24·C-30</x:v>
+        <x:v>결정 C-24·C-33</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8461,7 +8537,7 @@
         <x:v>마이 선택형 정책 추천</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>당시 현재 상태·연소득 구간·가구 상태를 마이에서 저장하고 상세에서 임시 재추천하기로 했다. 입력 조건과 상세 화면 재추천 방식은 C-30에서 대체한다.</x:v>
+        <x:v>당시 현재 상태·연소득 구간·가구 상태를 마이에서 저장하고 상세에서 임시 재추천하기로 했다. 입력 조건과 상세 화면 재추천 방식은 C-33에서 대체한다.</x:v>
       </x:c>
       <x:c r="D44" t="str">
         <x:v>A-1-04~07, E-1-01, E-3-01~04</x:v>
@@ -8486,13 +8562,83 @@
         <x:v>C-30</x:v>
       </x:c>
       <x:c r="B46" t="str">
+        <x:v>What-if 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>홈(WF-06)은 헤더·감축률 카드·오늘의 실천 두 카드로 구성한다. 감축률 카드는 지급 구간과 같은 4칸 바와 목표 마커를 사용한다. 전달 리포트·목표 카드는 하단 링크로 진입하고 참여신청 배너는 제외한다.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>B-4-01, B-4-03~06, B-3-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>C-31</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>포켓 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>포켓 홈(PK-01)은 헤더·잔액 카드·추천 상품·최근 내역 순으로 구성한다. 잔액 카드에는 전환 가능한 마일리지와 출금 신청 행을 두며, 계좌번호는 포켓 관리에서 표시한다.</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>D-1-04, D-1-06, D-4-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>C-32</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>혜택 홈 확정 시안</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>혜택 홈(BN-01·BN-02)은 연동 상태 헤더·헤드라인·적립 카드·실천 항목 카드로 구성한다. 미참여 상태에는 참여 방법과 공식 누리집 이동을 제공한다.</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>C-1-01~03, C-2-01~03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>C-33</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
         <x:v>청년정책 정밀 추천</x:v>
       </x:c>
-      <x:c r="C46" t="str">
-        <x:v>승인 완료·현재 신청 가능·개인 대상·분류·지역·신청 경로가 명확한 정책만 활성화한다. 현재 상태·연소득·학력·관심 분야 1~2개를 MY-02에서 저장하며 가구·혼인 상태는 받지 않는다. 저장값은 다시 저장할 때까지 유지한다. 조건 코드 누락은 제한 없음으로 해석하지 않고, 대출·보증·보험처럼 별도 심사가 필요한 정책은 CHECK_REQUIRED로 분류한다. 명확히 ELIGIBLE인 정책만 최대 5개 추천하며 5개 미만이어도 불확실한 정책으로 채우지 않는다. MY-06은 상세 정보만 제공하며 조건 변경·임시 재추천을 제공하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="C49" t="str">
+        <x:v>승인 완료·현재 신청 가능·개인 대상·분류·지역·신청 경로가 명확한 정책만 활성화한다. 현재 상태·연소득·학력·관심 분야 1~2개를 MY-02에서 저장한다. 명확히 ELIGIBLE인 정책만 최대 5개 추천하며 MY-06은 상세 정보만 제공한다.</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
         <x:v>A-1-04~06, E-1-01, E-3-01~05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>C-34</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>미션 계절 노출 규칙</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>목표 정하기·다시 고르기는 오늘부터 회차 끝까지 남은 달의 계절과 맞는 미션을 보여준다. 이미 고른 미션은 계절과 무관하게 보여 해제할 수 있게 하며, 오늘의 실천은 오늘 계절에 맞는 미션만 노출한다.</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>B-3-03, B-3-05, C-19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>C-35</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>진단 월별 1인 가구 기준선</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>전기·가스는 KESIS 2023년 기준 14차 가구에너지패널조사 마이크로데이터의 1인 가구 월별 사용량을 가구 횡단가중치로 평균한다. 전기는 1,221가구, 가스는 연간 사용량이 있는 841가구 고정 비교군이며 월별 0 사용량을 포함한다. GET /diagnosis는 최근 6개월의 내 사용량·평균 시계열을 제공하고 사용자 결측 월은 null로 둔다. 수도는 기존 월환산 기준을 유지한다.</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>A-3-01~03, A-3-07~08</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
